--- a/testLBB.xlsx
+++ b/testLBB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Agentic World\TestDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D977A20B-157D-4B44-AB87-6BD7DE40D11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1560FCC7-620D-4492-A8AC-56BED4806FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
+    <workbookView xWindow="24876" yWindow="432" windowWidth="20736" windowHeight="11832" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -266,7 +266,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S110" authorId="1" shapeId="0" xr:uid="{8A63E9C8-CD92-458B-B088-84D814853C81}">
+    <comment ref="T110" authorId="1" shapeId="0" xr:uid="{8A63E9C8-CD92-458B-B088-84D814853C81}">
       <text>
         <r>
           <rPr>
@@ -280,7 +280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T110" authorId="1" shapeId="0" xr:uid="{1D88008F-ABE2-403D-BD05-DA3C7516B0C0}">
+    <comment ref="U110" authorId="1" shapeId="0" xr:uid="{1D74ECC9-9275-4E9C-AE52-3BDFE9ECFCC4}">
       <text>
         <r>
           <rPr>
@@ -294,6 +294,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="V110" authorId="1" shapeId="0" xr:uid="{1D88008F-ABE2-403D-BD05-DA3C7516B0C0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PIT220-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B116" authorId="2" shapeId="0" xr:uid="{4608516B-34DA-4E87-85F1-345F80F368D2}">
       <text>
         <r>
@@ -325,7 +339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S116" authorId="1" shapeId="0" xr:uid="{0B8CEC1B-26B4-4C3C-A925-678DC1401F2B}">
+    <comment ref="S116" authorId="1" shapeId="0" xr:uid="{76BD6480-6239-4C4D-BDFD-3C6A39F1852D}">
       <text>
         <r>
           <rPr>
@@ -339,6 +353,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="T116" authorId="1" shapeId="0" xr:uid="{0B8CEC1B-26B4-4C3C-A925-678DC1401F2B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PIT221-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U116" authorId="1" shapeId="0" xr:uid="{1B9DE572-7AAD-495E-BE44-47E935023FF3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PIT221-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B130" authorId="3" shapeId="0" xr:uid="{37D13463-1186-4BC6-8059-F81F589B8465}">
       <text>
         <r>
@@ -538,7 +580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S130" authorId="1" shapeId="0" xr:uid="{753B9390-143B-48FA-9947-5F6488164205}">
+    <comment ref="T130" authorId="1" shapeId="0" xr:uid="{753B9390-143B-48FA-9947-5F6488164205}">
       <text>
         <r>
           <rPr>
@@ -552,7 +594,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T130" authorId="1" shapeId="0" xr:uid="{7960D3F7-BFDD-442A-93CF-A9A8A1E2E4D7}">
+    <comment ref="U130" authorId="1" shapeId="0" xr:uid="{4A3807F1-1A47-4F70-AB47-0CF1B85AF3EF}">
       <text>
         <r>
           <rPr>
@@ -566,6 +608,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="V130" authorId="1" shapeId="0" xr:uid="{7960D3F7-BFDD-442A-93CF-A9A8A1E2E4D7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PCV220-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B132" authorId="4" shapeId="0" xr:uid="{330CC50C-0FF1-4C20-92A7-B1A460F72FE0}">
       <text>
         <r>
@@ -597,7 +653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S132" authorId="1" shapeId="0" xr:uid="{6DA8F2A9-8B9D-428F-9D70-9845AF51C35A}">
+    <comment ref="S132" authorId="1" shapeId="0" xr:uid="{7E3D0F63-17C5-4B68-81B0-505AF44336C8}">
       <text>
         <r>
           <rPr>
@@ -611,6 +667,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="T132" authorId="1" shapeId="0" xr:uid="{6DA8F2A9-8B9D-428F-9D70-9845AF51C35A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PCV221-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U132" authorId="1" shapeId="0" xr:uid="{EF64C12F-8CC0-4584-AC06-EA4E8D21F8CC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PCV221-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B139" authorId="5" shapeId="0" xr:uid="{C128BBFA-0A9E-4E10-9DCF-02753B677457}">
       <text>
         <r>
@@ -824,7 +908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S139" authorId="1" shapeId="0" xr:uid="{47BB721E-C9FF-4937-9DFA-993FC6AF140A}">
+    <comment ref="S139" authorId="1" shapeId="0" xr:uid="{D4A8F356-F2B2-42BF-8E4E-859D99CD947B}">
       <text>
         <r>
           <rPr>
@@ -838,7 +922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T139" authorId="1" shapeId="0" xr:uid="{54220527-F067-4C46-B23C-E6C35A57C74A}">
+    <comment ref="T139" authorId="1" shapeId="0" xr:uid="{47BB721E-C9FF-4937-9DFA-993FC6AF140A}">
       <text>
         <r>
           <rPr>
@@ -852,6 +936,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="U139" authorId="1" shapeId="0" xr:uid="{B074B34C-47F5-4ABB-9BBE-8BAB833C43B7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ST741</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V139" authorId="1" shapeId="0" xr:uid="{54220527-F067-4C46-B23C-E6C35A57C74A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ST741</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B187" authorId="6" shapeId="0" xr:uid="{FAC71602-7205-4D4E-A8A7-63E13947D7F3}">
       <text>
         <r>
@@ -1124,7 +1236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S212" authorId="1" shapeId="0" xr:uid="{3CCADB93-08D3-4870-B402-B5D4CA8B6140}">
+    <comment ref="S212" authorId="1" shapeId="0" xr:uid="{7D680D7E-E6FE-4E1D-B6FC-4A1A10D01B25}">
       <text>
         <r>
           <rPr>
@@ -1138,7 +1250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T212" authorId="1" shapeId="0" xr:uid="{C54015D9-2054-40AD-BFC9-F96B33814BDF}">
+    <comment ref="T212" authorId="1" shapeId="0" xr:uid="{3CCADB93-08D3-4870-B402-B5D4CA8B6140}">
       <text>
         <r>
           <rPr>
@@ -1152,6 +1264,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="U212" authorId="1" shapeId="0" xr:uid="{49C527D4-4A75-4547-A8FB-09C451686743}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>YT750</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V212" authorId="1" shapeId="0" xr:uid="{C54015D9-2054-40AD-BFC9-F96B33814BDF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>YT750</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B214" authorId="8" shapeId="0" xr:uid="{932F2D4C-D793-48A0-8BED-5F38FC3D7DAF}">
       <text>
         <r>
@@ -1309,7 +1449,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S214" authorId="1" shapeId="0" xr:uid="{44EC05B4-875B-45AE-A54A-9DD618097B9A}">
+    <comment ref="S214" authorId="1" shapeId="0" xr:uid="{AC43E90C-8B87-49A5-B403-13A1F4FAA847}">
       <text>
         <r>
           <rPr>
@@ -1323,7 +1463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I216" authorId="1" shapeId="0" xr:uid="{17CB5577-3ABD-4AEA-83D7-68A683ADAE56}">
+    <comment ref="T214" authorId="1" shapeId="0" xr:uid="{44EC05B4-875B-45AE-A54A-9DD618097B9A}">
       <text>
         <r>
           <rPr>
@@ -1333,11 +1473,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>TT730a</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J216" authorId="1" shapeId="0" xr:uid="{90ADF558-91A0-4E4C-808B-786CD0944716}">
+          <t>PT376-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U214" authorId="1" shapeId="0" xr:uid="{23E45367-7D17-49C2-8FC9-C98E3FF1792E}">
       <text>
         <r>
           <rPr>
@@ -1347,11 +1487,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>TT730a</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K216" authorId="1" shapeId="0" xr:uid="{F814AE73-B49C-4857-94D2-5D83D6E75CE1}">
+          <t>PT376-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I216" authorId="1" shapeId="0" xr:uid="{17CB5577-3ABD-4AEA-83D7-68A683ADAE56}">
       <text>
         <r>
           <rPr>
@@ -1365,7 +1505,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K217" authorId="1" shapeId="0" xr:uid="{8470B15F-7325-4951-83C8-82D183ACB1B9}">
+    <comment ref="J216" authorId="1" shapeId="0" xr:uid="{90ADF558-91A0-4E4C-808B-786CD0944716}">
       <text>
         <r>
           <rPr>
@@ -1375,6 +1515,34 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t>TT730a</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K216" authorId="1" shapeId="0" xr:uid="{F814AE73-B49C-4857-94D2-5D83D6E75CE1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT730a</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K217" authorId="1" shapeId="0" xr:uid="{8470B15F-7325-4951-83C8-82D183ACB1B9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t>TT731A</t>
         </r>
       </text>
@@ -1526,7 +1694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S218" authorId="19" shapeId="0" xr:uid="{995B3D88-6D95-4D5B-9786-EB1EE33C8F08}">
+    <comment ref="S218" authorId="18" shapeId="0" xr:uid="{82388207-06CD-4B3E-8C3B-18201294153F}">
       <text>
         <r>
           <rPr>
@@ -1540,7 +1708,35 @@
         </r>
       </text>
     </comment>
-    <comment ref="T218" authorId="20" shapeId="0" xr:uid="{5A7995E4-2A1C-4734-8159-384E51055A94}">
+    <comment ref="T218" authorId="19" shapeId="0" xr:uid="{995B3D88-6D95-4D5B-9786-EB1EE33C8F08}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="MS Sans Serif"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sensor: TT733</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U218" authorId="19" shapeId="0" xr:uid="{AD8A4D06-417D-4507-A78A-558D5925CF3E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="MS Sans Serif"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sensor: TT733</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V218" authorId="20" shapeId="0" xr:uid="{5A7995E4-2A1C-4734-8159-384E51055A94}">
       <text>
         <r>
           <rPr>
@@ -1767,7 +1963,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S223" authorId="1" shapeId="0" xr:uid="{A2AD5EE8-9DAE-41A2-9707-E8A93AA509D7}">
+    <comment ref="S223" authorId="1" shapeId="0" xr:uid="{FF801CC6-0702-41B5-815A-842DF01959DF}">
       <text>
         <r>
           <rPr>
@@ -1781,7 +1977,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T223" authorId="1" shapeId="0" xr:uid="{AC1B3E75-0789-4CC7-9153-9855182D4BA3}">
+    <comment ref="T223" authorId="1" shapeId="0" xr:uid="{A2AD5EE8-9DAE-41A2-9707-E8A93AA509D7}">
       <text>
         <r>
           <rPr>
@@ -1795,6 +1991,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="U223" authorId="1" shapeId="0" xr:uid="{AAD01F94-97AC-482A-ABA1-73AF97E1CB5F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT410-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V223" authorId="1" shapeId="0" xr:uid="{AC1B3E75-0789-4CC7-9153-9855182D4BA3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT410-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B243" authorId="22" shapeId="0" xr:uid="{C29E9803-A59F-4197-99DC-10131D1A8691}">
       <text>
         <r>
@@ -2024,7 +2248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S248" authorId="1" shapeId="0" xr:uid="{91741EB9-BD1E-4DE2-8027-3330258F0BE1}">
+    <comment ref="S248" authorId="1" shapeId="0" xr:uid="{819B2302-BA41-48C3-86C7-003ADF711ECB}">
       <text>
         <r>
           <rPr>
@@ -2038,7 +2262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T248" authorId="1" shapeId="0" xr:uid="{B6B88AC9-B4B9-4626-998A-152D39BB8C8F}">
+    <comment ref="T248" authorId="1" shapeId="0" xr:uid="{91741EB9-BD1E-4DE2-8027-3330258F0BE1}">
       <text>
         <r>
           <rPr>
@@ -2052,7 +2276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P251" authorId="1" shapeId="0" xr:uid="{4C0CE6CB-5FB3-40F0-98A9-DAFEDBA61E56}">
+    <comment ref="U248" authorId="1" shapeId="0" xr:uid="{ADC20AEA-2C08-4103-B12D-9EC0F1F26B07}">
       <text>
         <r>
           <rPr>
@@ -2062,6 +2286,34 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t>AV375-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V248" authorId="1" shapeId="0" xr:uid="{B6B88AC9-B4B9-4626-998A-152D39BB8C8F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>AV375-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P251" authorId="1" shapeId="0" xr:uid="{4C0CE6CB-5FB3-40F0-98A9-DAFEDBA61E56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t>AV441-1</t>
         </r>
       </text>
@@ -2310,7 +2562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S253" authorId="1" shapeId="0" xr:uid="{CA07E862-A447-4473-BB0A-81C0A0734E5C}">
+    <comment ref="S253" authorId="1" shapeId="0" xr:uid="{EBDF1BB8-3B68-4AA9-8A1E-43EF4DD43FFD}">
       <text>
         <r>
           <rPr>
@@ -2324,7 +2576,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T253" authorId="1" shapeId="0" xr:uid="{4D07A8FF-3F1A-4CBB-8D69-156E718CA685}">
+    <comment ref="T253" authorId="1" shapeId="0" xr:uid="{CA07E862-A447-4473-BB0A-81C0A0734E5C}">
       <text>
         <r>
           <rPr>
@@ -2338,7 +2590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E354" authorId="1" shapeId="0" xr:uid="{C0B47CE5-D73E-476B-A5B9-42559C542AEB}">
+    <comment ref="U253" authorId="1" shapeId="0" xr:uid="{1001DC21-F748-414E-A177-FE216CEE24B4}">
       <text>
         <r>
           <rPr>
@@ -2348,11 +2600,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>FIT220-1</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F354" authorId="1" shapeId="0" xr:uid="{8AB58700-0B5F-4791-8C69-F153ED1BB30F}">
+          <t>506c</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V253" authorId="1" shapeId="0" xr:uid="{4D07A8FF-3F1A-4CBB-8D69-156E718CA685}">
       <text>
         <r>
           <rPr>
@@ -2362,11 +2614,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>FIT220-1</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G354" authorId="1" shapeId="0" xr:uid="{E1FDF170-EC3C-4C3E-9D47-490D5F042A9C}">
+          <t>506c</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E354" authorId="1" shapeId="0" xr:uid="{C0B47CE5-D73E-476B-A5B9-42559C542AEB}">
       <text>
         <r>
           <rPr>
@@ -2380,7 +2632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H354" authorId="1" shapeId="0" xr:uid="{712E4485-1474-4A27-BA32-2C9EB831D78F}">
+    <comment ref="F354" authorId="1" shapeId="0" xr:uid="{8AB58700-0B5F-4791-8C69-F153ED1BB30F}">
       <text>
         <r>
           <rPr>
@@ -2394,7 +2646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I354" authorId="1" shapeId="0" xr:uid="{36FF1E64-6471-4653-B1F0-0FAA16B29916}">
+    <comment ref="G354" authorId="1" shapeId="0" xr:uid="{E1FDF170-EC3C-4C3E-9D47-490D5F042A9C}">
       <text>
         <r>
           <rPr>
@@ -2408,7 +2660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J354" authorId="1" shapeId="0" xr:uid="{7DBD095E-E2BC-4769-9A92-480138A3F271}">
+    <comment ref="H354" authorId="1" shapeId="0" xr:uid="{712E4485-1474-4A27-BA32-2C9EB831D78F}">
       <text>
         <r>
           <rPr>
@@ -2422,7 +2674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K354" authorId="1" shapeId="0" xr:uid="{E1A905A5-6F64-4A3F-A10D-A47C8A33385D}">
+    <comment ref="I354" authorId="1" shapeId="0" xr:uid="{36FF1E64-6471-4653-B1F0-0FAA16B29916}">
       <text>
         <r>
           <rPr>
@@ -2436,7 +2688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L354" authorId="1" shapeId="0" xr:uid="{4903F214-4F8B-4EE0-9613-1279DF5648C1}">
+    <comment ref="J354" authorId="1" shapeId="0" xr:uid="{7DBD095E-E2BC-4769-9A92-480138A3F271}">
       <text>
         <r>
           <rPr>
@@ -2450,7 +2702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M354" authorId="1" shapeId="0" xr:uid="{B5F82680-9202-4A15-8853-FC83C7161852}">
+    <comment ref="K354" authorId="1" shapeId="0" xr:uid="{E1A905A5-6F64-4A3F-A10D-A47C8A33385D}">
       <text>
         <r>
           <rPr>
@@ -2464,7 +2716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N354" authorId="1" shapeId="0" xr:uid="{AB65A6B4-D5CB-45FA-BB16-8FCDA0B1CD01}">
+    <comment ref="L354" authorId="1" shapeId="0" xr:uid="{4903F214-4F8B-4EE0-9613-1279DF5648C1}">
       <text>
         <r>
           <rPr>
@@ -2478,7 +2730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O354" authorId="1" shapeId="0" xr:uid="{67D6C1B9-A0B6-4543-BB08-43568A6FD2FD}">
+    <comment ref="M354" authorId="1" shapeId="0" xr:uid="{B5F82680-9202-4A15-8853-FC83C7161852}">
       <text>
         <r>
           <rPr>
@@ -2492,7 +2744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P354" authorId="1" shapeId="0" xr:uid="{ED479785-87E9-46F3-83B9-5E0B297343AB}">
+    <comment ref="N354" authorId="1" shapeId="0" xr:uid="{AB65A6B4-D5CB-45FA-BB16-8FCDA0B1CD01}">
       <text>
         <r>
           <rPr>
@@ -2506,7 +2758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q354" authorId="1" shapeId="0" xr:uid="{9B09027D-39F7-4771-A6CD-CEF9292914CF}">
+    <comment ref="O354" authorId="1" shapeId="0" xr:uid="{67D6C1B9-A0B6-4543-BB08-43568A6FD2FD}">
       <text>
         <r>
           <rPr>
@@ -2520,7 +2772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R354" authorId="1" shapeId="0" xr:uid="{C03CC508-BABC-4F41-AAA6-893E2A965F97}">
+    <comment ref="P354" authorId="1" shapeId="0" xr:uid="{ED479785-87E9-46F3-83B9-5E0B297343AB}">
       <text>
         <r>
           <rPr>
@@ -2534,7 +2786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S354" authorId="1" shapeId="0" xr:uid="{B9AEFF40-72C7-42E9-82E6-42F1ACDF9CE9}">
+    <comment ref="Q354" authorId="1" shapeId="0" xr:uid="{9B09027D-39F7-4771-A6CD-CEF9292914CF}">
       <text>
         <r>
           <rPr>
@@ -2548,7 +2800,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T354" authorId="1" shapeId="0" xr:uid="{33111B3A-0575-4EDB-BD9B-24B5FB0F6DCA}">
+    <comment ref="R354" authorId="1" shapeId="0" xr:uid="{C03CC508-BABC-4F41-AAA6-893E2A965F97}">
       <text>
         <r>
           <rPr>
@@ -2562,7 +2814,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S355" authorId="1" shapeId="0" xr:uid="{440A1C78-42D9-460C-B33F-02721CBB208A}">
+    <comment ref="S354" authorId="1" shapeId="0" xr:uid="{7878160C-DFE2-43A4-B56B-5FD1C93BB65A}">
       <text>
         <r>
           <rPr>
@@ -2572,6 +2824,76 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t>FIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T354" authorId="1" shapeId="0" xr:uid="{B9AEFF40-72C7-42E9-82E6-42F1ACDF9CE9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U354" authorId="1" shapeId="0" xr:uid="{001518F0-2E57-4EF5-954F-D2AB688DAFA4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V354" authorId="1" shapeId="0" xr:uid="{33111B3A-0575-4EDB-BD9B-24B5FB0F6DCA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T355" authorId="1" shapeId="0" xr:uid="{440A1C78-42D9-460C-B33F-02721CBB208A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIT221-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U355" authorId="1" shapeId="0" xr:uid="{E6143D56-1F6F-4ADC-9F4E-D4A20B818F3E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t>FIT221-1</t>
         </r>
       </text>
@@ -2581,7 +2903,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2773" uniqueCount="293">
   <si>
     <t>Tag Label</t>
   </si>
@@ -3444,13 +3766,22 @@
     <t>CLARA 750H</t>
   </si>
   <si>
-    <t>CR 450/750</t>
-  </si>
-  <si>
-    <t>PP 450/750</t>
-  </si>
-  <si>
     <t>KR 400</t>
+  </si>
+  <si>
+    <t>MachineConfig</t>
+  </si>
+  <si>
+    <t>CR 450</t>
+  </si>
+  <si>
+    <t>CR 750</t>
+  </si>
+  <si>
+    <t>PP 450</t>
+  </si>
+  <si>
+    <t>PP 750</t>
   </si>
 </sst>
 </file>
@@ -4159,7 +4490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}">
-  <dimension ref="B2:T401"/>
+  <dimension ref="B1:V401"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.75" style="1" customWidth="1"/>
@@ -4167,15 +4498,74 @@
     <col min="4" max="4" width="20.75" style="1" customWidth="1"/>
     <col min="5" max="6" width="2.25" style="10" customWidth="1"/>
     <col min="7" max="8" width="2.875" style="10" customWidth="1"/>
-    <col min="9" max="11" width="2.25" style="10" customWidth="1"/>
+    <col min="9" max="11" width="6.75" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="2.625" style="10" customWidth="1"/>
     <col min="15" max="15" width="2.875" style="10" customWidth="1"/>
     <col min="16" max="16" width="2.625" style="10" customWidth="1"/>
-    <col min="17" max="19" width="2.875" style="10" customWidth="1"/>
-    <col min="20" max="20" width="2.625" style="10" customWidth="1"/>
+    <col min="17" max="21" width="2.875" style="10" customWidth="1"/>
+    <col min="22" max="22" width="2.625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" ht="58.5">
+    <row r="1" spans="2:22" ht="35.25" customHeight="1">
+      <c r="D1" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E1" s="10">
+        <v>7</v>
+      </c>
+      <c r="F1" s="10">
+        <v>8</v>
+      </c>
+      <c r="G1" s="10">
+        <v>9</v>
+      </c>
+      <c r="H1" s="10">
+        <v>10</v>
+      </c>
+      <c r="I1" s="10">
+        <v>11</v>
+      </c>
+      <c r="J1" s="10">
+        <v>12</v>
+      </c>
+      <c r="K1" s="10">
+        <v>13</v>
+      </c>
+      <c r="L1" s="10">
+        <v>9</v>
+      </c>
+      <c r="M1" s="10">
+        <v>10</v>
+      </c>
+      <c r="N1" s="10">
+        <v>11</v>
+      </c>
+      <c r="O1" s="10">
+        <v>12</v>
+      </c>
+      <c r="P1" s="10">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="10">
+        <v>14</v>
+      </c>
+      <c r="R1" s="10">
+        <v>2</v>
+      </c>
+      <c r="S1" s="10">
+        <v>3</v>
+      </c>
+      <c r="T1" s="10">
+        <v>2</v>
+      </c>
+      <c r="U1" s="10">
+        <v>3</v>
+      </c>
+      <c r="V1" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="2:22" ht="58.5">
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
@@ -4219,16 +4609,22 @@
         <v>286</v>
       </c>
       <c r="R2" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="V2" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="S2" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="T2" s="21" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="3" spans="2:20">
+    </row>
+    <row r="3" spans="2:22">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -4254,8 +4650,10 @@
       <c r="R3" s="12"/>
       <c r="S3" s="12"/>
       <c r="T3" s="12"/>
-    </row>
-    <row r="4" spans="2:20">
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+    </row>
+    <row r="4" spans="2:22">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -4275,8 +4673,10 @@
       <c r="R4" s="13"/>
       <c r="S4" s="13"/>
       <c r="T4" s="13"/>
-    </row>
-    <row r="5" spans="2:20">
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+    </row>
+    <row r="5" spans="2:22">
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -4296,8 +4696,10 @@
       <c r="R5" s="14"/>
       <c r="S5" s="14"/>
       <c r="T5" s="14"/>
-    </row>
-    <row r="6" spans="2:20">
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+    </row>
+    <row r="6" spans="2:22">
       <c r="B6" s="4"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -4317,8 +4719,10 @@
       <c r="R6" s="13"/>
       <c r="S6" s="13"/>
       <c r="T6" s="13"/>
-    </row>
-    <row r="7" spans="2:20">
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+    </row>
+    <row r="7" spans="2:22">
       <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
@@ -4374,8 +4778,14 @@
       <c r="T7" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="8" spans="2:20">
+      <c r="U7" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V7" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22">
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
@@ -4426,9 +4836,15 @@
       <c r="S8" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T8" s="13"/>
-    </row>
-    <row r="9" spans="2:20">
+      <c r="T8" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U8" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V8" s="13"/>
+    </row>
+    <row r="9" spans="2:22">
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
@@ -4479,9 +4895,15 @@
       <c r="S9" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T9" s="13"/>
-    </row>
-    <row r="10" spans="2:20">
+      <c r="T9" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V9" s="13"/>
+    </row>
+    <row r="10" spans="2:22">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -4510,9 +4932,15 @@
       <c r="S10" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T10" s="13"/>
-    </row>
-    <row r="11" spans="2:20">
+      <c r="T10" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U10" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V10" s="13"/>
+    </row>
+    <row r="11" spans="2:22">
       <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
@@ -4568,8 +4996,14 @@
       <c r="T11" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="12" spans="2:20">
+      <c r="U11" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V11" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22">
       <c r="B12" s="4" t="s">
         <v>6</v>
       </c>
@@ -4625,8 +5059,14 @@
       <c r="T12" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="13" spans="2:20">
+      <c r="U12" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V12" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22">
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
@@ -4682,8 +5122,14 @@
       <c r="T13" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="14" spans="2:20">
+      <c r="U13" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V13" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22">
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
@@ -4707,8 +5153,10 @@
       <c r="R14" s="13"/>
       <c r="S14" s="13"/>
       <c r="T14" s="13"/>
-    </row>
-    <row r="15" spans="2:20">
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+    </row>
+    <row r="15" spans="2:22">
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
@@ -4732,8 +5180,10 @@
       <c r="R15" s="13"/>
       <c r="S15" s="13"/>
       <c r="T15" s="13"/>
-    </row>
-    <row r="16" spans="2:20">
+      <c r="U15" s="13"/>
+      <c r="V15" s="13"/>
+    </row>
+    <row r="16" spans="2:22">
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
@@ -4783,8 +5233,10 @@
       <c r="R16" s="13"/>
       <c r="S16" s="13"/>
       <c r="T16" s="13"/>
-    </row>
-    <row r="17" spans="2:20">
+      <c r="U16" s="13"/>
+      <c r="V16" s="13"/>
+    </row>
+    <row r="17" spans="2:22">
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
@@ -4832,12 +5284,16 @@
         <v>141</v>
       </c>
       <c r="R17" s="13"/>
-      <c r="S17" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="T17" s="13"/>
-    </row>
-    <row r="18" spans="2:20">
+      <c r="S17" s="13"/>
+      <c r="T17" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U17" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V17" s="13"/>
+    </row>
+    <row r="18" spans="2:22">
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
@@ -4877,8 +5333,10 @@
       <c r="R18" s="13"/>
       <c r="S18" s="13"/>
       <c r="T18" s="13"/>
-    </row>
-    <row r="19" spans="2:20">
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+    </row>
+    <row r="19" spans="2:22">
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
@@ -4902,8 +5360,10 @@
       <c r="R19" s="13"/>
       <c r="S19" s="13"/>
       <c r="T19" s="13"/>
-    </row>
-    <row r="20" spans="2:20">
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+    </row>
+    <row r="20" spans="2:22">
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
@@ -4927,8 +5387,10 @@
       <c r="R20" s="13"/>
       <c r="S20" s="13"/>
       <c r="T20" s="13"/>
-    </row>
-    <row r="21" spans="2:20">
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+    </row>
+    <row r="21" spans="2:22">
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
@@ -4952,8 +5414,10 @@
       <c r="R21" s="13"/>
       <c r="S21" s="13"/>
       <c r="T21" s="13"/>
-    </row>
-    <row r="22" spans="2:20">
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+    </row>
+    <row r="22" spans="2:22">
       <c r="B22" s="4" t="s">
         <v>12</v>
       </c>
@@ -5011,8 +5475,14 @@
       <c r="T22" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="23" spans="2:20">
+      <c r="U22" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V22" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -5032,8 +5502,10 @@
       <c r="R23" s="13"/>
       <c r="S23" s="13"/>
       <c r="T23" s="13"/>
-    </row>
-    <row r="24" spans="2:20">
+      <c r="U23" s="13"/>
+      <c r="V23" s="13"/>
+    </row>
+    <row r="24" spans="2:22">
       <c r="B24" s="6" t="s">
         <v>13</v>
       </c>
@@ -5089,8 +5561,14 @@
       <c r="T24" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="25" spans="2:20">
+      <c r="U24" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V24" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
       <c r="B25" s="6" t="s">
         <v>13</v>
       </c>
@@ -5146,8 +5624,14 @@
       <c r="T25" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="26" spans="2:20">
+      <c r="U25" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V25" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
@@ -5187,8 +5671,10 @@
       <c r="R26" s="13"/>
       <c r="S26" s="13"/>
       <c r="T26" s="13"/>
-    </row>
-    <row r="27" spans="2:20">
+      <c r="U26" s="13"/>
+      <c r="V26" s="13"/>
+    </row>
+    <row r="27" spans="2:22">
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
@@ -5228,8 +5714,10 @@
       <c r="R27" s="13"/>
       <c r="S27" s="13"/>
       <c r="T27" s="13"/>
-    </row>
-    <row r="28" spans="2:20">
+      <c r="U27" s="13"/>
+      <c r="V27" s="13"/>
+    </row>
+    <row r="28" spans="2:22">
       <c r="B28" s="6" t="s">
         <v>15</v>
       </c>
@@ -5269,8 +5757,10 @@
       <c r="R28" s="13"/>
       <c r="S28" s="13"/>
       <c r="T28" s="13"/>
-    </row>
-    <row r="29" spans="2:20">
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+    </row>
+    <row r="29" spans="2:22">
       <c r="B29" s="6" t="s">
         <v>15</v>
       </c>
@@ -5310,8 +5800,10 @@
       <c r="R29" s="13"/>
       <c r="S29" s="13"/>
       <c r="T29" s="13"/>
-    </row>
-    <row r="30" spans="2:20">
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+    </row>
+    <row r="30" spans="2:22">
       <c r="B30" s="6" t="s">
         <v>16</v>
       </c>
@@ -5349,8 +5841,10 @@
       <c r="R30" s="13"/>
       <c r="S30" s="13"/>
       <c r="T30" s="13"/>
-    </row>
-    <row r="31" spans="2:20">
+      <c r="U30" s="13"/>
+      <c r="V30" s="13"/>
+    </row>
+    <row r="31" spans="2:22">
       <c r="B31" s="6" t="s">
         <v>16</v>
       </c>
@@ -5388,8 +5882,10 @@
       <c r="R31" s="13"/>
       <c r="S31" s="13"/>
       <c r="T31" s="13"/>
-    </row>
-    <row r="32" spans="2:20">
+      <c r="U31" s="13"/>
+      <c r="V31" s="13"/>
+    </row>
+    <row r="32" spans="2:22">
       <c r="B32" s="6" t="s">
         <v>17</v>
       </c>
@@ -5437,14 +5933,18 @@
         <v>140</v>
       </c>
       <c r="R32" s="13"/>
-      <c r="S32" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="S32" s="13"/>
       <c r="T32" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" spans="2:20">
+      <c r="U32" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V32" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22">
       <c r="B33" s="6" t="s">
         <v>17</v>
       </c>
@@ -5492,14 +5992,18 @@
         <v>140</v>
       </c>
       <c r="R33" s="13"/>
-      <c r="S33" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="S33" s="13"/>
       <c r="T33" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="34" spans="2:20">
+      <c r="U33" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V33" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22">
       <c r="B34" s="6" t="s">
         <v>18</v>
       </c>
@@ -5528,9 +6032,15 @@
       <c r="S34" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T34" s="13"/>
-    </row>
-    <row r="35" spans="2:20">
+      <c r="T34" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U34" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V34" s="13"/>
+    </row>
+    <row r="35" spans="2:22">
       <c r="B35" s="6" t="s">
         <v>18</v>
       </c>
@@ -5559,9 +6069,15 @@
       <c r="S35" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T35" s="13"/>
-    </row>
-    <row r="36" spans="2:20">
+      <c r="T35" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U35" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V35" s="13"/>
+    </row>
+    <row r="36" spans="2:22">
       <c r="B36" s="6" t="s">
         <v>19</v>
       </c>
@@ -5599,8 +6115,10 @@
       <c r="R36" s="13"/>
       <c r="S36" s="13"/>
       <c r="T36" s="13"/>
-    </row>
-    <row r="37" spans="2:20">
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+    </row>
+    <row r="37" spans="2:22">
       <c r="B37" s="7" t="s">
         <v>19</v>
       </c>
@@ -5638,8 +6156,10 @@
       <c r="R37" s="15"/>
       <c r="S37" s="15"/>
       <c r="T37" s="15"/>
-    </row>
-    <row r="38" spans="2:20">
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+    </row>
+    <row r="38" spans="2:22">
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
@@ -5663,8 +6183,10 @@
       <c r="R38" s="13"/>
       <c r="S38" s="13"/>
       <c r="T38" s="13"/>
-    </row>
-    <row r="39" spans="2:20">
+      <c r="U38" s="13"/>
+      <c r="V38" s="13"/>
+    </row>
+    <row r="39" spans="2:22">
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
@@ -5688,8 +6210,10 @@
       <c r="R39" s="13"/>
       <c r="S39" s="13"/>
       <c r="T39" s="13"/>
-    </row>
-    <row r="40" spans="2:20">
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+    </row>
+    <row r="40" spans="2:22">
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -5709,8 +6233,10 @@
       <c r="R40" s="13"/>
       <c r="S40" s="13"/>
       <c r="T40" s="13"/>
-    </row>
-    <row r="41" spans="2:20">
+      <c r="U40" s="13"/>
+      <c r="V40" s="13"/>
+    </row>
+    <row r="41" spans="2:22">
       <c r="B41" s="7" t="s">
         <v>20</v>
       </c>
@@ -5766,8 +6292,14 @@
       <c r="T41" s="15" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="42" spans="2:20">
+      <c r="U41" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="V41" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22">
       <c r="B42" s="6" t="s">
         <v>20</v>
       </c>
@@ -5823,8 +6355,14 @@
       <c r="T42" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="2:20">
+      <c r="U42" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V42" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22">
       <c r="B43" s="6" t="s">
         <v>21</v>
       </c>
@@ -5880,8 +6418,14 @@
       <c r="T43" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="44" spans="2:20">
+      <c r="U43" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V43" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22">
       <c r="B44" s="6" t="s">
         <v>21</v>
       </c>
@@ -5937,8 +6481,14 @@
       <c r="T44" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="45" spans="2:20">
+      <c r="U44" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V44" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22">
       <c r="B45" s="6" t="s">
         <v>22</v>
       </c>
@@ -5994,8 +6544,14 @@
       <c r="T45" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="46" spans="2:20">
+      <c r="U45" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V45" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22">
       <c r="B46" s="6" t="s">
         <v>22</v>
       </c>
@@ -6051,8 +6607,14 @@
       <c r="T46" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="47" spans="2:20">
+      <c r="U46" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V46" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22">
       <c r="B47" s="6" t="s">
         <v>23</v>
       </c>
@@ -6101,11 +6663,13 @@
       </c>
       <c r="R47" s="13"/>
       <c r="S47" s="13"/>
-      <c r="T47" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20">
+      <c r="T47" s="13"/>
+      <c r="U47" s="13"/>
+      <c r="V47" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22">
       <c r="B48" s="6" t="s">
         <v>23</v>
       </c>
@@ -6154,11 +6718,13 @@
       </c>
       <c r="R48" s="13"/>
       <c r="S48" s="13"/>
-      <c r="T48" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="49" spans="2:20">
+      <c r="T48" s="13"/>
+      <c r="U48" s="13"/>
+      <c r="V48" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="2:22">
       <c r="B49" s="6" t="s">
         <v>24</v>
       </c>
@@ -6206,14 +6772,18 @@
         <v>140</v>
       </c>
       <c r="R49" s="13"/>
-      <c r="S49" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="S49" s="13"/>
       <c r="T49" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="50" spans="2:20">
+      <c r="U49" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V49" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="2:22">
       <c r="B50" s="6" t="s">
         <v>24</v>
       </c>
@@ -6261,14 +6831,18 @@
         <v>140</v>
       </c>
       <c r="R50" s="13"/>
-      <c r="S50" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="S50" s="13"/>
       <c r="T50" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="51" spans="2:20">
+      <c r="U50" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V50" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="2:22">
       <c r="B51" s="6" t="s">
         <v>25</v>
       </c>
@@ -6317,11 +6891,13 @@
       </c>
       <c r="R51" s="13"/>
       <c r="S51" s="13"/>
-      <c r="T51" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="52" spans="2:20">
+      <c r="T51" s="13"/>
+      <c r="U51" s="13"/>
+      <c r="V51" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="2:22">
       <c r="B52" s="6" t="s">
         <v>25</v>
       </c>
@@ -6370,11 +6946,13 @@
       </c>
       <c r="R52" s="13"/>
       <c r="S52" s="13"/>
-      <c r="T52" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="53" spans="2:20">
+      <c r="T52" s="13"/>
+      <c r="U52" s="13"/>
+      <c r="V52" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="2:22">
       <c r="B53" s="6" t="s">
         <v>26</v>
       </c>
@@ -6410,8 +6988,10 @@
       <c r="R53" s="13"/>
       <c r="S53" s="13"/>
       <c r="T53" s="13"/>
-    </row>
-    <row r="54" spans="2:20">
+      <c r="U53" s="13"/>
+      <c r="V53" s="13"/>
+    </row>
+    <row r="54" spans="2:22">
       <c r="B54" s="6" t="s">
         <v>26</v>
       </c>
@@ -6447,8 +7027,10 @@
       <c r="R54" s="13"/>
       <c r="S54" s="13"/>
       <c r="T54" s="13"/>
-    </row>
-    <row r="55" spans="2:20">
+      <c r="U54" s="13"/>
+      <c r="V54" s="13"/>
+    </row>
+    <row r="55" spans="2:22">
       <c r="B55" s="5" t="s">
         <v>8</v>
       </c>
@@ -6472,8 +7054,10 @@
       <c r="R55" s="13"/>
       <c r="S55" s="13"/>
       <c r="T55" s="13"/>
-    </row>
-    <row r="56" spans="2:20">
+      <c r="U55" s="13"/>
+      <c r="V55" s="13"/>
+    </row>
+    <row r="56" spans="2:22">
       <c r="B56" s="5" t="s">
         <v>8</v>
       </c>
@@ -6497,8 +7081,10 @@
       <c r="R56" s="13"/>
       <c r="S56" s="13"/>
       <c r="T56" s="13"/>
-    </row>
-    <row r="57" spans="2:20">
+      <c r="U56" s="13"/>
+      <c r="V56" s="13"/>
+    </row>
+    <row r="57" spans="2:22">
       <c r="B57" s="6"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -6518,8 +7104,10 @@
       <c r="R57" s="13"/>
       <c r="S57" s="13"/>
       <c r="T57" s="13"/>
-    </row>
-    <row r="58" spans="2:20">
+      <c r="U57" s="13"/>
+      <c r="V57" s="13"/>
+    </row>
+    <row r="58" spans="2:22">
       <c r="B58" s="6" t="s">
         <v>27</v>
       </c>
@@ -6557,8 +7145,10 @@
       <c r="R58" s="13"/>
       <c r="S58" s="13"/>
       <c r="T58" s="13"/>
-    </row>
-    <row r="59" spans="2:20">
+      <c r="U58" s="13"/>
+      <c r="V58" s="13"/>
+    </row>
+    <row r="59" spans="2:22">
       <c r="B59" s="6" t="s">
         <v>27</v>
       </c>
@@ -6596,8 +7186,10 @@
       <c r="R59" s="13"/>
       <c r="S59" s="13"/>
       <c r="T59" s="13"/>
-    </row>
-    <row r="60" spans="2:20">
+      <c r="U59" s="13"/>
+      <c r="V59" s="13"/>
+    </row>
+    <row r="60" spans="2:22">
       <c r="B60" s="5" t="s">
         <v>8</v>
       </c>
@@ -6621,8 +7213,10 @@
       <c r="R60" s="13"/>
       <c r="S60" s="13"/>
       <c r="T60" s="13"/>
-    </row>
-    <row r="61" spans="2:20">
+      <c r="U60" s="13"/>
+      <c r="V60" s="13"/>
+    </row>
+    <row r="61" spans="2:22">
       <c r="B61" s="5" t="s">
         <v>8</v>
       </c>
@@ -6646,8 +7240,10 @@
       <c r="R61" s="13"/>
       <c r="S61" s="13"/>
       <c r="T61" s="13"/>
-    </row>
-    <row r="62" spans="2:20">
+      <c r="U61" s="13"/>
+      <c r="V61" s="13"/>
+    </row>
+    <row r="62" spans="2:22">
       <c r="B62" s="6" t="s">
         <v>28</v>
       </c>
@@ -6694,9 +7290,15 @@
       <c r="S62" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T62" s="13"/>
-    </row>
-    <row r="63" spans="2:20">
+      <c r="T62" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U62" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V62" s="13"/>
+    </row>
+    <row r="63" spans="2:22">
       <c r="B63" s="6" t="s">
         <v>28</v>
       </c>
@@ -6743,9 +7345,15 @@
       <c r="S63" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T63" s="13"/>
-    </row>
-    <row r="64" spans="2:20">
+      <c r="T63" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U63" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V63" s="13"/>
+    </row>
+    <row r="64" spans="2:22">
       <c r="B64" s="6" t="s">
         <v>29</v>
       </c>
@@ -6792,9 +7400,15 @@
       <c r="S64" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T64" s="13"/>
-    </row>
-    <row r="65" spans="2:20">
+      <c r="T64" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U64" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V64" s="13"/>
+    </row>
+    <row r="65" spans="2:22">
       <c r="B65" s="6" t="s">
         <v>29</v>
       </c>
@@ -6841,9 +7455,15 @@
       <c r="S65" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T65" s="13"/>
-    </row>
-    <row r="66" spans="2:20">
+      <c r="T65" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U65" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V65" s="13"/>
+    </row>
+    <row r="66" spans="2:22">
       <c r="B66" s="6" t="s">
         <v>30</v>
       </c>
@@ -6872,9 +7492,15 @@
       <c r="S66" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T66" s="13"/>
-    </row>
-    <row r="67" spans="2:20">
+      <c r="T66" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U66" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V66" s="13"/>
+    </row>
+    <row r="67" spans="2:22">
       <c r="B67" s="6" t="s">
         <v>30</v>
       </c>
@@ -6903,9 +7529,15 @@
       <c r="S67" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T67" s="13"/>
-    </row>
-    <row r="68" spans="2:20">
+      <c r="T67" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U67" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V67" s="13"/>
+    </row>
+    <row r="68" spans="2:22">
       <c r="B68" s="5" t="s">
         <v>8</v>
       </c>
@@ -6929,8 +7561,10 @@
       <c r="R68" s="13"/>
       <c r="S68" s="13"/>
       <c r="T68" s="13"/>
-    </row>
-    <row r="69" spans="2:20">
+      <c r="U68" s="13"/>
+      <c r="V68" s="13"/>
+    </row>
+    <row r="69" spans="2:22">
       <c r="B69" s="5" t="s">
         <v>8</v>
       </c>
@@ -6954,8 +7588,10 @@
       <c r="R69" s="13"/>
       <c r="S69" s="13"/>
       <c r="T69" s="13"/>
-    </row>
-    <row r="70" spans="2:20">
+      <c r="U69" s="13"/>
+      <c r="V69" s="13"/>
+    </row>
+    <row r="70" spans="2:22">
       <c r="B70" s="5" t="s">
         <v>8</v>
       </c>
@@ -6979,8 +7615,10 @@
       <c r="R70" s="13"/>
       <c r="S70" s="13"/>
       <c r="T70" s="13"/>
-    </row>
-    <row r="71" spans="2:20">
+      <c r="U70" s="13"/>
+      <c r="V70" s="13"/>
+    </row>
+    <row r="71" spans="2:22">
       <c r="B71" s="5" t="s">
         <v>8</v>
       </c>
@@ -7004,8 +7642,10 @@
       <c r="R71" s="13"/>
       <c r="S71" s="13"/>
       <c r="T71" s="13"/>
-    </row>
-    <row r="72" spans="2:20">
+      <c r="U71" s="13"/>
+      <c r="V71" s="13"/>
+    </row>
+    <row r="72" spans="2:22">
       <c r="B72" s="5" t="s">
         <v>8</v>
       </c>
@@ -7029,8 +7669,10 @@
       <c r="R72" s="13"/>
       <c r="S72" s="13"/>
       <c r="T72" s="13"/>
-    </row>
-    <row r="73" spans="2:20">
+      <c r="U72" s="13"/>
+      <c r="V72" s="13"/>
+    </row>
+    <row r="73" spans="2:22">
       <c r="B73" s="5" t="s">
         <v>8</v>
       </c>
@@ -7054,8 +7696,10 @@
       <c r="R73" s="13"/>
       <c r="S73" s="13"/>
       <c r="T73" s="13"/>
-    </row>
-    <row r="74" spans="2:20">
+      <c r="U73" s="13"/>
+      <c r="V73" s="13"/>
+    </row>
+    <row r="74" spans="2:22">
       <c r="B74" s="6"/>
       <c r="C74" s="3"/>
       <c r="D74" s="20"/>
@@ -7075,8 +7719,10 @@
       <c r="R74" s="13"/>
       <c r="S74" s="13"/>
       <c r="T74" s="13"/>
-    </row>
-    <row r="75" spans="2:20">
+      <c r="U74" s="13"/>
+      <c r="V74" s="13"/>
+    </row>
+    <row r="75" spans="2:22">
       <c r="B75" s="6" t="s">
         <v>13</v>
       </c>
@@ -7132,8 +7778,14 @@
       <c r="T75" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="76" spans="2:20">
+      <c r="U75" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V75" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22">
       <c r="B76" s="6" t="s">
         <v>14</v>
       </c>
@@ -7173,8 +7825,10 @@
       <c r="R76" s="13"/>
       <c r="S76" s="13"/>
       <c r="T76" s="13"/>
-    </row>
-    <row r="77" spans="2:20">
+      <c r="U76" s="13"/>
+      <c r="V76" s="13"/>
+    </row>
+    <row r="77" spans="2:22">
       <c r="B77" s="6" t="s">
         <v>15</v>
       </c>
@@ -7214,8 +7868,10 @@
       <c r="R77" s="13"/>
       <c r="S77" s="13"/>
       <c r="T77" s="13"/>
-    </row>
-    <row r="78" spans="2:20">
+      <c r="U77" s="13"/>
+      <c r="V77" s="13"/>
+    </row>
+    <row r="78" spans="2:22">
       <c r="B78" s="6" t="s">
         <v>16</v>
       </c>
@@ -7253,8 +7909,10 @@
       <c r="R78" s="13"/>
       <c r="S78" s="13"/>
       <c r="T78" s="13"/>
-    </row>
-    <row r="79" spans="2:20">
+      <c r="U78" s="13"/>
+      <c r="V78" s="13"/>
+    </row>
+    <row r="79" spans="2:22">
       <c r="B79" s="6" t="s">
         <v>17</v>
       </c>
@@ -7302,14 +7960,18 @@
         <v>140</v>
       </c>
       <c r="R79" s="13"/>
-      <c r="S79" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="S79" s="13"/>
       <c r="T79" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="80" spans="2:20">
+      <c r="U79" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V79" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="2:22">
       <c r="B80" s="6" t="s">
         <v>18</v>
       </c>
@@ -7338,9 +8000,15 @@
       <c r="S80" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T80" s="13"/>
-    </row>
-    <row r="81" spans="2:20">
+      <c r="T80" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U80" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V80" s="13"/>
+    </row>
+    <row r="81" spans="2:22">
       <c r="B81" s="6" t="s">
         <v>19</v>
       </c>
@@ -7378,8 +8046,10 @@
       <c r="R81" s="13"/>
       <c r="S81" s="13"/>
       <c r="T81" s="13"/>
-    </row>
-    <row r="82" spans="2:20">
+      <c r="U81" s="13"/>
+      <c r="V81" s="13"/>
+    </row>
+    <row r="82" spans="2:22">
       <c r="B82" s="5" t="s">
         <v>8</v>
       </c>
@@ -7403,8 +8073,10 @@
       <c r="R82" s="13"/>
       <c r="S82" s="13"/>
       <c r="T82" s="13"/>
-    </row>
-    <row r="83" spans="2:20">
+      <c r="U82" s="13"/>
+      <c r="V82" s="13"/>
+    </row>
+    <row r="83" spans="2:22">
       <c r="B83" s="6" t="s">
         <v>20</v>
       </c>
@@ -7460,8 +8132,14 @@
       <c r="T83" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="84" spans="2:20">
+      <c r="U83" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V83" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="84" spans="2:22">
       <c r="B84" s="6" t="s">
         <v>21</v>
       </c>
@@ -7517,8 +8195,14 @@
       <c r="T84" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="85" spans="2:20">
+      <c r="U84" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V84" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="85" spans="2:22">
       <c r="B85" s="6" t="s">
         <v>22</v>
       </c>
@@ -7574,8 +8258,14 @@
       <c r="T85" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="86" spans="2:20">
+      <c r="U85" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V85" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" spans="2:22">
       <c r="B86" s="6" t="s">
         <v>23</v>
       </c>
@@ -7624,11 +8314,13 @@
       </c>
       <c r="R86" s="13"/>
       <c r="S86" s="13"/>
-      <c r="T86" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="87" spans="2:20">
+      <c r="T86" s="13"/>
+      <c r="U86" s="13"/>
+      <c r="V86" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="87" spans="2:22">
       <c r="B87" s="6" t="s">
         <v>24</v>
       </c>
@@ -7676,14 +8368,18 @@
         <v>140</v>
       </c>
       <c r="R87" s="13"/>
-      <c r="S87" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="S87" s="13"/>
       <c r="T87" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="88" spans="2:20">
+      <c r="U87" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V87" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="88" spans="2:22">
       <c r="B88" s="6" t="s">
         <v>25</v>
       </c>
@@ -7732,11 +8428,13 @@
       </c>
       <c r="R88" s="13"/>
       <c r="S88" s="13"/>
-      <c r="T88" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="89" spans="2:20">
+      <c r="T88" s="13"/>
+      <c r="U88" s="13"/>
+      <c r="V88" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="89" spans="2:22">
       <c r="B89" s="6" t="s">
         <v>26</v>
       </c>
@@ -7772,8 +8470,10 @@
       <c r="R89" s="13"/>
       <c r="S89" s="13"/>
       <c r="T89" s="13"/>
-    </row>
-    <row r="90" spans="2:20">
+      <c r="U89" s="13"/>
+      <c r="V89" s="13"/>
+    </row>
+    <row r="90" spans="2:22">
       <c r="B90" s="5" t="s">
         <v>8</v>
       </c>
@@ -7797,8 +8497,10 @@
       <c r="R90" s="13"/>
       <c r="S90" s="13"/>
       <c r="T90" s="13"/>
-    </row>
-    <row r="91" spans="2:20">
+      <c r="U90" s="13"/>
+      <c r="V90" s="13"/>
+    </row>
+    <row r="91" spans="2:22">
       <c r="B91" s="6"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
@@ -7818,8 +8520,10 @@
       <c r="R91" s="13"/>
       <c r="S91" s="13"/>
       <c r="T91" s="13"/>
-    </row>
-    <row r="92" spans="2:20">
+      <c r="U91" s="13"/>
+      <c r="V91" s="13"/>
+    </row>
+    <row r="92" spans="2:22">
       <c r="B92" s="6" t="s">
         <v>27</v>
       </c>
@@ -7857,8 +8561,10 @@
       <c r="R92" s="13"/>
       <c r="S92" s="13"/>
       <c r="T92" s="13"/>
-    </row>
-    <row r="93" spans="2:20">
+      <c r="U92" s="13"/>
+      <c r="V92" s="13"/>
+    </row>
+    <row r="93" spans="2:22">
       <c r="B93" s="5" t="s">
         <v>8</v>
       </c>
@@ -7884,8 +8590,10 @@
       <c r="R93" s="13"/>
       <c r="S93" s="13"/>
       <c r="T93" s="13"/>
-    </row>
-    <row r="94" spans="2:20">
+      <c r="U93" s="13"/>
+      <c r="V93" s="13"/>
+    </row>
+    <row r="94" spans="2:22">
       <c r="B94" s="6" t="s">
         <v>28</v>
       </c>
@@ -7932,9 +8640,15 @@
       <c r="S94" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T94" s="13"/>
-    </row>
-    <row r="95" spans="2:20">
+      <c r="T94" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U94" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V94" s="13"/>
+    </row>
+    <row r="95" spans="2:22">
       <c r="B95" s="6" t="s">
         <v>29</v>
       </c>
@@ -7981,9 +8695,15 @@
       <c r="S95" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T95" s="13"/>
-    </row>
-    <row r="96" spans="2:20">
+      <c r="T95" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U95" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V95" s="13"/>
+    </row>
+    <row r="96" spans="2:22">
       <c r="B96" s="6" t="s">
         <v>30</v>
       </c>
@@ -8012,9 +8732,15 @@
       <c r="S96" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T96" s="13"/>
-    </row>
-    <row r="97" spans="2:20">
+      <c r="T96" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U96" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V96" s="13"/>
+    </row>
+    <row r="97" spans="2:22">
       <c r="B97" s="5" t="s">
         <v>8</v>
       </c>
@@ -8038,8 +8764,10 @@
       <c r="R97" s="13"/>
       <c r="S97" s="13"/>
       <c r="T97" s="13"/>
-    </row>
-    <row r="98" spans="2:20">
+      <c r="U97" s="13"/>
+      <c r="V97" s="13"/>
+    </row>
+    <row r="98" spans="2:22">
       <c r="B98" s="5" t="s">
         <v>8</v>
       </c>
@@ -8063,8 +8791,10 @@
       <c r="R98" s="13"/>
       <c r="S98" s="13"/>
       <c r="T98" s="13"/>
-    </row>
-    <row r="99" spans="2:20">
+      <c r="U98" s="13"/>
+      <c r="V98" s="13"/>
+    </row>
+    <row r="99" spans="2:22">
       <c r="B99" s="5" t="s">
         <v>8</v>
       </c>
@@ -8088,8 +8818,10 @@
       <c r="R99" s="13"/>
       <c r="S99" s="13"/>
       <c r="T99" s="13"/>
-    </row>
-    <row r="100" spans="2:20">
+      <c r="U99" s="13"/>
+      <c r="V99" s="13"/>
+    </row>
+    <row r="100" spans="2:22">
       <c r="B100" s="5" t="s">
         <v>8</v>
       </c>
@@ -8113,8 +8845,10 @@
       <c r="R100" s="13"/>
       <c r="S100" s="13"/>
       <c r="T100" s="13"/>
-    </row>
-    <row r="101" spans="2:20">
+      <c r="U100" s="13"/>
+      <c r="V100" s="13"/>
+    </row>
+    <row r="101" spans="2:22">
       <c r="B101" s="4" t="s">
         <v>31</v>
       </c>
@@ -8152,8 +8886,10 @@
       <c r="R101" s="13"/>
       <c r="S101" s="13"/>
       <c r="T101" s="13"/>
-    </row>
-    <row r="102" spans="2:20">
+      <c r="U101" s="13"/>
+      <c r="V101" s="13"/>
+    </row>
+    <row r="102" spans="2:22">
       <c r="B102" s="8" t="s">
         <v>32</v>
       </c>
@@ -8209,8 +8945,14 @@
       <c r="T102" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="103" spans="2:20">
+      <c r="U102" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V102" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="103" spans="2:22">
       <c r="B103" s="4" t="s">
         <v>33</v>
       </c>
@@ -8266,8 +9008,14 @@
       <c r="T103" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="104" spans="2:20">
+      <c r="U103" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V103" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="104" spans="2:22">
       <c r="B104" s="4" t="s">
         <v>34</v>
       </c>
@@ -8305,8 +9053,10 @@
       <c r="R104" s="13"/>
       <c r="S104" s="13"/>
       <c r="T104" s="13"/>
-    </row>
-    <row r="105" spans="2:20">
+      <c r="U104" s="13"/>
+      <c r="V104" s="13"/>
+    </row>
+    <row r="105" spans="2:22">
       <c r="B105" s="4" t="s">
         <v>35</v>
       </c>
@@ -8362,8 +9112,14 @@
       <c r="T105" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="106" spans="2:20">
+      <c r="U105" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V105" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="106" spans="2:22">
       <c r="B106" s="4" t="s">
         <v>36</v>
       </c>
@@ -8419,8 +9175,14 @@
       <c r="T106" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="107" spans="2:20">
+      <c r="U106" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V106" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="107" spans="2:22">
       <c r="B107" s="4" t="s">
         <v>37</v>
       </c>
@@ -8444,8 +9206,10 @@
       <c r="R107" s="13"/>
       <c r="S107" s="13"/>
       <c r="T107" s="13"/>
-    </row>
-    <row r="108" spans="2:20">
+      <c r="U107" s="13"/>
+      <c r="V107" s="13"/>
+    </row>
+    <row r="108" spans="2:22">
       <c r="B108" s="4"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -8465,8 +9229,10 @@
       <c r="R108" s="13"/>
       <c r="S108" s="13"/>
       <c r="T108" s="13"/>
-    </row>
-    <row r="109" spans="2:20">
+      <c r="U108" s="13"/>
+      <c r="V108" s="13"/>
+    </row>
+    <row r="109" spans="2:22">
       <c r="B109" s="4" t="s">
         <v>38</v>
       </c>
@@ -8522,8 +9288,14 @@
       <c r="T109" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="110" spans="2:20">
+      <c r="U109" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V109" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="2:22">
       <c r="B110" s="4" t="s">
         <v>39</v>
       </c>
@@ -8571,14 +9343,18 @@
         <v>140</v>
       </c>
       <c r="R110" s="13"/>
-      <c r="S110" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="S110" s="13"/>
       <c r="T110" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="111" spans="2:20">
+      <c r="U110" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V110" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="111" spans="2:22">
       <c r="B111" s="4" t="s">
         <v>40</v>
       </c>
@@ -8628,8 +9404,10 @@
       <c r="R111" s="13"/>
       <c r="S111" s="13"/>
       <c r="T111" s="13"/>
-    </row>
-    <row r="112" spans="2:20">
+      <c r="U111" s="13"/>
+      <c r="V111" s="13"/>
+    </row>
+    <row r="112" spans="2:22">
       <c r="B112" s="4" t="s">
         <v>41</v>
       </c>
@@ -8677,12 +9455,16 @@
         <v>141</v>
       </c>
       <c r="R112" s="13"/>
-      <c r="S112" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="T112" s="13"/>
-    </row>
-    <row r="113" spans="2:20">
+      <c r="S112" s="13"/>
+      <c r="T112" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U112" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V112" s="13"/>
+    </row>
+    <row r="113" spans="2:22">
       <c r="B113" s="4"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
@@ -8702,8 +9484,10 @@
       <c r="R113" s="13"/>
       <c r="S113" s="13"/>
       <c r="T113" s="13"/>
-    </row>
-    <row r="114" spans="2:20">
+      <c r="U113" s="13"/>
+      <c r="V113" s="13"/>
+    </row>
+    <row r="114" spans="2:22">
       <c r="B114" s="4" t="s">
         <v>42</v>
       </c>
@@ -8743,8 +9527,10 @@
       <c r="R114" s="13"/>
       <c r="S114" s="13"/>
       <c r="T114" s="13"/>
-    </row>
-    <row r="115" spans="2:20">
+      <c r="U114" s="13"/>
+      <c r="V114" s="13"/>
+    </row>
+    <row r="115" spans="2:22">
       <c r="B115" s="5" t="s">
         <v>8</v>
       </c>
@@ -8768,8 +9554,10 @@
       <c r="R115" s="13"/>
       <c r="S115" s="13"/>
       <c r="T115" s="13"/>
-    </row>
-    <row r="116" spans="2:20">
+      <c r="U115" s="13"/>
+      <c r="V115" s="13"/>
+    </row>
+    <row r="116" spans="2:22">
       <c r="B116" s="4" t="s">
         <v>43</v>
       </c>
@@ -8798,9 +9586,15 @@
       <c r="S116" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T116" s="13"/>
-    </row>
-    <row r="117" spans="2:20">
+      <c r="T116" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U116" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V116" s="13"/>
+    </row>
+    <row r="117" spans="2:22">
       <c r="B117" s="4" t="s">
         <v>44</v>
       </c>
@@ -8826,8 +9620,10 @@
       <c r="R117" s="13"/>
       <c r="S117" s="13"/>
       <c r="T117" s="13"/>
-    </row>
-    <row r="118" spans="2:20">
+      <c r="U117" s="13"/>
+      <c r="V117" s="13"/>
+    </row>
+    <row r="118" spans="2:22">
       <c r="B118" s="4"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
@@ -8847,8 +9643,10 @@
       <c r="R118" s="13"/>
       <c r="S118" s="13"/>
       <c r="T118" s="13"/>
-    </row>
-    <row r="119" spans="2:20">
+      <c r="U118" s="13"/>
+      <c r="V118" s="13"/>
+    </row>
+    <row r="119" spans="2:22">
       <c r="B119" s="4" t="s">
         <v>45</v>
       </c>
@@ -8904,8 +9702,14 @@
       <c r="T119" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="120" spans="2:20">
+      <c r="U119" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V119" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="2:22">
       <c r="B120" s="4" t="s">
         <v>46</v>
       </c>
@@ -8952,9 +9756,15 @@
       <c r="S120" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T120" s="13"/>
-    </row>
-    <row r="121" spans="2:20">
+      <c r="T120" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U120" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V120" s="13"/>
+    </row>
+    <row r="121" spans="2:22">
       <c r="B121" s="4" t="s">
         <v>47</v>
       </c>
@@ -9001,9 +9811,15 @@
       <c r="S121" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T121" s="13"/>
-    </row>
-    <row r="122" spans="2:20">
+      <c r="T121" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U121" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V121" s="13"/>
+    </row>
+    <row r="122" spans="2:22">
       <c r="B122" s="4" t="s">
         <v>48</v>
       </c>
@@ -9043,8 +9859,10 @@
       <c r="R122" s="13"/>
       <c r="S122" s="13"/>
       <c r="T122" s="13"/>
-    </row>
-    <row r="123" spans="2:20">
+      <c r="U122" s="13"/>
+      <c r="V122" s="13"/>
+    </row>
+    <row r="123" spans="2:22">
       <c r="B123" s="4"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
@@ -9064,8 +9882,10 @@
       <c r="R123" s="13"/>
       <c r="S123" s="13"/>
       <c r="T123" s="13"/>
-    </row>
-    <row r="124" spans="2:20">
+      <c r="U123" s="13"/>
+      <c r="V123" s="13"/>
+    </row>
+    <row r="124" spans="2:22">
       <c r="B124" s="4" t="s">
         <v>49</v>
       </c>
@@ -9089,8 +9909,10 @@
       <c r="R124" s="13"/>
       <c r="S124" s="13"/>
       <c r="T124" s="13"/>
-    </row>
-    <row r="125" spans="2:20">
+      <c r="U124" s="13"/>
+      <c r="V124" s="13"/>
+    </row>
+    <row r="125" spans="2:22">
       <c r="B125" s="4" t="s">
         <v>50</v>
       </c>
@@ -9116,8 +9938,10 @@
       <c r="R125" s="13"/>
       <c r="S125" s="13"/>
       <c r="T125" s="13"/>
-    </row>
-    <row r="126" spans="2:20">
+      <c r="U125" s="13"/>
+      <c r="V125" s="13"/>
+    </row>
+    <row r="126" spans="2:22">
       <c r="B126" s="4" t="s">
         <v>51</v>
       </c>
@@ -9175,8 +9999,14 @@
       <c r="T126" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="127" spans="2:20">
+      <c r="U126" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V126" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="127" spans="2:22">
       <c r="B127" s="5" t="s">
         <v>8</v>
       </c>
@@ -9200,8 +10030,10 @@
       <c r="R127" s="13"/>
       <c r="S127" s="13"/>
       <c r="T127" s="13"/>
-    </row>
-    <row r="128" spans="2:20">
+      <c r="U127" s="13"/>
+      <c r="V127" s="13"/>
+    </row>
+    <row r="128" spans="2:22">
       <c r="B128" s="4"/>
       <c r="C128" s="3"/>
       <c r="D128" s="19"/>
@@ -9221,8 +10053,10 @@
       <c r="R128" s="13"/>
       <c r="S128" s="13"/>
       <c r="T128" s="13"/>
-    </row>
-    <row r="129" spans="2:20">
+      <c r="U128" s="13"/>
+      <c r="V128" s="13"/>
+    </row>
+    <row r="129" spans="2:22">
       <c r="B129" s="4" t="s">
         <v>52</v>
       </c>
@@ -9278,8 +10112,14 @@
       <c r="T129" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="130" spans="2:20">
+      <c r="U129" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V129" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="130" spans="2:22">
       <c r="B130" s="4" t="s">
         <v>53</v>
       </c>
@@ -9327,14 +10167,18 @@
         <v>140</v>
       </c>
       <c r="R130" s="13"/>
-      <c r="S130" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="S130" s="13"/>
       <c r="T130" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="131" spans="2:20">
+      <c r="U130" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V130" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="131" spans="2:22">
       <c r="B131" s="4" t="s">
         <v>54</v>
       </c>
@@ -9390,8 +10234,14 @@
       <c r="T131" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="132" spans="2:20">
+      <c r="U131" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V131" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="132" spans="2:22">
       <c r="B132" s="4" t="s">
         <v>55</v>
       </c>
@@ -9418,9 +10268,15 @@
       <c r="S132" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T132" s="13"/>
-    </row>
-    <row r="133" spans="2:20">
+      <c r="T132" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U132" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V132" s="13"/>
+    </row>
+    <row r="133" spans="2:22">
       <c r="B133" s="4"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
@@ -9440,8 +10296,10 @@
       <c r="R133" s="13"/>
       <c r="S133" s="13"/>
       <c r="T133" s="13"/>
-    </row>
-    <row r="134" spans="2:20">
+      <c r="U133" s="13"/>
+      <c r="V133" s="13"/>
+    </row>
+    <row r="134" spans="2:22">
       <c r="B134" s="4" t="s">
         <v>56</v>
       </c>
@@ -9481,8 +10339,10 @@
       <c r="R134" s="13"/>
       <c r="S134" s="13"/>
       <c r="T134" s="13"/>
-    </row>
-    <row r="135" spans="2:20">
+      <c r="U134" s="13"/>
+      <c r="V134" s="13"/>
+    </row>
+    <row r="135" spans="2:22">
       <c r="B135" s="4" t="s">
         <v>57</v>
       </c>
@@ -9522,8 +10382,10 @@
       <c r="R135" s="13"/>
       <c r="S135" s="13"/>
       <c r="T135" s="13"/>
-    </row>
-    <row r="136" spans="2:20">
+      <c r="U135" s="13"/>
+      <c r="V135" s="13"/>
+    </row>
+    <row r="136" spans="2:22">
       <c r="B136" s="4" t="s">
         <v>58</v>
       </c>
@@ -9563,8 +10425,10 @@
       <c r="R136" s="13"/>
       <c r="S136" s="13"/>
       <c r="T136" s="13"/>
-    </row>
-    <row r="137" spans="2:20">
+      <c r="U136" s="13"/>
+      <c r="V136" s="13"/>
+    </row>
+    <row r="137" spans="2:22">
       <c r="B137" s="4" t="s">
         <v>59</v>
       </c>
@@ -9622,8 +10486,14 @@
       <c r="T137" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="138" spans="2:20">
+      <c r="U137" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V137" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="138" spans="2:22">
       <c r="B138" s="4"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
@@ -9643,8 +10513,10 @@
       <c r="R138" s="13"/>
       <c r="S138" s="13"/>
       <c r="T138" s="13"/>
-    </row>
-    <row r="139" spans="2:20">
+      <c r="U138" s="13"/>
+      <c r="V138" s="13"/>
+    </row>
+    <row r="139" spans="2:22">
       <c r="B139" s="4" t="s">
         <v>60</v>
       </c>
@@ -9700,8 +10572,14 @@
       <c r="T139" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="140" spans="2:20">
+      <c r="U139" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V139" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="140" spans="2:22">
       <c r="B140" s="4"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
@@ -9721,8 +10599,10 @@
       <c r="R140" s="13"/>
       <c r="S140" s="13"/>
       <c r="T140" s="13"/>
-    </row>
-    <row r="141" spans="2:20">
+      <c r="U140" s="13"/>
+      <c r="V140" s="13"/>
+    </row>
+    <row r="141" spans="2:22">
       <c r="B141" s="4" t="s">
         <v>61</v>
       </c>
@@ -9750,8 +10630,10 @@
       <c r="R141" s="14"/>
       <c r="S141" s="14"/>
       <c r="T141" s="14"/>
-    </row>
-    <row r="142" spans="2:20">
+      <c r="U141" s="14"/>
+      <c r="V141" s="14"/>
+    </row>
+    <row r="142" spans="2:22">
       <c r="B142" s="4"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
@@ -9771,8 +10653,10 @@
       <c r="R142" s="13"/>
       <c r="S142" s="13"/>
       <c r="T142" s="13"/>
-    </row>
-    <row r="143" spans="2:20">
+      <c r="U142" s="13"/>
+      <c r="V142" s="13"/>
+    </row>
+    <row r="143" spans="2:22">
       <c r="B143" s="4" t="s">
         <v>62</v>
       </c>
@@ -9828,8 +10712,14 @@
       <c r="T143" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="144" spans="2:20">
+      <c r="U143" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V143" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="144" spans="2:22">
       <c r="B144" s="4" t="s">
         <v>63</v>
       </c>
@@ -9885,8 +10775,14 @@
       <c r="T144" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="145" spans="2:20">
+      <c r="U144" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V144" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="2:22">
       <c r="B145" s="4" t="s">
         <v>64</v>
       </c>
@@ -9942,8 +10838,14 @@
       <c r="T145" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="146" spans="2:20">
+      <c r="U145" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V145" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="146" spans="2:22">
       <c r="B146" s="4" t="s">
         <v>65</v>
       </c>
@@ -9999,8 +10901,14 @@
       <c r="T146" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="147" spans="2:20">
+      <c r="U146" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V146" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="147" spans="2:22">
       <c r="B147" s="4" t="s">
         <v>66</v>
       </c>
@@ -10056,8 +10964,14 @@
       <c r="T147" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="148" spans="2:20">
+      <c r="U147" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V147" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="148" spans="2:22">
       <c r="B148" s="4" t="s">
         <v>67</v>
       </c>
@@ -10109,8 +11023,14 @@
       <c r="T148" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="149" spans="2:20">
+      <c r="U148" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V148" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="149" spans="2:22">
       <c r="B149" s="4" t="s">
         <v>68</v>
       </c>
@@ -10168,8 +11088,14 @@
       <c r="T149" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="150" spans="2:20">
+      <c r="U149" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V149" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="150" spans="2:22">
       <c r="B150" s="4" t="s">
         <v>69</v>
       </c>
@@ -10197,8 +11123,10 @@
       <c r="R150" s="13"/>
       <c r="S150" s="13"/>
       <c r="T150" s="13"/>
-    </row>
-    <row r="151" spans="2:20">
+      <c r="U150" s="13"/>
+      <c r="V150" s="13"/>
+    </row>
+    <row r="151" spans="2:22">
       <c r="B151" s="4" t="s">
         <v>70</v>
       </c>
@@ -10226,8 +11154,10 @@
       <c r="R151" s="13"/>
       <c r="S151" s="13"/>
       <c r="T151" s="13"/>
-    </row>
-    <row r="152" spans="2:20">
+      <c r="U151" s="13"/>
+      <c r="V151" s="13"/>
+    </row>
+    <row r="152" spans="2:22">
       <c r="B152" s="5" t="s">
         <v>8</v>
       </c>
@@ -10251,8 +11181,10 @@
       <c r="R152" s="13"/>
       <c r="S152" s="13"/>
       <c r="T152" s="13"/>
-    </row>
-    <row r="153" spans="2:20">
+      <c r="U152" s="13"/>
+      <c r="V152" s="13"/>
+    </row>
+    <row r="153" spans="2:22">
       <c r="B153" s="4" t="s">
         <v>71</v>
       </c>
@@ -10308,8 +11240,14 @@
       <c r="T153" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="154" spans="2:20">
+      <c r="U153" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V153" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="154" spans="2:22">
       <c r="B154" s="4" t="s">
         <v>71</v>
       </c>
@@ -10365,8 +11303,14 @@
       <c r="T154" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="155" spans="2:20">
+      <c r="U154" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V154" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="155" spans="2:22">
       <c r="B155" s="4" t="s">
         <v>72</v>
       </c>
@@ -10424,8 +11368,14 @@
       <c r="T155" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="156" spans="2:20">
+      <c r="U155" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V155" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="156" spans="2:22">
       <c r="B156" s="4" t="s">
         <v>72</v>
       </c>
@@ -10483,8 +11433,14 @@
       <c r="T156" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="157" spans="2:20">
+      <c r="U156" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V156" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="157" spans="2:22">
       <c r="B157" s="5" t="s">
         <v>8</v>
       </c>
@@ -10508,8 +11464,10 @@
       <c r="R157" s="13"/>
       <c r="S157" s="13"/>
       <c r="T157" s="13"/>
-    </row>
-    <row r="158" spans="2:20">
+      <c r="U157" s="13"/>
+      <c r="V157" s="13"/>
+    </row>
+    <row r="158" spans="2:22">
       <c r="B158" s="5" t="s">
         <v>8</v>
       </c>
@@ -10533,8 +11491,10 @@
       <c r="R158" s="13"/>
       <c r="S158" s="13"/>
       <c r="T158" s="13"/>
-    </row>
-    <row r="159" spans="2:20">
+      <c r="U158" s="13"/>
+      <c r="V158" s="13"/>
+    </row>
+    <row r="159" spans="2:22">
       <c r="B159" s="4"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
@@ -10554,8 +11514,10 @@
       <c r="R159" s="13"/>
       <c r="S159" s="13"/>
       <c r="T159" s="13"/>
-    </row>
-    <row r="160" spans="2:20">
+      <c r="U159" s="13"/>
+      <c r="V159" s="13"/>
+    </row>
+    <row r="160" spans="2:22">
       <c r="B160" s="4" t="s">
         <v>73</v>
       </c>
@@ -10585,8 +11547,10 @@
       <c r="R160" s="13"/>
       <c r="S160" s="13"/>
       <c r="T160" s="13"/>
-    </row>
-    <row r="161" spans="2:20">
+      <c r="U160" s="13"/>
+      <c r="V160" s="13"/>
+    </row>
+    <row r="161" spans="2:22">
       <c r="B161" s="4" t="s">
         <v>73</v>
       </c>
@@ -10616,8 +11580,10 @@
       <c r="R161" s="13"/>
       <c r="S161" s="13"/>
       <c r="T161" s="13"/>
-    </row>
-    <row r="162" spans="2:20">
+      <c r="U161" s="13"/>
+      <c r="V161" s="13"/>
+    </row>
+    <row r="162" spans="2:22">
       <c r="B162" s="4" t="s">
         <v>74</v>
       </c>
@@ -10657,8 +11623,10 @@
       <c r="R162" s="13"/>
       <c r="S162" s="13"/>
       <c r="T162" s="13"/>
-    </row>
-    <row r="163" spans="2:20">
+      <c r="U162" s="13"/>
+      <c r="V162" s="13"/>
+    </row>
+    <row r="163" spans="2:22">
       <c r="B163" s="4" t="s">
         <v>74</v>
       </c>
@@ -10698,8 +11666,10 @@
       <c r="R163" s="13"/>
       <c r="S163" s="13"/>
       <c r="T163" s="13"/>
-    </row>
-    <row r="164" spans="2:20">
+      <c r="U163" s="13"/>
+      <c r="V163" s="13"/>
+    </row>
+    <row r="164" spans="2:22">
       <c r="B164" s="4" t="s">
         <v>75</v>
       </c>
@@ -10746,9 +11716,15 @@
       <c r="S164" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T164" s="13"/>
-    </row>
-    <row r="165" spans="2:20">
+      <c r="T164" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U164" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V164" s="13"/>
+    </row>
+    <row r="165" spans="2:22">
       <c r="B165" s="4" t="s">
         <v>75</v>
       </c>
@@ -10795,9 +11771,15 @@
       <c r="S165" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T165" s="13"/>
-    </row>
-    <row r="166" spans="2:20">
+      <c r="T165" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U165" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V165" s="13"/>
+    </row>
+    <row r="166" spans="2:22">
       <c r="B166" s="4" t="s">
         <v>76</v>
       </c>
@@ -10855,8 +11837,14 @@
       <c r="T166" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="167" spans="2:20">
+      <c r="U166" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V166" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="167" spans="2:22">
       <c r="B167" s="4" t="s">
         <v>76</v>
       </c>
@@ -10914,8 +11902,14 @@
       <c r="T167" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="168" spans="2:20">
+      <c r="U167" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V167" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="168" spans="2:22">
       <c r="B168" s="4" t="s">
         <v>77</v>
       </c>
@@ -10955,8 +11949,10 @@
       <c r="R168" s="13"/>
       <c r="S168" s="13"/>
       <c r="T168" s="13"/>
-    </row>
-    <row r="169" spans="2:20">
+      <c r="U168" s="13"/>
+      <c r="V168" s="13"/>
+    </row>
+    <row r="169" spans="2:22">
       <c r="B169" s="4" t="s">
         <v>77</v>
       </c>
@@ -10996,8 +11992,10 @@
       <c r="R169" s="13"/>
       <c r="S169" s="13"/>
       <c r="T169" s="13"/>
-    </row>
-    <row r="170" spans="2:20">
+      <c r="U169" s="13"/>
+      <c r="V169" s="13"/>
+    </row>
+    <row r="170" spans="2:22">
       <c r="B170" s="5" t="s">
         <v>8</v>
       </c>
@@ -11021,8 +12019,10 @@
       <c r="R170" s="13"/>
       <c r="S170" s="13"/>
       <c r="T170" s="13"/>
-    </row>
-    <row r="171" spans="2:20">
+      <c r="U170" s="13"/>
+      <c r="V170" s="13"/>
+    </row>
+    <row r="171" spans="2:22">
       <c r="B171" s="5" t="s">
         <v>8</v>
       </c>
@@ -11046,8 +12046,10 @@
       <c r="R171" s="13"/>
       <c r="S171" s="13"/>
       <c r="T171" s="13"/>
-    </row>
-    <row r="172" spans="2:20">
+      <c r="U171" s="13"/>
+      <c r="V171" s="13"/>
+    </row>
+    <row r="172" spans="2:22">
       <c r="B172" s="5" t="s">
         <v>8</v>
       </c>
@@ -11071,8 +12073,10 @@
       <c r="R172" s="13"/>
       <c r="S172" s="13"/>
       <c r="T172" s="13"/>
-    </row>
-    <row r="173" spans="2:20">
+      <c r="U172" s="13"/>
+      <c r="V172" s="13"/>
+    </row>
+    <row r="173" spans="2:22">
       <c r="B173" s="5" t="s">
         <v>8</v>
       </c>
@@ -11096,8 +12100,10 @@
       <c r="R173" s="13"/>
       <c r="S173" s="13"/>
       <c r="T173" s="13"/>
-    </row>
-    <row r="174" spans="2:20">
+      <c r="U173" s="13"/>
+      <c r="V173" s="13"/>
+    </row>
+    <row r="174" spans="2:22">
       <c r="B174" s="5" t="s">
         <v>8</v>
       </c>
@@ -11121,8 +12127,10 @@
       <c r="R174" s="13"/>
       <c r="S174" s="13"/>
       <c r="T174" s="13"/>
-    </row>
-    <row r="175" spans="2:20">
+      <c r="U174" s="13"/>
+      <c r="V174" s="13"/>
+    </row>
+    <row r="175" spans="2:22">
       <c r="B175" s="5" t="s">
         <v>8</v>
       </c>
@@ -11146,8 +12154,10 @@
       <c r="R175" s="13"/>
       <c r="S175" s="13"/>
       <c r="T175" s="13"/>
-    </row>
-    <row r="176" spans="2:20">
+      <c r="U175" s="13"/>
+      <c r="V175" s="13"/>
+    </row>
+    <row r="176" spans="2:22">
       <c r="B176" s="4"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
@@ -11167,8 +12177,10 @@
       <c r="R176" s="13"/>
       <c r="S176" s="13"/>
       <c r="T176" s="13"/>
-    </row>
-    <row r="177" spans="2:20">
+      <c r="U176" s="13"/>
+      <c r="V176" s="13"/>
+    </row>
+    <row r="177" spans="2:22">
       <c r="B177" s="4" t="s">
         <v>78</v>
       </c>
@@ -11208,8 +12220,10 @@
       <c r="R177" s="13"/>
       <c r="S177" s="13"/>
       <c r="T177" s="13"/>
-    </row>
-    <row r="178" spans="2:20">
+      <c r="U177" s="13"/>
+      <c r="V177" s="13"/>
+    </row>
+    <row r="178" spans="2:22">
       <c r="B178" s="4" t="s">
         <v>79</v>
       </c>
@@ -11249,8 +12263,10 @@
       <c r="R178" s="13"/>
       <c r="S178" s="13"/>
       <c r="T178" s="13"/>
-    </row>
-    <row r="179" spans="2:20">
+      <c r="U178" s="13"/>
+      <c r="V178" s="13"/>
+    </row>
+    <row r="179" spans="2:22">
       <c r="B179" s="4" t="s">
         <v>80</v>
       </c>
@@ -11290,8 +12306,10 @@
       <c r="R179" s="13"/>
       <c r="S179" s="13"/>
       <c r="T179" s="13"/>
-    </row>
-    <row r="180" spans="2:20">
+      <c r="U179" s="13"/>
+      <c r="V179" s="13"/>
+    </row>
+    <row r="180" spans="2:22">
       <c r="B180" s="4" t="s">
         <v>81</v>
       </c>
@@ -11331,8 +12349,10 @@
       <c r="R180" s="13"/>
       <c r="S180" s="13"/>
       <c r="T180" s="13"/>
-    </row>
-    <row r="181" spans="2:20">
+      <c r="U180" s="13"/>
+      <c r="V180" s="13"/>
+    </row>
+    <row r="181" spans="2:22">
       <c r="B181" s="5" t="s">
         <v>8</v>
       </c>
@@ -11356,8 +12376,10 @@
       <c r="R181" s="13"/>
       <c r="S181" s="13"/>
       <c r="T181" s="13"/>
-    </row>
-    <row r="182" spans="2:20">
+      <c r="U181" s="13"/>
+      <c r="V181" s="13"/>
+    </row>
+    <row r="182" spans="2:22">
       <c r="B182" s="5" t="s">
         <v>8</v>
       </c>
@@ -11381,8 +12403,10 @@
       <c r="R182" s="13"/>
       <c r="S182" s="13"/>
       <c r="T182" s="13"/>
-    </row>
-    <row r="183" spans="2:20">
+      <c r="U182" s="13"/>
+      <c r="V182" s="13"/>
+    </row>
+    <row r="183" spans="2:22">
       <c r="B183" s="4" t="s">
         <v>82</v>
       </c>
@@ -11412,8 +12436,10 @@
       <c r="R183" s="13"/>
       <c r="S183" s="13"/>
       <c r="T183" s="13"/>
-    </row>
-    <row r="184" spans="2:20">
+      <c r="U183" s="13"/>
+      <c r="V183" s="13"/>
+    </row>
+    <row r="184" spans="2:22">
       <c r="B184" s="4" t="s">
         <v>83</v>
       </c>
@@ -11443,8 +12469,10 @@
       <c r="R184" s="13"/>
       <c r="S184" s="13"/>
       <c r="T184" s="13"/>
-    </row>
-    <row r="185" spans="2:20">
+      <c r="U184" s="13"/>
+      <c r="V184" s="13"/>
+    </row>
+    <row r="185" spans="2:22">
       <c r="B185" s="4" t="s">
         <v>84</v>
       </c>
@@ -11474,8 +12502,10 @@
       <c r="R185" s="13"/>
       <c r="S185" s="13"/>
       <c r="T185" s="13"/>
-    </row>
-    <row r="186" spans="2:20">
+      <c r="U185" s="13"/>
+      <c r="V185" s="13"/>
+    </row>
+    <row r="186" spans="2:22">
       <c r="B186" s="4" t="s">
         <v>85</v>
       </c>
@@ -11505,8 +12535,10 @@
       <c r="R186" s="13"/>
       <c r="S186" s="13"/>
       <c r="T186" s="13"/>
-    </row>
-    <row r="187" spans="2:20">
+      <c r="U186" s="13"/>
+      <c r="V186" s="13"/>
+    </row>
+    <row r="187" spans="2:22">
       <c r="B187" s="4" t="s">
         <v>86</v>
       </c>
@@ -11538,8 +12570,10 @@
       <c r="R187" s="13"/>
       <c r="S187" s="13"/>
       <c r="T187" s="13"/>
-    </row>
-    <row r="188" spans="2:20">
+      <c r="U187" s="13"/>
+      <c r="V187" s="13"/>
+    </row>
+    <row r="188" spans="2:22">
       <c r="B188" s="4" t="s">
         <v>87</v>
       </c>
@@ -11569,8 +12603,10 @@
       <c r="R188" s="13"/>
       <c r="S188" s="13"/>
       <c r="T188" s="13"/>
-    </row>
-    <row r="189" spans="2:20">
+      <c r="U188" s="13"/>
+      <c r="V188" s="13"/>
+    </row>
+    <row r="189" spans="2:22">
       <c r="B189" s="4" t="s">
         <v>88</v>
       </c>
@@ -11598,8 +12634,10 @@
       <c r="R189" s="13"/>
       <c r="S189" s="13"/>
       <c r="T189" s="13"/>
-    </row>
-    <row r="190" spans="2:20">
+      <c r="U189" s="13"/>
+      <c r="V189" s="13"/>
+    </row>
+    <row r="190" spans="2:22">
       <c r="B190" s="5" t="s">
         <v>8</v>
       </c>
@@ -11623,8 +12661,10 @@
       <c r="R190" s="13"/>
       <c r="S190" s="13"/>
       <c r="T190" s="13"/>
-    </row>
-    <row r="191" spans="2:20">
+      <c r="U190" s="13"/>
+      <c r="V190" s="13"/>
+    </row>
+    <row r="191" spans="2:22">
       <c r="B191" s="5" t="s">
         <v>8</v>
       </c>
@@ -11648,8 +12688,10 @@
       <c r="R191" s="13"/>
       <c r="S191" s="13"/>
       <c r="T191" s="13"/>
-    </row>
-    <row r="192" spans="2:20">
+      <c r="U191" s="13"/>
+      <c r="V191" s="13"/>
+    </row>
+    <row r="192" spans="2:22">
       <c r="B192" s="5" t="s">
         <v>8</v>
       </c>
@@ -11673,8 +12715,10 @@
       <c r="R192" s="13"/>
       <c r="S192" s="13"/>
       <c r="T192" s="13"/>
-    </row>
-    <row r="193" spans="2:20">
+      <c r="U192" s="13"/>
+      <c r="V192" s="13"/>
+    </row>
+    <row r="193" spans="2:22">
       <c r="B193" s="4"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
@@ -11694,8 +12738,10 @@
       <c r="R193" s="13"/>
       <c r="S193" s="13"/>
       <c r="T193" s="13"/>
-    </row>
-    <row r="194" spans="2:20">
+      <c r="U193" s="13"/>
+      <c r="V193" s="13"/>
+    </row>
+    <row r="194" spans="2:22">
       <c r="B194" s="4" t="s">
         <v>71</v>
       </c>
@@ -11751,8 +12797,14 @@
       <c r="T194" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="195" spans="2:20">
+      <c r="U194" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V194" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="195" spans="2:22">
       <c r="B195" s="4" t="s">
         <v>71</v>
       </c>
@@ -11808,8 +12860,14 @@
       <c r="T195" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="196" spans="2:20">
+      <c r="U195" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V195" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="196" spans="2:22">
       <c r="B196" s="4" t="s">
         <v>72</v>
       </c>
@@ -11867,8 +12925,14 @@
       <c r="T196" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="197" spans="2:20">
+      <c r="U196" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V196" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="197" spans="2:22">
       <c r="B197" s="4" t="s">
         <v>73</v>
       </c>
@@ -11898,8 +12962,10 @@
       <c r="R197" s="13"/>
       <c r="S197" s="13"/>
       <c r="T197" s="13"/>
-    </row>
-    <row r="198" spans="2:20">
+      <c r="U197" s="13"/>
+      <c r="V197" s="13"/>
+    </row>
+    <row r="198" spans="2:22">
       <c r="B198" s="4" t="s">
         <v>74</v>
       </c>
@@ -11939,8 +13005,10 @@
       <c r="R198" s="13"/>
       <c r="S198" s="13"/>
       <c r="T198" s="13"/>
-    </row>
-    <row r="199" spans="2:20">
+      <c r="U198" s="13"/>
+      <c r="V198" s="13"/>
+    </row>
+    <row r="199" spans="2:22">
       <c r="B199" s="4" t="s">
         <v>75</v>
       </c>
@@ -11987,9 +13055,15 @@
       <c r="S199" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T199" s="13"/>
-    </row>
-    <row r="200" spans="2:20">
+      <c r="T199" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U199" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V199" s="13"/>
+    </row>
+    <row r="200" spans="2:22">
       <c r="B200" s="4" t="s">
         <v>76</v>
       </c>
@@ -12047,8 +13121,14 @@
       <c r="T200" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="201" spans="2:20">
+      <c r="U200" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V200" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="201" spans="2:22">
       <c r="B201" s="4" t="s">
         <v>76</v>
       </c>
@@ -12106,8 +13186,14 @@
       <c r="T201" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="202" spans="2:20">
+      <c r="U201" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V201" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="202" spans="2:22">
       <c r="B202" s="4" t="s">
         <v>77</v>
       </c>
@@ -12147,8 +13233,10 @@
       <c r="R202" s="13"/>
       <c r="S202" s="13"/>
       <c r="T202" s="13"/>
-    </row>
-    <row r="203" spans="2:20">
+      <c r="U202" s="13"/>
+      <c r="V202" s="13"/>
+    </row>
+    <row r="203" spans="2:22">
       <c r="B203" s="5" t="s">
         <v>8</v>
       </c>
@@ -12172,8 +13260,10 @@
       <c r="R203" s="13"/>
       <c r="S203" s="13"/>
       <c r="T203" s="13"/>
-    </row>
-    <row r="204" spans="2:20">
+      <c r="U203" s="13"/>
+      <c r="V203" s="13"/>
+    </row>
+    <row r="204" spans="2:22">
       <c r="B204" s="4" t="s">
         <v>89</v>
       </c>
@@ -12229,8 +13319,14 @@
       <c r="T204" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="205" spans="2:20">
+      <c r="U204" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V204" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="205" spans="2:22">
       <c r="B205" s="5" t="s">
         <v>8</v>
       </c>
@@ -12254,8 +13350,10 @@
       <c r="R205" s="13"/>
       <c r="S205" s="13"/>
       <c r="T205" s="13"/>
-    </row>
-    <row r="206" spans="2:20">
+      <c r="U205" s="13"/>
+      <c r="V205" s="13"/>
+    </row>
+    <row r="206" spans="2:22">
       <c r="B206" s="5" t="s">
         <v>8</v>
       </c>
@@ -12279,8 +13377,10 @@
       <c r="R206" s="13"/>
       <c r="S206" s="13"/>
       <c r="T206" s="13"/>
-    </row>
-    <row r="207" spans="2:20">
+      <c r="U206" s="13"/>
+      <c r="V206" s="13"/>
+    </row>
+    <row r="207" spans="2:22">
       <c r="B207" s="5" t="s">
         <v>8</v>
       </c>
@@ -12304,8 +13404,10 @@
       <c r="R207" s="13"/>
       <c r="S207" s="13"/>
       <c r="T207" s="13"/>
-    </row>
-    <row r="208" spans="2:20">
+      <c r="U207" s="13"/>
+      <c r="V207" s="13"/>
+    </row>
+    <row r="208" spans="2:22">
       <c r="B208" s="5" t="s">
         <v>8</v>
       </c>
@@ -12329,8 +13431,10 @@
       <c r="R208" s="13"/>
       <c r="S208" s="13"/>
       <c r="T208" s="13"/>
-    </row>
-    <row r="209" spans="2:20">
+      <c r="U208" s="13"/>
+      <c r="V208" s="13"/>
+    </row>
+    <row r="209" spans="2:22">
       <c r="B209" s="5" t="s">
         <v>8</v>
       </c>
@@ -12354,8 +13458,10 @@
       <c r="R209" s="13"/>
       <c r="S209" s="13"/>
       <c r="T209" s="13"/>
-    </row>
-    <row r="210" spans="2:20">
+      <c r="U209" s="13"/>
+      <c r="V209" s="13"/>
+    </row>
+    <row r="210" spans="2:22">
       <c r="B210" s="4"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
@@ -12375,8 +13481,10 @@
       <c r="R210" s="13"/>
       <c r="S210" s="13"/>
       <c r="T210" s="13"/>
-    </row>
-    <row r="211" spans="2:20">
+      <c r="U210" s="13"/>
+      <c r="V210" s="13"/>
+    </row>
+    <row r="211" spans="2:22">
       <c r="B211" s="4" t="s">
         <v>90</v>
       </c>
@@ -12432,8 +13540,14 @@
       <c r="T211" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="212" spans="2:20">
+      <c r="U211" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V211" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="212" spans="2:22">
       <c r="B212" s="4" t="s">
         <v>91</v>
       </c>
@@ -12489,8 +13603,14 @@
       <c r="T212" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="213" spans="2:20">
+      <c r="U212" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V212" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="213" spans="2:22">
       <c r="B213" s="4" t="s">
         <v>92</v>
       </c>
@@ -12520,8 +13640,10 @@
       <c r="R213" s="13"/>
       <c r="S213" s="13"/>
       <c r="T213" s="13"/>
-    </row>
-    <row r="214" spans="2:20">
+      <c r="U213" s="13"/>
+      <c r="V213" s="13"/>
+    </row>
+    <row r="214" spans="2:22">
       <c r="B214" s="4" t="s">
         <v>93</v>
       </c>
@@ -12568,9 +13690,15 @@
       <c r="S214" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T214" s="13"/>
-    </row>
-    <row r="215" spans="2:20">
+      <c r="T214" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U214" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V214" s="13"/>
+    </row>
+    <row r="215" spans="2:22">
       <c r="B215" s="4"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
@@ -12590,8 +13718,10 @@
       <c r="R215" s="13"/>
       <c r="S215" s="13"/>
       <c r="T215" s="13"/>
-    </row>
-    <row r="216" spans="2:20">
+      <c r="U215" s="13"/>
+      <c r="V215" s="13"/>
+    </row>
+    <row r="216" spans="2:22">
       <c r="B216" s="4" t="s">
         <v>94</v>
       </c>
@@ -12621,8 +13751,10 @@
       <c r="R216" s="13"/>
       <c r="S216" s="13"/>
       <c r="T216" s="13"/>
-    </row>
-    <row r="217" spans="2:20">
+      <c r="U216" s="13"/>
+      <c r="V216" s="13"/>
+    </row>
+    <row r="217" spans="2:22">
       <c r="B217" s="4" t="s">
         <v>95</v>
       </c>
@@ -12676,8 +13808,14 @@
       <c r="T217" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="218" spans="2:20">
+      <c r="U217" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V217" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="218" spans="2:22">
       <c r="B218" s="4" t="s">
         <v>96</v>
       </c>
@@ -12727,8 +13865,14 @@
       <c r="T218" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="219" spans="2:20">
+      <c r="U218" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V218" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="219" spans="2:22">
       <c r="B219" s="4" t="s">
         <v>97</v>
       </c>
@@ -12784,8 +13928,14 @@
       <c r="T219" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="220" spans="2:20">
+      <c r="U219" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V219" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="220" spans="2:22">
       <c r="B220" s="4" t="s">
         <v>98</v>
       </c>
@@ -12815,8 +13965,10 @@
       <c r="R220" s="13"/>
       <c r="S220" s="13"/>
       <c r="T220" s="13"/>
-    </row>
-    <row r="221" spans="2:20">
+      <c r="U220" s="13"/>
+      <c r="V220" s="13"/>
+    </row>
+    <row r="221" spans="2:22">
       <c r="B221" s="4" t="s">
         <v>99</v>
       </c>
@@ -12846,8 +13998,10 @@
       <c r="R221" s="13"/>
       <c r="S221" s="13"/>
       <c r="T221" s="13"/>
-    </row>
-    <row r="222" spans="2:20">
+      <c r="U221" s="13"/>
+      <c r="V221" s="13"/>
+    </row>
+    <row r="222" spans="2:22">
       <c r="B222" s="4" t="s">
         <v>100</v>
       </c>
@@ -12879,8 +14033,10 @@
       <c r="R222" s="13"/>
       <c r="S222" s="13"/>
       <c r="T222" s="13"/>
-    </row>
-    <row r="223" spans="2:20">
+      <c r="U222" s="13"/>
+      <c r="V222" s="13"/>
+    </row>
+    <row r="223" spans="2:22">
       <c r="B223" s="4" t="s">
         <v>101</v>
       </c>
@@ -12938,8 +14094,14 @@
       <c r="T223" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="224" spans="2:20">
+      <c r="U223" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V223" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="224" spans="2:22">
       <c r="B224" s="4"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
@@ -12959,8 +14121,10 @@
       <c r="R224" s="13"/>
       <c r="S224" s="13"/>
       <c r="T224" s="13"/>
-    </row>
-    <row r="225" spans="2:20">
+      <c r="U224" s="13"/>
+      <c r="V224" s="13"/>
+    </row>
+    <row r="225" spans="2:22">
       <c r="B225" s="4" t="s">
         <v>71</v>
       </c>
@@ -13016,8 +14180,14 @@
       <c r="T225" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="226" spans="2:20">
+      <c r="U225" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V225" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="226" spans="2:22">
       <c r="B226" s="4" t="s">
         <v>76</v>
       </c>
@@ -13075,8 +14245,14 @@
       <c r="T226" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="227" spans="2:20">
+      <c r="U226" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V226" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="227" spans="2:22">
       <c r="B227" s="5" t="s">
         <v>8</v>
       </c>
@@ -13100,8 +14276,10 @@
       <c r="R227" s="13"/>
       <c r="S227" s="13"/>
       <c r="T227" s="13"/>
-    </row>
-    <row r="228" spans="2:20">
+      <c r="U227" s="13"/>
+      <c r="V227" s="13"/>
+    </row>
+    <row r="228" spans="2:22">
       <c r="B228" s="5" t="s">
         <v>8</v>
       </c>
@@ -13125,8 +14303,10 @@
       <c r="R228" s="13"/>
       <c r="S228" s="13"/>
       <c r="T228" s="13"/>
-    </row>
-    <row r="229" spans="2:20">
+      <c r="U228" s="13"/>
+      <c r="V228" s="13"/>
+    </row>
+    <row r="229" spans="2:22">
       <c r="B229" s="4"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
@@ -13146,8 +14326,10 @@
       <c r="R229" s="13"/>
       <c r="S229" s="13"/>
       <c r="T229" s="13"/>
-    </row>
-    <row r="230" spans="2:20">
+      <c r="U229" s="13"/>
+      <c r="V229" s="13"/>
+    </row>
+    <row r="230" spans="2:22">
       <c r="B230" s="4"/>
       <c r="C230" s="3" t="s">
         <v>234</v>
@@ -13185,8 +14367,10 @@
       <c r="R230" s="13"/>
       <c r="S230" s="13"/>
       <c r="T230" s="13"/>
-    </row>
-    <row r="231" spans="2:20">
+      <c r="U230" s="13"/>
+      <c r="V230" s="13"/>
+    </row>
+    <row r="231" spans="2:22">
       <c r="B231" s="4"/>
       <c r="C231" s="3" t="s">
         <v>235</v>
@@ -13224,8 +14408,10 @@
       <c r="R231" s="13"/>
       <c r="S231" s="13"/>
       <c r="T231" s="13"/>
-    </row>
-    <row r="232" spans="2:20">
+      <c r="U231" s="13"/>
+      <c r="V231" s="13"/>
+    </row>
+    <row r="232" spans="2:22">
       <c r="B232" s="4"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
@@ -13245,8 +14431,10 @@
       <c r="R232" s="13"/>
       <c r="S232" s="13"/>
       <c r="T232" s="13"/>
-    </row>
-    <row r="233" spans="2:20">
+      <c r="U232" s="13"/>
+      <c r="V232" s="13"/>
+    </row>
+    <row r="233" spans="2:22">
       <c r="B233" s="4" t="s">
         <v>102</v>
       </c>
@@ -13286,8 +14474,10 @@
       <c r="R233" s="13"/>
       <c r="S233" s="13"/>
       <c r="T233" s="13"/>
-    </row>
-    <row r="234" spans="2:20">
+      <c r="U233" s="13"/>
+      <c r="V233" s="13"/>
+    </row>
+    <row r="234" spans="2:22">
       <c r="B234" s="4" t="s">
         <v>103</v>
       </c>
@@ -13327,8 +14517,10 @@
       <c r="R234" s="13"/>
       <c r="S234" s="13"/>
       <c r="T234" s="13"/>
-    </row>
-    <row r="235" spans="2:20">
+      <c r="U234" s="13"/>
+      <c r="V234" s="13"/>
+    </row>
+    <row r="235" spans="2:22">
       <c r="B235" s="4" t="s">
         <v>104</v>
       </c>
@@ -13368,8 +14560,10 @@
       <c r="R235" s="13"/>
       <c r="S235" s="13"/>
       <c r="T235" s="13"/>
-    </row>
-    <row r="236" spans="2:20">
+      <c r="U235" s="13"/>
+      <c r="V235" s="13"/>
+    </row>
+    <row r="236" spans="2:22">
       <c r="B236" s="5" t="s">
         <v>8</v>
       </c>
@@ -13409,8 +14603,10 @@
       <c r="R236" s="13"/>
       <c r="S236" s="13"/>
       <c r="T236" s="13"/>
-    </row>
-    <row r="237" spans="2:20">
+      <c r="U236" s="13"/>
+      <c r="V236" s="13"/>
+    </row>
+    <row r="237" spans="2:22">
       <c r="B237" s="4"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
@@ -13430,8 +14626,10 @@
       <c r="R237" s="13"/>
       <c r="S237" s="13"/>
       <c r="T237" s="13"/>
-    </row>
-    <row r="238" spans="2:20">
+      <c r="U237" s="13"/>
+      <c r="V237" s="13"/>
+    </row>
+    <row r="238" spans="2:22">
       <c r="B238" s="4" t="s">
         <v>105</v>
       </c>
@@ -13471,8 +14669,10 @@
       <c r="R238" s="13"/>
       <c r="S238" s="13"/>
       <c r="T238" s="13"/>
-    </row>
-    <row r="239" spans="2:20">
+      <c r="U238" s="13"/>
+      <c r="V238" s="13"/>
+    </row>
+    <row r="239" spans="2:22">
       <c r="B239" s="4" t="s">
         <v>80</v>
       </c>
@@ -13512,8 +14712,10 @@
       <c r="R239" s="13"/>
       <c r="S239" s="13"/>
       <c r="T239" s="13"/>
-    </row>
-    <row r="240" spans="2:20">
+      <c r="U239" s="13"/>
+      <c r="V239" s="13"/>
+    </row>
+    <row r="240" spans="2:22">
       <c r="B240" s="4" t="s">
         <v>106</v>
       </c>
@@ -13553,8 +14755,10 @@
       <c r="R240" s="13"/>
       <c r="S240" s="13"/>
       <c r="T240" s="13"/>
-    </row>
-    <row r="241" spans="2:20">
+      <c r="U240" s="13"/>
+      <c r="V240" s="13"/>
+    </row>
+    <row r="241" spans="2:22">
       <c r="B241" s="4" t="s">
         <v>81</v>
       </c>
@@ -13594,8 +14798,10 @@
       <c r="R241" s="13"/>
       <c r="S241" s="13"/>
       <c r="T241" s="13"/>
-    </row>
-    <row r="242" spans="2:20">
+      <c r="U241" s="13"/>
+      <c r="V241" s="13"/>
+    </row>
+    <row r="242" spans="2:22">
       <c r="B242" s="4"/>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
@@ -13615,8 +14821,10 @@
       <c r="R242" s="13"/>
       <c r="S242" s="13"/>
       <c r="T242" s="13"/>
-    </row>
-    <row r="243" spans="2:20">
+      <c r="U242" s="13"/>
+      <c r="V242" s="13"/>
+    </row>
+    <row r="243" spans="2:22">
       <c r="B243" s="4" t="s">
         <v>107</v>
       </c>
@@ -13658,8 +14866,10 @@
       <c r="R243" s="13"/>
       <c r="S243" s="13"/>
       <c r="T243" s="13"/>
-    </row>
-    <row r="244" spans="2:20">
+      <c r="U243" s="13"/>
+      <c r="V243" s="13"/>
+    </row>
+    <row r="244" spans="2:22">
       <c r="B244" s="4" t="s">
         <v>108</v>
       </c>
@@ -13715,8 +14925,14 @@
       <c r="T244" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="245" spans="2:20">
+      <c r="U244" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V244" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="245" spans="2:22">
       <c r="B245" s="4" t="s">
         <v>109</v>
       </c>
@@ -13772,8 +14988,14 @@
       <c r="T245" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="246" spans="2:20">
+      <c r="U245" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V245" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="246" spans="2:22">
       <c r="B246" s="4" t="s">
         <v>110</v>
       </c>
@@ -13829,8 +15051,14 @@
       <c r="T246" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="247" spans="2:20">
+      <c r="U246" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V246" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="247" spans="2:22">
       <c r="B247" s="4" t="s">
         <v>111</v>
       </c>
@@ -13868,8 +15096,10 @@
       <c r="R247" s="13"/>
       <c r="S247" s="13"/>
       <c r="T247" s="13"/>
-    </row>
-    <row r="248" spans="2:20">
+      <c r="U247" s="13"/>
+      <c r="V247" s="13"/>
+    </row>
+    <row r="248" spans="2:22">
       <c r="B248" s="4" t="s">
         <v>112</v>
       </c>
@@ -13925,8 +15155,14 @@
       <c r="T248" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="249" spans="2:20">
+      <c r="U248" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V248" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="249" spans="2:22">
       <c r="B249" s="4" t="s">
         <v>113</v>
       </c>
@@ -13982,8 +15218,14 @@
       <c r="T249" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="250" spans="2:20">
+      <c r="U249" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V249" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="250" spans="2:22">
       <c r="B250" s="4" t="s">
         <v>114</v>
       </c>
@@ -14034,9 +15276,15 @@
       <c r="S250" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T250" s="13"/>
-    </row>
-    <row r="251" spans="2:20">
+      <c r="T250" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U250" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V250" s="13"/>
+    </row>
+    <row r="251" spans="2:22">
       <c r="B251" s="4" t="s">
         <v>115</v>
       </c>
@@ -14087,9 +15335,15 @@
       <c r="S251" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="T251" s="13"/>
-    </row>
-    <row r="252" spans="2:20">
+      <c r="T251" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U251" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V251" s="13"/>
+    </row>
+    <row r="252" spans="2:22">
       <c r="B252" s="4" t="s">
         <v>116</v>
       </c>
@@ -14115,8 +15369,10 @@
       <c r="R252" s="13"/>
       <c r="S252" s="13"/>
       <c r="T252" s="13"/>
-    </row>
-    <row r="253" spans="2:20">
+      <c r="U252" s="13"/>
+      <c r="V252" s="13"/>
+    </row>
+    <row r="253" spans="2:22">
       <c r="B253" s="4" t="s">
         <v>117</v>
       </c>
@@ -14172,8 +15428,14 @@
       <c r="T253" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="254" spans="2:20">
+      <c r="U253" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V253" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="254" spans="2:22">
       <c r="B254" s="5" t="s">
         <v>8</v>
       </c>
@@ -14197,8 +15459,10 @@
       <c r="R254" s="13"/>
       <c r="S254" s="13"/>
       <c r="T254" s="13"/>
-    </row>
-    <row r="255" spans="2:20">
+      <c r="U254" s="13"/>
+      <c r="V254" s="13"/>
+    </row>
+    <row r="255" spans="2:22">
       <c r="B255" s="4" t="s">
         <v>118</v>
       </c>
@@ -14224,8 +15488,10 @@
       <c r="R255" s="13"/>
       <c r="S255" s="13"/>
       <c r="T255" s="13"/>
-    </row>
-    <row r="256" spans="2:20">
+      <c r="U255" s="13"/>
+      <c r="V255" s="13"/>
+    </row>
+    <row r="256" spans="2:22">
       <c r="B256" s="4" t="s">
         <v>119</v>
       </c>
@@ -14255,8 +15521,10 @@
       <c r="R256" s="13"/>
       <c r="S256" s="13"/>
       <c r="T256" s="13"/>
-    </row>
-    <row r="257" spans="2:20">
+      <c r="U256" s="13"/>
+      <c r="V256" s="13"/>
+    </row>
+    <row r="257" spans="2:22">
       <c r="B257" s="4" t="s">
         <v>120</v>
       </c>
@@ -14288,8 +15556,10 @@
       <c r="R257" s="13"/>
       <c r="S257" s="13"/>
       <c r="T257" s="13"/>
-    </row>
-    <row r="258" spans="2:20">
+      <c r="U257" s="13"/>
+      <c r="V257" s="13"/>
+    </row>
+    <row r="258" spans="2:22">
       <c r="B258" s="4" t="s">
         <v>121</v>
       </c>
@@ -14336,9 +15606,15 @@
       <c r="S258" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T258" s="13"/>
-    </row>
-    <row r="259" spans="2:20">
+      <c r="T258" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U258" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V258" s="13"/>
+    </row>
+    <row r="259" spans="2:22">
       <c r="B259" s="4" t="s">
         <v>122</v>
       </c>
@@ -14385,9 +15661,15 @@
       <c r="S259" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T259" s="13"/>
-    </row>
-    <row r="260" spans="2:20">
+      <c r="T259" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U259" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V259" s="13"/>
+    </row>
+    <row r="260" spans="2:22">
       <c r="B260" s="4" t="s">
         <v>123</v>
       </c>
@@ -14434,9 +15716,15 @@
       <c r="S260" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T260" s="13"/>
-    </row>
-    <row r="261" spans="2:20">
+      <c r="T260" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U260" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V260" s="13"/>
+    </row>
+    <row r="261" spans="2:22">
       <c r="B261" s="4" t="s">
         <v>124</v>
       </c>
@@ -14483,9 +15771,15 @@
       <c r="S261" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T261" s="13"/>
-    </row>
-    <row r="262" spans="2:20">
+      <c r="T261" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U261" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V261" s="13"/>
+    </row>
+    <row r="262" spans="2:22">
       <c r="B262" s="4" t="s">
         <v>125</v>
       </c>
@@ -14525,8 +15819,10 @@
       <c r="R262" s="13"/>
       <c r="S262" s="13"/>
       <c r="T262" s="13"/>
-    </row>
-    <row r="263" spans="2:20">
+      <c r="U262" s="13"/>
+      <c r="V262" s="13"/>
+    </row>
+    <row r="263" spans="2:22">
       <c r="B263" s="5" t="s">
         <v>8</v>
       </c>
@@ -14550,8 +15846,10 @@
       <c r="R263" s="13"/>
       <c r="S263" s="13"/>
       <c r="T263" s="13"/>
-    </row>
-    <row r="264" spans="2:20">
+      <c r="U263" s="13"/>
+      <c r="V263" s="13"/>
+    </row>
+    <row r="264" spans="2:22">
       <c r="B264" s="4" t="s">
         <v>126</v>
       </c>
@@ -14598,9 +15896,15 @@
       <c r="S264" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T264" s="13"/>
-    </row>
-    <row r="265" spans="2:20">
+      <c r="T264" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U264" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V264" s="13"/>
+    </row>
+    <row r="265" spans="2:22">
       <c r="B265" s="4" t="s">
         <v>127</v>
       </c>
@@ -14647,9 +15951,15 @@
       <c r="S265" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="T265" s="13"/>
-    </row>
-    <row r="266" spans="2:20">
+      <c r="T265" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U265" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V265" s="13"/>
+    </row>
+    <row r="266" spans="2:22">
       <c r="B266" s="5" t="s">
         <v>8</v>
       </c>
@@ -14673,8 +15983,10 @@
       <c r="R266" s="13"/>
       <c r="S266" s="13"/>
       <c r="T266" s="13"/>
-    </row>
-    <row r="267" spans="2:20">
+      <c r="U266" s="13"/>
+      <c r="V266" s="13"/>
+    </row>
+    <row r="267" spans="2:22">
       <c r="B267" s="5" t="s">
         <v>128</v>
       </c>
@@ -14698,8 +16010,10 @@
       <c r="R267" s="13"/>
       <c r="S267" s="13"/>
       <c r="T267" s="13"/>
-    </row>
-    <row r="268" spans="2:20">
+      <c r="U267" s="13"/>
+      <c r="V267" s="13"/>
+    </row>
+    <row r="268" spans="2:22">
       <c r="B268" s="5" t="s">
         <v>128</v>
       </c>
@@ -14723,8 +16037,10 @@
       <c r="R268" s="13"/>
       <c r="S268" s="13"/>
       <c r="T268" s="13"/>
-    </row>
-    <row r="269" spans="2:20">
+      <c r="U268" s="13"/>
+      <c r="V268" s="13"/>
+    </row>
+    <row r="269" spans="2:22">
       <c r="B269" s="5" t="s">
         <v>128</v>
       </c>
@@ -14748,8 +16064,10 @@
       <c r="R269" s="13"/>
       <c r="S269" s="13"/>
       <c r="T269" s="13"/>
-    </row>
-    <row r="270" spans="2:20">
+      <c r="U269" s="13"/>
+      <c r="V269" s="13"/>
+    </row>
+    <row r="270" spans="2:22">
       <c r="B270" s="5" t="s">
         <v>128</v>
       </c>
@@ -14773,8 +16091,10 @@
       <c r="R270" s="13"/>
       <c r="S270" s="13"/>
       <c r="T270" s="13"/>
-    </row>
-    <row r="271" spans="2:20">
+      <c r="U270" s="13"/>
+      <c r="V270" s="13"/>
+    </row>
+    <row r="271" spans="2:22">
       <c r="B271" s="5" t="s">
         <v>128</v>
       </c>
@@ -14798,8 +16118,10 @@
       <c r="R271" s="13"/>
       <c r="S271" s="13"/>
       <c r="T271" s="13"/>
-    </row>
-    <row r="272" spans="2:20">
+      <c r="U271" s="13"/>
+      <c r="V271" s="13"/>
+    </row>
+    <row r="272" spans="2:22">
       <c r="B272" s="5" t="s">
         <v>128</v>
       </c>
@@ -14823,8 +16145,10 @@
       <c r="R272" s="13"/>
       <c r="S272" s="13"/>
       <c r="T272" s="13"/>
-    </row>
-    <row r="273" spans="2:20">
+      <c r="U272" s="13"/>
+      <c r="V272" s="13"/>
+    </row>
+    <row r="273" spans="2:22">
       <c r="B273" s="5" t="s">
         <v>128</v>
       </c>
@@ -14848,8 +16172,10 @@
       <c r="R273" s="13"/>
       <c r="S273" s="13"/>
       <c r="T273" s="13"/>
-    </row>
-    <row r="274" spans="2:20">
+      <c r="U273" s="13"/>
+      <c r="V273" s="13"/>
+    </row>
+    <row r="274" spans="2:22">
       <c r="B274" s="5" t="s">
         <v>128</v>
       </c>
@@ -14873,8 +16199,10 @@
       <c r="R274" s="13"/>
       <c r="S274" s="13"/>
       <c r="T274" s="13"/>
-    </row>
-    <row r="275" spans="2:20">
+      <c r="U274" s="13"/>
+      <c r="V274" s="13"/>
+    </row>
+    <row r="275" spans="2:22">
       <c r="B275" s="4"/>
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
@@ -14894,8 +16222,10 @@
       <c r="R275" s="13"/>
       <c r="S275" s="13"/>
       <c r="T275" s="13"/>
-    </row>
-    <row r="276" spans="2:20">
+      <c r="U275" s="13"/>
+      <c r="V275" s="13"/>
+    </row>
+    <row r="276" spans="2:22">
       <c r="B276" s="4"/>
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
@@ -14915,8 +16245,10 @@
       <c r="R276" s="14"/>
       <c r="S276" s="14"/>
       <c r="T276" s="14"/>
-    </row>
-    <row r="277" spans="2:20">
+      <c r="U276" s="14"/>
+      <c r="V276" s="14"/>
+    </row>
+    <row r="277" spans="2:22">
       <c r="B277" s="4"/>
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
@@ -14936,8 +16268,10 @@
       <c r="R277" s="14"/>
       <c r="S277" s="14"/>
       <c r="T277" s="14"/>
-    </row>
-    <row r="278" spans="2:20">
+      <c r="U277" s="14"/>
+      <c r="V277" s="14"/>
+    </row>
+    <row r="278" spans="2:22">
       <c r="B278" s="4"/>
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
@@ -14957,8 +16291,10 @@
       <c r="R278" s="14"/>
       <c r="S278" s="14"/>
       <c r="T278" s="14"/>
-    </row>
-    <row r="279" spans="2:20">
+      <c r="U278" s="14"/>
+      <c r="V278" s="14"/>
+    </row>
+    <row r="279" spans="2:22">
       <c r="B279" s="4"/>
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
@@ -14978,8 +16314,10 @@
       <c r="R279" s="14"/>
       <c r="S279" s="14"/>
       <c r="T279" s="14"/>
-    </row>
-    <row r="280" spans="2:20">
+      <c r="U279" s="14"/>
+      <c r="V279" s="14"/>
+    </row>
+    <row r="280" spans="2:22">
       <c r="B280" s="4"/>
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
@@ -14999,8 +16337,10 @@
       <c r="R280" s="14"/>
       <c r="S280" s="14"/>
       <c r="T280" s="14"/>
-    </row>
-    <row r="281" spans="2:20">
+      <c r="U280" s="14"/>
+      <c r="V280" s="14"/>
+    </row>
+    <row r="281" spans="2:22">
       <c r="B281" s="4"/>
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
@@ -15020,8 +16360,10 @@
       <c r="R281" s="14"/>
       <c r="S281" s="14"/>
       <c r="T281" s="14"/>
-    </row>
-    <row r="282" spans="2:20">
+      <c r="U281" s="14"/>
+      <c r="V281" s="14"/>
+    </row>
+    <row r="282" spans="2:22">
       <c r="B282" s="4"/>
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
@@ -15041,8 +16383,10 @@
       <c r="R282" s="14"/>
       <c r="S282" s="14"/>
       <c r="T282" s="14"/>
-    </row>
-    <row r="283" spans="2:20">
+      <c r="U282" s="14"/>
+      <c r="V282" s="14"/>
+    </row>
+    <row r="283" spans="2:22">
       <c r="B283" s="4"/>
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
@@ -15062,8 +16406,10 @@
       <c r="R283" s="14"/>
       <c r="S283" s="14"/>
       <c r="T283" s="14"/>
-    </row>
-    <row r="284" spans="2:20">
+      <c r="U283" s="14"/>
+      <c r="V283" s="14"/>
+    </row>
+    <row r="284" spans="2:22">
       <c r="B284" s="4"/>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
@@ -15083,8 +16429,10 @@
       <c r="R284" s="14"/>
       <c r="S284" s="14"/>
       <c r="T284" s="14"/>
-    </row>
-    <row r="285" spans="2:20">
+      <c r="U284" s="14"/>
+      <c r="V284" s="14"/>
+    </row>
+    <row r="285" spans="2:22">
       <c r="B285" s="5"/>
       <c r="C285" s="17"/>
       <c r="D285" s="3"/>
@@ -15104,8 +16452,10 @@
       <c r="R285" s="14"/>
       <c r="S285" s="14"/>
       <c r="T285" s="14"/>
-    </row>
-    <row r="286" spans="2:20">
+      <c r="U285" s="14"/>
+      <c r="V285" s="14"/>
+    </row>
+    <row r="286" spans="2:22">
       <c r="B286" s="4"/>
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
@@ -15125,8 +16475,10 @@
       <c r="R286" s="14"/>
       <c r="S286" s="14"/>
       <c r="T286" s="14"/>
-    </row>
-    <row r="287" spans="2:20">
+      <c r="U286" s="14"/>
+      <c r="V286" s="14"/>
+    </row>
+    <row r="287" spans="2:22">
       <c r="B287" s="5"/>
       <c r="C287" s="17"/>
       <c r="D287" s="3"/>
@@ -15146,8 +16498,10 @@
       <c r="R287" s="14"/>
       <c r="S287" s="14"/>
       <c r="T287" s="14"/>
-    </row>
-    <row r="288" spans="2:20">
+      <c r="U287" s="14"/>
+      <c r="V287" s="14"/>
+    </row>
+    <row r="288" spans="2:22">
       <c r="B288" s="5"/>
       <c r="C288" s="17"/>
       <c r="D288" s="3"/>
@@ -15167,8 +16521,10 @@
       <c r="R288" s="14"/>
       <c r="S288" s="14"/>
       <c r="T288" s="14"/>
-    </row>
-    <row r="289" spans="2:20">
+      <c r="U288" s="14"/>
+      <c r="V288" s="14"/>
+    </row>
+    <row r="289" spans="2:22">
       <c r="B289" s="4"/>
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
@@ -15188,8 +16544,10 @@
       <c r="R289" s="14"/>
       <c r="S289" s="14"/>
       <c r="T289" s="14"/>
-    </row>
-    <row r="290" spans="2:20">
+      <c r="U289" s="14"/>
+      <c r="V289" s="14"/>
+    </row>
+    <row r="290" spans="2:22">
       <c r="B290" s="4"/>
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
@@ -15209,8 +16567,10 @@
       <c r="R290" s="14"/>
       <c r="S290" s="14"/>
       <c r="T290" s="14"/>
-    </row>
-    <row r="291" spans="2:20">
+      <c r="U290" s="14"/>
+      <c r="V290" s="14"/>
+    </row>
+    <row r="291" spans="2:22">
       <c r="B291" s="4"/>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
@@ -15230,8 +16590,10 @@
       <c r="R291" s="14"/>
       <c r="S291" s="14"/>
       <c r="T291" s="14"/>
-    </row>
-    <row r="292" spans="2:20">
+      <c r="U291" s="14"/>
+      <c r="V291" s="14"/>
+    </row>
+    <row r="292" spans="2:22">
       <c r="B292" s="4"/>
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
@@ -15251,8 +16613,10 @@
       <c r="R292" s="13"/>
       <c r="S292" s="13"/>
       <c r="T292" s="13"/>
-    </row>
-    <row r="293" spans="2:20">
+      <c r="U292" s="13"/>
+      <c r="V292" s="13"/>
+    </row>
+    <row r="293" spans="2:22">
       <c r="B293" s="4"/>
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
@@ -15272,8 +16636,10 @@
       <c r="R293" s="14"/>
       <c r="S293" s="14"/>
       <c r="T293" s="14"/>
-    </row>
-    <row r="294" spans="2:20">
+      <c r="U293" s="14"/>
+      <c r="V293" s="14"/>
+    </row>
+    <row r="294" spans="2:22">
       <c r="B294" s="4"/>
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
@@ -15293,8 +16659,10 @@
       <c r="R294" s="14"/>
       <c r="S294" s="14"/>
       <c r="T294" s="14"/>
-    </row>
-    <row r="295" spans="2:20">
+      <c r="U294" s="14"/>
+      <c r="V294" s="14"/>
+    </row>
+    <row r="295" spans="2:22">
       <c r="B295" s="4"/>
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
@@ -15314,8 +16682,10 @@
       <c r="R295" s="14"/>
       <c r="S295" s="14"/>
       <c r="T295" s="14"/>
-    </row>
-    <row r="296" spans="2:20">
+      <c r="U295" s="14"/>
+      <c r="V295" s="14"/>
+    </row>
+    <row r="296" spans="2:22">
       <c r="B296" s="4"/>
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
@@ -15335,8 +16705,10 @@
       <c r="R296" s="14"/>
       <c r="S296" s="14"/>
       <c r="T296" s="14"/>
-    </row>
-    <row r="297" spans="2:20">
+      <c r="U296" s="14"/>
+      <c r="V296" s="14"/>
+    </row>
+    <row r="297" spans="2:22">
       <c r="B297" s="4"/>
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
@@ -15356,8 +16728,10 @@
       <c r="R297" s="14"/>
       <c r="S297" s="14"/>
       <c r="T297" s="14"/>
-    </row>
-    <row r="298" spans="2:20">
+      <c r="U297" s="14"/>
+      <c r="V297" s="14"/>
+    </row>
+    <row r="298" spans="2:22">
       <c r="B298" s="4"/>
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
@@ -15377,8 +16751,10 @@
       <c r="R298" s="14"/>
       <c r="S298" s="14"/>
       <c r="T298" s="14"/>
-    </row>
-    <row r="299" spans="2:20">
+      <c r="U298" s="14"/>
+      <c r="V298" s="14"/>
+    </row>
+    <row r="299" spans="2:22">
       <c r="B299" s="4"/>
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
@@ -15398,8 +16774,10 @@
       <c r="R299" s="14"/>
       <c r="S299" s="14"/>
       <c r="T299" s="14"/>
-    </row>
-    <row r="300" spans="2:20">
+      <c r="U299" s="14"/>
+      <c r="V299" s="14"/>
+    </row>
+    <row r="300" spans="2:22">
       <c r="B300" s="4"/>
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
@@ -15419,8 +16797,10 @@
       <c r="R300" s="14"/>
       <c r="S300" s="14"/>
       <c r="T300" s="14"/>
-    </row>
-    <row r="301" spans="2:20">
+      <c r="U300" s="14"/>
+      <c r="V300" s="14"/>
+    </row>
+    <row r="301" spans="2:22">
       <c r="B301" s="4"/>
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
@@ -15440,8 +16820,10 @@
       <c r="R301" s="14"/>
       <c r="S301" s="14"/>
       <c r="T301" s="14"/>
-    </row>
-    <row r="302" spans="2:20">
+      <c r="U301" s="14"/>
+      <c r="V301" s="14"/>
+    </row>
+    <row r="302" spans="2:22">
       <c r="B302" s="5"/>
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
@@ -15461,8 +16843,10 @@
       <c r="R302" s="14"/>
       <c r="S302" s="14"/>
       <c r="T302" s="14"/>
-    </row>
-    <row r="303" spans="2:20">
+      <c r="U302" s="14"/>
+      <c r="V302" s="14"/>
+    </row>
+    <row r="303" spans="2:22">
       <c r="B303" s="4"/>
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
@@ -15482,8 +16866,10 @@
       <c r="R303" s="14"/>
       <c r="S303" s="14"/>
       <c r="T303" s="14"/>
-    </row>
-    <row r="304" spans="2:20">
+      <c r="U303" s="14"/>
+      <c r="V303" s="14"/>
+    </row>
+    <row r="304" spans="2:22">
       <c r="B304" s="5"/>
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
@@ -15503,8 +16889,10 @@
       <c r="R304" s="14"/>
       <c r="S304" s="14"/>
       <c r="T304" s="14"/>
-    </row>
-    <row r="305" spans="2:20">
+      <c r="U304" s="14"/>
+      <c r="V304" s="14"/>
+    </row>
+    <row r="305" spans="2:22">
       <c r="B305" s="5"/>
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
@@ -15524,8 +16912,10 @@
       <c r="R305" s="14"/>
       <c r="S305" s="14"/>
       <c r="T305" s="14"/>
-    </row>
-    <row r="306" spans="2:20">
+      <c r="U305" s="14"/>
+      <c r="V305" s="14"/>
+    </row>
+    <row r="306" spans="2:22">
       <c r="B306" s="4"/>
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
@@ -15545,8 +16935,10 @@
       <c r="R306" s="14"/>
       <c r="S306" s="14"/>
       <c r="T306" s="14"/>
-    </row>
-    <row r="307" spans="2:20">
+      <c r="U306" s="14"/>
+      <c r="V306" s="14"/>
+    </row>
+    <row r="307" spans="2:22">
       <c r="B307" s="4"/>
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
@@ -15566,8 +16958,10 @@
       <c r="R307" s="14"/>
       <c r="S307" s="14"/>
       <c r="T307" s="14"/>
-    </row>
-    <row r="308" spans="2:20">
+      <c r="U307" s="14"/>
+      <c r="V307" s="14"/>
+    </row>
+    <row r="308" spans="2:22">
       <c r="B308" s="4"/>
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
@@ -15587,8 +16981,10 @@
       <c r="R308" s="14"/>
       <c r="S308" s="14"/>
       <c r="T308" s="14"/>
-    </row>
-    <row r="309" spans="2:20">
+      <c r="U308" s="14"/>
+      <c r="V308" s="14"/>
+    </row>
+    <row r="309" spans="2:22">
       <c r="B309" s="4"/>
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
@@ -15608,8 +17004,10 @@
       <c r="R309" s="13"/>
       <c r="S309" s="13"/>
       <c r="T309" s="13"/>
-    </row>
-    <row r="310" spans="2:20">
+      <c r="U309" s="13"/>
+      <c r="V309" s="13"/>
+    </row>
+    <row r="310" spans="2:22">
       <c r="B310" s="4"/>
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
@@ -15629,8 +17027,10 @@
       <c r="R310" s="14"/>
       <c r="S310" s="14"/>
       <c r="T310" s="14"/>
-    </row>
-    <row r="311" spans="2:20">
+      <c r="U310" s="14"/>
+      <c r="V310" s="14"/>
+    </row>
+    <row r="311" spans="2:22">
       <c r="B311" s="4"/>
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
@@ -15650,8 +17050,10 @@
       <c r="R311" s="14"/>
       <c r="S311" s="14"/>
       <c r="T311" s="14"/>
-    </row>
-    <row r="312" spans="2:20">
+      <c r="U311" s="14"/>
+      <c r="V311" s="14"/>
+    </row>
+    <row r="312" spans="2:22">
       <c r="B312" s="4"/>
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
@@ -15671,8 +17073,10 @@
       <c r="R312" s="14"/>
       <c r="S312" s="14"/>
       <c r="T312" s="14"/>
-    </row>
-    <row r="313" spans="2:20">
+      <c r="U312" s="14"/>
+      <c r="V312" s="14"/>
+    </row>
+    <row r="313" spans="2:22">
       <c r="B313" s="4"/>
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
@@ -15692,8 +17096,10 @@
       <c r="R313" s="14"/>
       <c r="S313" s="14"/>
       <c r="T313" s="14"/>
-    </row>
-    <row r="314" spans="2:20">
+      <c r="U313" s="14"/>
+      <c r="V313" s="14"/>
+    </row>
+    <row r="314" spans="2:22">
       <c r="B314" s="4"/>
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
@@ -15713,8 +17119,10 @@
       <c r="R314" s="14"/>
       <c r="S314" s="14"/>
       <c r="T314" s="14"/>
-    </row>
-    <row r="315" spans="2:20">
+      <c r="U314" s="14"/>
+      <c r="V314" s="14"/>
+    </row>
+    <row r="315" spans="2:22">
       <c r="B315" s="4"/>
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
@@ -15734,8 +17142,10 @@
       <c r="R315" s="14"/>
       <c r="S315" s="14"/>
       <c r="T315" s="14"/>
-    </row>
-    <row r="316" spans="2:20">
+      <c r="U315" s="14"/>
+      <c r="V315" s="14"/>
+    </row>
+    <row r="316" spans="2:22">
       <c r="B316" s="4"/>
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
@@ -15755,8 +17165,10 @@
       <c r="R316" s="14"/>
       <c r="S316" s="14"/>
       <c r="T316" s="14"/>
-    </row>
-    <row r="317" spans="2:20">
+      <c r="U316" s="14"/>
+      <c r="V316" s="14"/>
+    </row>
+    <row r="317" spans="2:22">
       <c r="B317" s="4"/>
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
@@ -15776,8 +17188,10 @@
       <c r="R317" s="14"/>
       <c r="S317" s="14"/>
       <c r="T317" s="14"/>
-    </row>
-    <row r="318" spans="2:20">
+      <c r="U317" s="14"/>
+      <c r="V317" s="14"/>
+    </row>
+    <row r="318" spans="2:22">
       <c r="B318" s="4"/>
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
@@ -15797,8 +17211,10 @@
       <c r="R318" s="14"/>
       <c r="S318" s="14"/>
       <c r="T318" s="14"/>
-    </row>
-    <row r="319" spans="2:20">
+      <c r="U318" s="14"/>
+      <c r="V318" s="14"/>
+    </row>
+    <row r="319" spans="2:22">
       <c r="B319" s="5"/>
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
@@ -15818,8 +17234,10 @@
       <c r="R319" s="14"/>
       <c r="S319" s="14"/>
       <c r="T319" s="14"/>
-    </row>
-    <row r="320" spans="2:20">
+      <c r="U319" s="14"/>
+      <c r="V319" s="14"/>
+    </row>
+    <row r="320" spans="2:22">
       <c r="B320" s="4"/>
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
@@ -15839,8 +17257,10 @@
       <c r="R320" s="14"/>
       <c r="S320" s="14"/>
       <c r="T320" s="14"/>
-    </row>
-    <row r="321" spans="2:20">
+      <c r="U320" s="14"/>
+      <c r="V320" s="14"/>
+    </row>
+    <row r="321" spans="2:22">
       <c r="B321" s="5"/>
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
@@ -15860,8 +17280,10 @@
       <c r="R321" s="14"/>
       <c r="S321" s="14"/>
       <c r="T321" s="14"/>
-    </row>
-    <row r="322" spans="2:20">
+      <c r="U321" s="14"/>
+      <c r="V321" s="14"/>
+    </row>
+    <row r="322" spans="2:22">
       <c r="B322" s="5"/>
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
@@ -15881,8 +17303,10 @@
       <c r="R322" s="14"/>
       <c r="S322" s="14"/>
       <c r="T322" s="14"/>
-    </row>
-    <row r="323" spans="2:20">
+      <c r="U322" s="14"/>
+      <c r="V322" s="14"/>
+    </row>
+    <row r="323" spans="2:22">
       <c r="B323" s="4"/>
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
@@ -15902,8 +17326,10 @@
       <c r="R323" s="14"/>
       <c r="S323" s="14"/>
       <c r="T323" s="14"/>
-    </row>
-    <row r="324" spans="2:20">
+      <c r="U323" s="14"/>
+      <c r="V323" s="14"/>
+    </row>
+    <row r="324" spans="2:22">
       <c r="B324" s="4"/>
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
@@ -15923,8 +17349,10 @@
       <c r="R324" s="14"/>
       <c r="S324" s="14"/>
       <c r="T324" s="14"/>
-    </row>
-    <row r="325" spans="2:20">
+      <c r="U324" s="14"/>
+      <c r="V324" s="14"/>
+    </row>
+    <row r="325" spans="2:22">
       <c r="B325" s="4"/>
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
@@ -15944,8 +17372,10 @@
       <c r="R325" s="14"/>
       <c r="S325" s="14"/>
       <c r="T325" s="14"/>
-    </row>
-    <row r="326" spans="2:20">
+      <c r="U325" s="14"/>
+      <c r="V325" s="14"/>
+    </row>
+    <row r="326" spans="2:22">
       <c r="B326" s="4"/>
       <c r="C326" s="19"/>
       <c r="D326" s="19"/>
@@ -15965,8 +17395,10 @@
       <c r="R326" s="13"/>
       <c r="S326" s="13"/>
       <c r="T326" s="13"/>
-    </row>
-    <row r="327" spans="2:20">
+      <c r="U326" s="13"/>
+      <c r="V326" s="13"/>
+    </row>
+    <row r="327" spans="2:22">
       <c r="B327" s="4"/>
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
@@ -15986,8 +17418,10 @@
       <c r="R327" s="14"/>
       <c r="S327" s="14"/>
       <c r="T327" s="14"/>
-    </row>
-    <row r="328" spans="2:20">
+      <c r="U327" s="14"/>
+      <c r="V327" s="14"/>
+    </row>
+    <row r="328" spans="2:22">
       <c r="B328" s="4"/>
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
@@ -16007,8 +17441,10 @@
       <c r="R328" s="14"/>
       <c r="S328" s="14"/>
       <c r="T328" s="14"/>
-    </row>
-    <row r="329" spans="2:20">
+      <c r="U328" s="14"/>
+      <c r="V328" s="14"/>
+    </row>
+    <row r="329" spans="2:22">
       <c r="B329" s="4"/>
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
@@ -16028,8 +17464,10 @@
       <c r="R329" s="14"/>
       <c r="S329" s="14"/>
       <c r="T329" s="14"/>
-    </row>
-    <row r="330" spans="2:20">
+      <c r="U329" s="14"/>
+      <c r="V329" s="14"/>
+    </row>
+    <row r="330" spans="2:22">
       <c r="B330" s="4"/>
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
@@ -16049,8 +17487,10 @@
       <c r="R330" s="14"/>
       <c r="S330" s="14"/>
       <c r="T330" s="14"/>
-    </row>
-    <row r="331" spans="2:20">
+      <c r="U330" s="14"/>
+      <c r="V330" s="14"/>
+    </row>
+    <row r="331" spans="2:22">
       <c r="B331" s="4"/>
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
@@ -16070,8 +17510,10 @@
       <c r="R331" s="14"/>
       <c r="S331" s="14"/>
       <c r="T331" s="14"/>
-    </row>
-    <row r="332" spans="2:20">
+      <c r="U331" s="14"/>
+      <c r="V331" s="14"/>
+    </row>
+    <row r="332" spans="2:22">
       <c r="B332" s="4"/>
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
@@ -16091,8 +17533,10 @@
       <c r="R332" s="14"/>
       <c r="S332" s="14"/>
       <c r="T332" s="14"/>
-    </row>
-    <row r="333" spans="2:20">
+      <c r="U332" s="14"/>
+      <c r="V332" s="14"/>
+    </row>
+    <row r="333" spans="2:22">
       <c r="B333" s="4"/>
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
@@ -16112,8 +17556,10 @@
       <c r="R333" s="14"/>
       <c r="S333" s="14"/>
       <c r="T333" s="14"/>
-    </row>
-    <row r="334" spans="2:20">
+      <c r="U333" s="14"/>
+      <c r="V333" s="14"/>
+    </row>
+    <row r="334" spans="2:22">
       <c r="B334" s="4"/>
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
@@ -16133,8 +17579,10 @@
       <c r="R334" s="14"/>
       <c r="S334" s="14"/>
       <c r="T334" s="14"/>
-    </row>
-    <row r="335" spans="2:20">
+      <c r="U334" s="14"/>
+      <c r="V334" s="14"/>
+    </row>
+    <row r="335" spans="2:22">
       <c r="B335" s="4"/>
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
@@ -16154,8 +17602,10 @@
       <c r="R335" s="14"/>
       <c r="S335" s="14"/>
       <c r="T335" s="14"/>
-    </row>
-    <row r="336" spans="2:20">
+      <c r="U335" s="14"/>
+      <c r="V335" s="14"/>
+    </row>
+    <row r="336" spans="2:22">
       <c r="B336" s="5"/>
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
@@ -16175,8 +17625,10 @@
       <c r="R336" s="14"/>
       <c r="S336" s="14"/>
       <c r="T336" s="14"/>
-    </row>
-    <row r="337" spans="2:20">
+      <c r="U336" s="14"/>
+      <c r="V336" s="14"/>
+    </row>
+    <row r="337" spans="2:22">
       <c r="B337" s="4"/>
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
@@ -16196,8 +17648,10 @@
       <c r="R337" s="14"/>
       <c r="S337" s="14"/>
       <c r="T337" s="14"/>
-    </row>
-    <row r="338" spans="2:20">
+      <c r="U337" s="14"/>
+      <c r="V337" s="14"/>
+    </row>
+    <row r="338" spans="2:22">
       <c r="B338" s="5"/>
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
@@ -16217,8 +17671,10 @@
       <c r="R338" s="14"/>
       <c r="S338" s="14"/>
       <c r="T338" s="14"/>
-    </row>
-    <row r="339" spans="2:20">
+      <c r="U338" s="14"/>
+      <c r="V338" s="14"/>
+    </row>
+    <row r="339" spans="2:22">
       <c r="B339" s="5"/>
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
@@ -16238,8 +17694,10 @@
       <c r="R339" s="14"/>
       <c r="S339" s="14"/>
       <c r="T339" s="14"/>
-    </row>
-    <row r="340" spans="2:20">
+      <c r="U339" s="14"/>
+      <c r="V339" s="14"/>
+    </row>
+    <row r="340" spans="2:22">
       <c r="B340" s="4"/>
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
@@ -16259,8 +17717,10 @@
       <c r="R340" s="14"/>
       <c r="S340" s="14"/>
       <c r="T340" s="14"/>
-    </row>
-    <row r="341" spans="2:20">
+      <c r="U340" s="14"/>
+      <c r="V340" s="14"/>
+    </row>
+    <row r="341" spans="2:22">
       <c r="B341" s="4"/>
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
@@ -16280,8 +17740,10 @@
       <c r="R341" s="14"/>
       <c r="S341" s="14"/>
       <c r="T341" s="14"/>
-    </row>
-    <row r="342" spans="2:20">
+      <c r="U341" s="14"/>
+      <c r="V341" s="14"/>
+    </row>
+    <row r="342" spans="2:22">
       <c r="B342" s="4"/>
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
@@ -16301,8 +17763,10 @@
       <c r="R342" s="14"/>
       <c r="S342" s="14"/>
       <c r="T342" s="14"/>
-    </row>
-    <row r="343" spans="2:20">
+      <c r="U342" s="14"/>
+      <c r="V342" s="14"/>
+    </row>
+    <row r="343" spans="2:22">
       <c r="B343" s="4"/>
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
@@ -16322,8 +17786,10 @@
       <c r="R343" s="14"/>
       <c r="S343" s="14"/>
       <c r="T343" s="14"/>
-    </row>
-    <row r="344" spans="2:20">
+      <c r="U343" s="14"/>
+      <c r="V343" s="14"/>
+    </row>
+    <row r="344" spans="2:22">
       <c r="B344" s="4"/>
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
@@ -16343,8 +17809,10 @@
       <c r="R344" s="14"/>
       <c r="S344" s="14"/>
       <c r="T344" s="14"/>
-    </row>
-    <row r="345" spans="2:20">
+      <c r="U344" s="14"/>
+      <c r="V344" s="14"/>
+    </row>
+    <row r="345" spans="2:22">
       <c r="B345" s="4"/>
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
@@ -16364,8 +17832,10 @@
       <c r="R345" s="14"/>
       <c r="S345" s="14"/>
       <c r="T345" s="14"/>
-    </row>
-    <row r="346" spans="2:20">
+      <c r="U345" s="14"/>
+      <c r="V345" s="14"/>
+    </row>
+    <row r="346" spans="2:22">
       <c r="B346" s="4"/>
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
@@ -16385,8 +17855,10 @@
       <c r="R346" s="14"/>
       <c r="S346" s="14"/>
       <c r="T346" s="14"/>
-    </row>
-    <row r="347" spans="2:20">
+      <c r="U346" s="14"/>
+      <c r="V346" s="14"/>
+    </row>
+    <row r="347" spans="2:22">
       <c r="B347" s="4"/>
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
@@ -16406,8 +17878,10 @@
       <c r="R347" s="14"/>
       <c r="S347" s="14"/>
       <c r="T347" s="14"/>
-    </row>
-    <row r="348" spans="2:20">
+      <c r="U347" s="14"/>
+      <c r="V347" s="14"/>
+    </row>
+    <row r="348" spans="2:22">
       <c r="B348" s="4"/>
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
@@ -16427,8 +17901,10 @@
       <c r="R348" s="14"/>
       <c r="S348" s="14"/>
       <c r="T348" s="14"/>
-    </row>
-    <row r="349" spans="2:20">
+      <c r="U348" s="14"/>
+      <c r="V348" s="14"/>
+    </row>
+    <row r="349" spans="2:22">
       <c r="B349" s="4"/>
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
@@ -16448,8 +17924,10 @@
       <c r="R349" s="14"/>
       <c r="S349" s="14"/>
       <c r="T349" s="14"/>
-    </row>
-    <row r="350" spans="2:20">
+      <c r="U349" s="14"/>
+      <c r="V349" s="14"/>
+    </row>
+    <row r="350" spans="2:22">
       <c r="B350" s="4"/>
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
@@ -16469,8 +17947,10 @@
       <c r="R350" s="14"/>
       <c r="S350" s="14"/>
       <c r="T350" s="14"/>
-    </row>
-    <row r="351" spans="2:20">
+      <c r="U350" s="14"/>
+      <c r="V350" s="14"/>
+    </row>
+    <row r="351" spans="2:22">
       <c r="B351" s="4"/>
       <c r="C351" s="19"/>
       <c r="D351" s="19"/>
@@ -16490,8 +17970,10 @@
       <c r="R351" s="13"/>
       <c r="S351" s="13"/>
       <c r="T351" s="13"/>
-    </row>
-    <row r="352" spans="2:20">
+      <c r="U351" s="13"/>
+      <c r="V351" s="13"/>
+    </row>
+    <row r="352" spans="2:22">
       <c r="B352" s="4" t="s">
         <v>49</v>
       </c>
@@ -16547,8 +18029,14 @@
       <c r="T352" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="353" spans="2:20">
+      <c r="U352" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V352" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="353" spans="2:22">
       <c r="B353" s="4" t="s">
         <v>50</v>
       </c>
@@ -16588,8 +18076,10 @@
       <c r="R353" s="13"/>
       <c r="S353" s="13"/>
       <c r="T353" s="13"/>
-    </row>
-    <row r="354" spans="2:20">
+      <c r="U353" s="13"/>
+      <c r="V353" s="13"/>
+    </row>
+    <row r="354" spans="2:22">
       <c r="B354" s="4" t="s">
         <v>129</v>
       </c>
@@ -16645,8 +18135,14 @@
       <c r="T354" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="355" spans="2:20">
+      <c r="U354" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V354" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="355" spans="2:22">
       <c r="B355" s="4" t="s">
         <v>130</v>
       </c>
@@ -16670,12 +18166,16 @@
       <c r="P355" s="13"/>
       <c r="Q355" s="13"/>
       <c r="R355" s="13"/>
-      <c r="S355" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="T355" s="13"/>
-    </row>
-    <row r="356" spans="2:20">
+      <c r="S355" s="13"/>
+      <c r="T355" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U355" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V355" s="13"/>
+    </row>
+    <row r="356" spans="2:22">
       <c r="B356" s="4"/>
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
@@ -16695,8 +18195,10 @@
       <c r="R356" s="13"/>
       <c r="S356" s="13"/>
       <c r="T356" s="13"/>
-    </row>
-    <row r="357" spans="2:20">
+      <c r="U356" s="13"/>
+      <c r="V356" s="13"/>
+    </row>
+    <row r="357" spans="2:22">
       <c r="B357" s="4" t="s">
         <v>131</v>
       </c>
@@ -16720,8 +18222,10 @@
       <c r="R357" s="13"/>
       <c r="S357" s="13"/>
       <c r="T357" s="13"/>
-    </row>
-    <row r="358" spans="2:20">
+      <c r="U357" s="13"/>
+      <c r="V357" s="13"/>
+    </row>
+    <row r="358" spans="2:22">
       <c r="B358" s="4" t="s">
         <v>132</v>
       </c>
@@ -16745,8 +18249,10 @@
       <c r="R358" s="13"/>
       <c r="S358" s="13"/>
       <c r="T358" s="13"/>
-    </row>
-    <row r="359" spans="2:20">
+      <c r="U358" s="13"/>
+      <c r="V358" s="13"/>
+    </row>
+    <row r="359" spans="2:22">
       <c r="B359" s="4" t="s">
         <v>133</v>
       </c>
@@ -16770,8 +18276,10 @@
       <c r="R359" s="13"/>
       <c r="S359" s="13"/>
       <c r="T359" s="13"/>
-    </row>
-    <row r="360" spans="2:20">
+      <c r="U359" s="13"/>
+      <c r="V359" s="13"/>
+    </row>
+    <row r="360" spans="2:22">
       <c r="B360" s="4" t="s">
         <v>134</v>
       </c>
@@ -16795,8 +18303,10 @@
       <c r="R360" s="13"/>
       <c r="S360" s="13"/>
       <c r="T360" s="13"/>
-    </row>
-    <row r="361" spans="2:20">
+      <c r="U360" s="13"/>
+      <c r="V360" s="13"/>
+    </row>
+    <row r="361" spans="2:22">
       <c r="B361" s="4" t="s">
         <v>135</v>
       </c>
@@ -16820,8 +18330,10 @@
       <c r="R361" s="13"/>
       <c r="S361" s="13"/>
       <c r="T361" s="13"/>
-    </row>
-    <row r="362" spans="2:20">
+      <c r="U361" s="13"/>
+      <c r="V361" s="13"/>
+    </row>
+    <row r="362" spans="2:22">
       <c r="B362" s="4"/>
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
@@ -16841,8 +18353,10 @@
       <c r="R362" s="13"/>
       <c r="S362" s="13"/>
       <c r="T362" s="13"/>
-    </row>
-    <row r="363" spans="2:20">
+      <c r="U362" s="13"/>
+      <c r="V362" s="13"/>
+    </row>
+    <row r="363" spans="2:22">
       <c r="B363" s="4" t="s">
         <v>131</v>
       </c>
@@ -16866,8 +18380,10 @@
       <c r="R363" s="13"/>
       <c r="S363" s="13"/>
       <c r="T363" s="13"/>
-    </row>
-    <row r="364" spans="2:20">
+      <c r="U363" s="13"/>
+      <c r="V363" s="13"/>
+    </row>
+    <row r="364" spans="2:22">
       <c r="B364" s="4" t="s">
         <v>132</v>
       </c>
@@ -16891,8 +18407,10 @@
       <c r="R364" s="13"/>
       <c r="S364" s="13"/>
       <c r="T364" s="13"/>
-    </row>
-    <row r="365" spans="2:20">
+      <c r="U364" s="13"/>
+      <c r="V364" s="13"/>
+    </row>
+    <row r="365" spans="2:22">
       <c r="B365" s="4" t="s">
         <v>133</v>
       </c>
@@ -16916,8 +18434,10 @@
       <c r="R365" s="13"/>
       <c r="S365" s="13"/>
       <c r="T365" s="13"/>
-    </row>
-    <row r="366" spans="2:20">
+      <c r="U365" s="13"/>
+      <c r="V365" s="13"/>
+    </row>
+    <row r="366" spans="2:22">
       <c r="B366" s="4" t="s">
         <v>134</v>
       </c>
@@ -16941,8 +18461,10 @@
       <c r="R366" s="13"/>
       <c r="S366" s="13"/>
       <c r="T366" s="13"/>
-    </row>
-    <row r="367" spans="2:20">
+      <c r="U366" s="13"/>
+      <c r="V366" s="13"/>
+    </row>
+    <row r="367" spans="2:22">
       <c r="B367" s="4" t="s">
         <v>135</v>
       </c>
@@ -16966,8 +18488,10 @@
       <c r="R367" s="13"/>
       <c r="S367" s="13"/>
       <c r="T367" s="13"/>
-    </row>
-    <row r="368" spans="2:20">
+      <c r="U367" s="13"/>
+      <c r="V367" s="13"/>
+    </row>
+    <row r="368" spans="2:22">
       <c r="B368" s="4"/>
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
@@ -16987,8 +18511,10 @@
       <c r="R368" s="13"/>
       <c r="S368" s="13"/>
       <c r="T368" s="13"/>
-    </row>
-    <row r="369" spans="2:20">
+      <c r="U368" s="13"/>
+      <c r="V368" s="13"/>
+    </row>
+    <row r="369" spans="2:22">
       <c r="B369" s="4" t="s">
         <v>136</v>
       </c>
@@ -17014,8 +18540,10 @@
       <c r="R369" s="13"/>
       <c r="S369" s="13"/>
       <c r="T369" s="13"/>
-    </row>
-    <row r="370" spans="2:20">
+      <c r="U369" s="13"/>
+      <c r="V369" s="13"/>
+    </row>
+    <row r="370" spans="2:22">
       <c r="B370" s="4" t="s">
         <v>137</v>
       </c>
@@ -17041,8 +18569,10 @@
       <c r="R370" s="13"/>
       <c r="S370" s="13"/>
       <c r="T370" s="13"/>
-    </row>
-    <row r="371" spans="2:20">
+      <c r="U370" s="13"/>
+      <c r="V370" s="13"/>
+    </row>
+    <row r="371" spans="2:22">
       <c r="B371" s="4" t="s">
         <v>138</v>
       </c>
@@ -17068,8 +18598,10 @@
       <c r="R371" s="13"/>
       <c r="S371" s="13"/>
       <c r="T371" s="13"/>
-    </row>
-    <row r="372" spans="2:20">
+      <c r="U371" s="13"/>
+      <c r="V371" s="13"/>
+    </row>
+    <row r="372" spans="2:22">
       <c r="B372" s="4"/>
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
@@ -17089,8 +18621,10 @@
       <c r="R372" s="13"/>
       <c r="S372" s="13"/>
       <c r="T372" s="13"/>
-    </row>
-    <row r="373" spans="2:20">
+      <c r="U372" s="13"/>
+      <c r="V372" s="13"/>
+    </row>
+    <row r="373" spans="2:22">
       <c r="B373" s="4" t="s">
         <v>136</v>
       </c>
@@ -17116,8 +18650,10 @@
       <c r="R373" s="13"/>
       <c r="S373" s="13"/>
       <c r="T373" s="13"/>
-    </row>
-    <row r="374" spans="2:20">
+      <c r="U373" s="13"/>
+      <c r="V373" s="13"/>
+    </row>
+    <row r="374" spans="2:22">
       <c r="B374" s="4" t="s">
         <v>137</v>
       </c>
@@ -17143,8 +18679,10 @@
       <c r="R374" s="13"/>
       <c r="S374" s="13"/>
       <c r="T374" s="13"/>
-    </row>
-    <row r="375" spans="2:20">
+      <c r="U374" s="13"/>
+      <c r="V374" s="13"/>
+    </row>
+    <row r="375" spans="2:22">
       <c r="B375" s="4" t="s">
         <v>138</v>
       </c>
@@ -17170,8 +18708,10 @@
       <c r="R375" s="13"/>
       <c r="S375" s="13"/>
       <c r="T375" s="13"/>
-    </row>
-    <row r="376" spans="2:20">
+      <c r="U375" s="13"/>
+      <c r="V375" s="13"/>
+    </row>
+    <row r="376" spans="2:22">
       <c r="B376" s="4"/>
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
@@ -17191,8 +18731,10 @@
       <c r="R376" s="13"/>
       <c r="S376" s="13"/>
       <c r="T376" s="13"/>
-    </row>
-    <row r="377" spans="2:20">
+      <c r="U376" s="13"/>
+      <c r="V376" s="13"/>
+    </row>
+    <row r="377" spans="2:22">
       <c r="B377" s="4"/>
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
@@ -17212,8 +18754,10 @@
       <c r="R377" s="13"/>
       <c r="S377" s="13"/>
       <c r="T377" s="13"/>
-    </row>
-    <row r="378" spans="2:20">
+      <c r="U377" s="13"/>
+      <c r="V377" s="13"/>
+    </row>
+    <row r="378" spans="2:22">
       <c r="B378" s="4"/>
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
@@ -17233,8 +18777,10 @@
       <c r="R378" s="13"/>
       <c r="S378" s="13"/>
       <c r="T378" s="13"/>
-    </row>
-    <row r="379" spans="2:20">
+      <c r="U378" s="13"/>
+      <c r="V378" s="13"/>
+    </row>
+    <row r="379" spans="2:22">
       <c r="B379" s="4"/>
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
@@ -17254,8 +18800,10 @@
       <c r="R379" s="13"/>
       <c r="S379" s="13"/>
       <c r="T379" s="13"/>
-    </row>
-    <row r="380" spans="2:20">
+      <c r="U379" s="13"/>
+      <c r="V379" s="13"/>
+    </row>
+    <row r="380" spans="2:22">
       <c r="B380" s="4"/>
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
@@ -17275,8 +18823,10 @@
       <c r="R380" s="13"/>
       <c r="S380" s="13"/>
       <c r="T380" s="13"/>
-    </row>
-    <row r="381" spans="2:20">
+      <c r="U380" s="13"/>
+      <c r="V380" s="13"/>
+    </row>
+    <row r="381" spans="2:22">
       <c r="B381" s="4"/>
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
@@ -17296,8 +18846,10 @@
       <c r="R381" s="13"/>
       <c r="S381" s="13"/>
       <c r="T381" s="13"/>
-    </row>
-    <row r="382" spans="2:20">
+      <c r="U381" s="13"/>
+      <c r="V381" s="13"/>
+    </row>
+    <row r="382" spans="2:22">
       <c r="B382" s="4"/>
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
@@ -17317,8 +18869,10 @@
       <c r="R382" s="13"/>
       <c r="S382" s="13"/>
       <c r="T382" s="13"/>
-    </row>
-    <row r="383" spans="2:20">
+      <c r="U382" s="13"/>
+      <c r="V382" s="13"/>
+    </row>
+    <row r="383" spans="2:22">
       <c r="B383" s="4"/>
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
@@ -17338,8 +18892,10 @@
       <c r="R383" s="13"/>
       <c r="S383" s="13"/>
       <c r="T383" s="13"/>
-    </row>
-    <row r="384" spans="2:20">
+      <c r="U383" s="13"/>
+      <c r="V383" s="13"/>
+    </row>
+    <row r="384" spans="2:22">
       <c r="B384" s="4"/>
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
@@ -17359,8 +18915,10 @@
       <c r="R384" s="13"/>
       <c r="S384" s="13"/>
       <c r="T384" s="13"/>
-    </row>
-    <row r="385" spans="2:20">
+      <c r="U384" s="13"/>
+      <c r="V384" s="13"/>
+    </row>
+    <row r="385" spans="2:22">
       <c r="B385" s="4"/>
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
@@ -17380,8 +18938,10 @@
       <c r="R385" s="13"/>
       <c r="S385" s="13"/>
       <c r="T385" s="13"/>
-    </row>
-    <row r="386" spans="2:20">
+      <c r="U385" s="13"/>
+      <c r="V385" s="13"/>
+    </row>
+    <row r="386" spans="2:22">
       <c r="B386" s="4"/>
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
@@ -17401,8 +18961,10 @@
       <c r="R386" s="13"/>
       <c r="S386" s="13"/>
       <c r="T386" s="13"/>
-    </row>
-    <row r="387" spans="2:20">
+      <c r="U386" s="13"/>
+      <c r="V386" s="13"/>
+    </row>
+    <row r="387" spans="2:22">
       <c r="B387" s="4"/>
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
@@ -17422,8 +18984,10 @@
       <c r="R387" s="13"/>
       <c r="S387" s="13"/>
       <c r="T387" s="13"/>
-    </row>
-    <row r="388" spans="2:20">
+      <c r="U387" s="13"/>
+      <c r="V387" s="13"/>
+    </row>
+    <row r="388" spans="2:22">
       <c r="B388" s="4"/>
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
@@ -17443,8 +19007,10 @@
       <c r="R388" s="13"/>
       <c r="S388" s="13"/>
       <c r="T388" s="13"/>
-    </row>
-    <row r="389" spans="2:20">
+      <c r="U388" s="13"/>
+      <c r="V388" s="13"/>
+    </row>
+    <row r="389" spans="2:22">
       <c r="B389" s="4"/>
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
@@ -17464,8 +19030,10 @@
       <c r="R389" s="13"/>
       <c r="S389" s="13"/>
       <c r="T389" s="13"/>
-    </row>
-    <row r="390" spans="2:20">
+      <c r="U389" s="13"/>
+      <c r="V389" s="13"/>
+    </row>
+    <row r="390" spans="2:22">
       <c r="B390" s="4"/>
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
@@ -17485,8 +19053,10 @@
       <c r="R390" s="13"/>
       <c r="S390" s="13"/>
       <c r="T390" s="13"/>
-    </row>
-    <row r="391" spans="2:20">
+      <c r="U390" s="13"/>
+      <c r="V390" s="13"/>
+    </row>
+    <row r="391" spans="2:22">
       <c r="B391" s="4"/>
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
@@ -17506,8 +19076,10 @@
       <c r="R391" s="13"/>
       <c r="S391" s="13"/>
       <c r="T391" s="13"/>
-    </row>
-    <row r="392" spans="2:20">
+      <c r="U391" s="13"/>
+      <c r="V391" s="13"/>
+    </row>
+    <row r="392" spans="2:22">
       <c r="B392" s="4"/>
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
@@ -17527,8 +19099,10 @@
       <c r="R392" s="13"/>
       <c r="S392" s="13"/>
       <c r="T392" s="13"/>
-    </row>
-    <row r="393" spans="2:20">
+      <c r="U392" s="13"/>
+      <c r="V392" s="13"/>
+    </row>
+    <row r="393" spans="2:22">
       <c r="B393" s="4"/>
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
@@ -17548,8 +19122,10 @@
       <c r="R393" s="13"/>
       <c r="S393" s="13"/>
       <c r="T393" s="13"/>
-    </row>
-    <row r="394" spans="2:20">
+      <c r="U393" s="13"/>
+      <c r="V393" s="13"/>
+    </row>
+    <row r="394" spans="2:22">
       <c r="B394" s="4"/>
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
@@ -17569,8 +19145,10 @@
       <c r="R394" s="13"/>
       <c r="S394" s="13"/>
       <c r="T394" s="13"/>
-    </row>
-    <row r="395" spans="2:20">
+      <c r="U394" s="13"/>
+      <c r="V394" s="13"/>
+    </row>
+    <row r="395" spans="2:22">
       <c r="B395" s="4"/>
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
@@ -17590,8 +19168,10 @@
       <c r="R395" s="13"/>
       <c r="S395" s="13"/>
       <c r="T395" s="13"/>
-    </row>
-    <row r="396" spans="2:20">
+      <c r="U395" s="13"/>
+      <c r="V395" s="13"/>
+    </row>
+    <row r="396" spans="2:22">
       <c r="B396" s="4"/>
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
@@ -17611,8 +19191,10 @@
       <c r="R396" s="13"/>
       <c r="S396" s="13"/>
       <c r="T396" s="13"/>
-    </row>
-    <row r="397" spans="2:20">
+      <c r="U396" s="13"/>
+      <c r="V396" s="13"/>
+    </row>
+    <row r="397" spans="2:22">
       <c r="B397" s="9"/>
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
@@ -17632,8 +19214,10 @@
       <c r="R397" s="13"/>
       <c r="S397" s="13"/>
       <c r="T397" s="13"/>
-    </row>
-    <row r="398" spans="2:20">
+      <c r="U397" s="13"/>
+      <c r="V397" s="13"/>
+    </row>
+    <row r="398" spans="2:22">
       <c r="B398" s="9"/>
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
@@ -17653,8 +19237,10 @@
       <c r="R398" s="13"/>
       <c r="S398" s="13"/>
       <c r="T398" s="13"/>
-    </row>
-    <row r="399" spans="2:20">
+      <c r="U398" s="13"/>
+      <c r="V398" s="13"/>
+    </row>
+    <row r="399" spans="2:22">
       <c r="B399" s="9"/>
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
@@ -17674,8 +19260,10 @@
       <c r="R399" s="13"/>
       <c r="S399" s="13"/>
       <c r="T399" s="13"/>
-    </row>
-    <row r="400" spans="2:20">
+      <c r="U399" s="13"/>
+      <c r="V399" s="13"/>
+    </row>
+    <row r="400" spans="2:22">
       <c r="B400" s="9"/>
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
@@ -17695,8 +19283,10 @@
       <c r="R400" s="13"/>
       <c r="S400" s="13"/>
       <c r="T400" s="13"/>
-    </row>
-    <row r="401" spans="2:20">
+      <c r="U400" s="13"/>
+      <c r="V400" s="13"/>
+    </row>
+    <row r="401" spans="2:22">
       <c r="B401" s="4"/>
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
@@ -17716,13 +19306,16 @@
       <c r="R401" s="13"/>
       <c r="S401" s="13"/>
       <c r="T401" s="13"/>
+      <c r="U401" s="13"/>
+      <c r="V401" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="E2:K401" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Arial"&amp;8&amp;K737373 Classified by Alfa Laval as: Business</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/testLBB.xlsx
+++ b/testLBB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SETUMHNE\Downloads\myLearning\gitPlayGround\PlayGround\TestDB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Agentic World\TestDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BC3075-9EB6-47A2-9FD5-D283D546DD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF99A034-B823-44A1-A719-A31EABF5B0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,27 +62,51 @@
   <commentList>
     <comment ref="E24" authorId="0" shapeId="0" xr:uid="{C9784531-5C6D-44EC-AB65-162B1CE3680D}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    True</t>
+    False</t>
+        </r>
       </text>
     </comment>
     <comment ref="E30" authorId="1" shapeId="0" xr:uid="{71BB7FBC-F32F-4C72-9332-1C81A6EC2304}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    False</t>
+    True</t>
+        </r>
       </text>
     </comment>
     <comment ref="B110" authorId="2" shapeId="0" xr:uid="{73D4B7F6-243F-4FF2-99C8-413E3B588F2F}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PIT220-1 / PIT221-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="F110" authorId="3" shapeId="0" xr:uid="{ACEAC60E-563F-4328-B54F-2D31DA895568}">
@@ -311,11 +335,19 @@
     </comment>
     <comment ref="B116" authorId="4" shapeId="0" xr:uid="{4608516B-34DA-4E87-85F1-345F80F368D2}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PIT221-1 / PIT220-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="S116" authorId="3" shapeId="0" xr:uid="{32126A50-CE7D-4FF2-ADF3-AC79E3BFC8D7}">
@@ -376,11 +408,19 @@
     </comment>
     <comment ref="B130" authorId="5" shapeId="0" xr:uid="{37D13463-1186-4BC6-8059-F81F589B8465}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PCV220-1 / PCV221-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="F130" authorId="3" shapeId="0" xr:uid="{A163B90D-1EF5-443F-899F-87AE8DB0F188}">
@@ -609,11 +649,19 @@
     </comment>
     <comment ref="B132" authorId="6" shapeId="0" xr:uid="{330CC50C-0FF1-4C20-92A7-B1A460F72FE0}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PCV221-1 / PCV220-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="S132" authorId="3" shapeId="0" xr:uid="{22150A06-9848-4929-8ED5-23E9E8AE01F0}">
@@ -674,11 +722,19 @@
     </comment>
     <comment ref="B139" authorId="7" shapeId="0" xr:uid="{C128BBFA-0A9E-4E10-9DCF-02753B677457}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 ST740/ST741</t>
+        </r>
       </text>
     </comment>
     <comment ref="F139" authorId="3" shapeId="0" xr:uid="{71DF5CC9-8C1C-486E-B5BB-3BCC7CA84727}">
@@ -935,11 +991,19 @@
     </comment>
     <comment ref="B187" authorId="8" shapeId="0" xr:uid="{FAC71602-7205-4D4E-A8A7-63E13947D7F3}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 LS422b / LS423</t>
+        </r>
       </text>
     </comment>
     <comment ref="J187" authorId="3" shapeId="0" xr:uid="{7BE8016D-9A39-41FB-B16C-9D5E1B3F75EA}">
@@ -986,11 +1050,19 @@
     </comment>
     <comment ref="B212" authorId="9" shapeId="0" xr:uid="{4A8C6723-E87B-4DCF-BC82-3EEAFFA13634}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 YT750/YT752</t>
+        </r>
       </text>
     </comment>
     <comment ref="F212" authorId="3" shapeId="0" xr:uid="{7A748396-5D90-45A2-BCDA-09E9D00EB824}">
@@ -1247,11 +1319,19 @@
     </comment>
     <comment ref="B214" authorId="10" shapeId="0" xr:uid="{932F2D4C-D793-48A0-8BED-5F38FC3D7DAF}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 PT375-1/PT376-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="G214" authorId="3" shapeId="0" xr:uid="{A7A9E8D1-727E-4B93-BDEB-E67DFF623450}">
@@ -1494,36 +1574,68 @@
     </comment>
     <comment ref="B218" authorId="11" shapeId="0" xr:uid="{E1E2F944-CF9F-4061-9330-99AC06440908}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative sensors, same PIW:
 TT731b/TT733</t>
+        </r>
       </text>
     </comment>
     <comment ref="G218" authorId="12" shapeId="0" xr:uid="{F8073023-E3D6-437F-A368-4B60DA804058}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Sensor: TT733</t>
+        </r>
       </text>
     </comment>
     <comment ref="L218" authorId="13" shapeId="0" xr:uid="{ED46C518-7286-47D1-963D-3F59595A0F45}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Sensor: TT731b</t>
+        </r>
       </text>
     </comment>
     <comment ref="B223" authorId="14" shapeId="0" xr:uid="{FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 TT410-1/TT412-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="F223" authorId="3" shapeId="0" xr:uid="{3F0AF3B0-2ABB-45F3-8CF9-4442E029B36F}">
@@ -1780,19 +1892,35 @@
     </comment>
     <comment ref="B243" authorId="15" shapeId="0" xr:uid="{C29E9803-A59F-4197-99DC-10131D1A8691}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Old AV635b-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="B248" authorId="16" shapeId="0" xr:uid="{F05B5C03-D80C-44EE-911F-FD4F08369CD1}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 AV375-1/AV376-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="F248" authorId="3" shapeId="0" xr:uid="{7EF7BC57-4FCC-448F-8A09-38CD88A5340F}">
@@ -2063,11 +2191,19 @@
     </comment>
     <comment ref="B252" authorId="17" shapeId="0" xr:uid="{6BE60107-F28C-41F1-A623-84DD5A6A045C}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 AV441-1/AV630-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="M252" authorId="3" shapeId="0" xr:uid="{6F128C66-A3BA-4965-B079-6A928BE29365}">
@@ -2086,11 +2222,19 @@
     </comment>
     <comment ref="B253" authorId="18" shapeId="0" xr:uid="{573F35F3-86C4-417F-BDB5-9F88836E09BB}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 506c/AV372-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="F253" authorId="3" shapeId="0" xr:uid="{68836ADC-7909-428F-90A1-5710219BA6C4}">
@@ -3530,7 +3674,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3577,12 +3721,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -4257,23 +4395,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}">
   <dimension ref="B1:W401"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="31.25" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.75" style="10" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="2.25" style="10" customWidth="1"/>
-    <col min="8" max="9" width="2.83203125" style="10" customWidth="1"/>
+    <col min="8" max="9" width="2.875" style="10" customWidth="1"/>
     <col min="10" max="12" width="6.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="2.58203125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="2.83203125" style="10" customWidth="1"/>
-    <col min="17" max="17" width="2.58203125" style="10" customWidth="1"/>
-    <col min="18" max="22" width="2.83203125" style="10" customWidth="1"/>
-    <col min="23" max="23" width="2.58203125" style="10" customWidth="1"/>
+    <col min="13" max="15" width="2.625" style="10" customWidth="1"/>
+    <col min="16" max="16" width="2.875" style="10" customWidth="1"/>
+    <col min="17" max="17" width="2.625" style="10" customWidth="1"/>
+    <col min="18" max="22" width="2.875" style="10" customWidth="1"/>
+    <col min="23" max="23" width="2.625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:23" ht="35.25" customHeight="1">
       <c r="D1" s="1" t="s">
         <v>285</v>
       </c>
@@ -4332,7 +4470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:23" ht="57" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:23" ht="58.5">
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
@@ -4392,7 +4530,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:23">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -4424,7 +4562,7 @@
       <c r="V3" s="12"/>
       <c r="W3" s="12"/>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:23">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -4448,7 +4586,7 @@
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
     </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:23">
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -4472,7 +4610,7 @@
       <c r="V5" s="14"/>
       <c r="W5" s="14"/>
     </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:23">
       <c r="B6" s="4"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -4496,7 +4634,7 @@
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
     </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:23">
       <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
@@ -4560,7 +4698,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:23">
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
@@ -4620,7 +4758,7 @@
       </c>
       <c r="W8" s="13"/>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:23">
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
@@ -4680,7 +4818,7 @@
       </c>
       <c r="W9" s="13"/>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:23">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -4718,7 +4856,7 @@
       </c>
       <c r="W10" s="13"/>
     </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:23">
       <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
@@ -4782,7 +4920,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:23">
       <c r="B12" s="4" t="s">
         <v>6</v>
       </c>
@@ -4846,7 +4984,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:23">
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
@@ -4910,7 +5048,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:23">
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
@@ -4938,7 +5076,7 @@
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:23">
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
@@ -4966,7 +5104,7 @@
       <c r="V15" s="13"/>
       <c r="W15" s="13"/>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:23">
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
@@ -5020,7 +5158,7 @@
       <c r="V16" s="13"/>
       <c r="W16" s="13"/>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:23">
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
@@ -5078,7 +5216,7 @@
       </c>
       <c r="W17" s="13"/>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:23">
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
@@ -5122,7 +5260,7 @@
       <c r="V18" s="13"/>
       <c r="W18" s="13"/>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:23">
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
@@ -5150,7 +5288,7 @@
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:23">
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
@@ -5178,7 +5316,7 @@
       <c r="V20" s="13"/>
       <c r="W20" s="13"/>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:23">
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
@@ -5206,7 +5344,7 @@
       <c r="V21" s="13"/>
       <c r="W21" s="13"/>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:23">
       <c r="B22" s="4" t="s">
         <v>12</v>
       </c>
@@ -5272,7 +5410,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:23">
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -5296,7 +5434,7 @@
       <c r="V23" s="13"/>
       <c r="W23" s="13"/>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:23">
       <c r="B24" s="6" t="s">
         <v>13</v>
       </c>
@@ -5362,7 +5500,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:23">
       <c r="B25" s="6" t="s">
         <v>13</v>
       </c>
@@ -5428,7 +5566,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:23">
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
@@ -5474,7 +5612,7 @@
       <c r="V26" s="13"/>
       <c r="W26" s="13"/>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:23">
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
@@ -5520,7 +5658,7 @@
       <c r="V27" s="13"/>
       <c r="W27" s="13"/>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:23">
       <c r="B28" s="6" t="s">
         <v>15</v>
       </c>
@@ -5566,7 +5704,7 @@
       <c r="V28" s="13"/>
       <c r="W28" s="13"/>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:23">
       <c r="B29" s="6" t="s">
         <v>15</v>
       </c>
@@ -5612,7 +5750,7 @@
       <c r="V29" s="13"/>
       <c r="W29" s="13"/>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:23">
       <c r="B30" s="6" t="s">
         <v>16</v>
       </c>
@@ -5656,7 +5794,7 @@
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:23">
       <c r="B31" s="6" t="s">
         <v>16</v>
       </c>
@@ -5700,7 +5838,7 @@
       <c r="V31" s="13"/>
       <c r="W31" s="13"/>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:23">
       <c r="B32" s="6" t="s">
         <v>17</v>
       </c>
@@ -5762,7 +5900,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:23">
       <c r="B33" s="6" t="s">
         <v>17</v>
       </c>
@@ -5824,7 +5962,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:23">
       <c r="B34" s="6" t="s">
         <v>18</v>
       </c>
@@ -5864,7 +6002,7 @@
       </c>
       <c r="W34" s="13"/>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:23">
       <c r="B35" s="6" t="s">
         <v>18</v>
       </c>
@@ -5904,7 +6042,7 @@
       </c>
       <c r="W35" s="13"/>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:23">
       <c r="B36" s="6" t="s">
         <v>19</v>
       </c>
@@ -5948,7 +6086,7 @@
       <c r="V36" s="13"/>
       <c r="W36" s="13"/>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:23">
       <c r="B37" s="7" t="s">
         <v>19</v>
       </c>
@@ -5992,7 +6130,7 @@
       <c r="V37" s="15"/>
       <c r="W37" s="15"/>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:23">
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
@@ -6020,7 +6158,7 @@
       <c r="V38" s="13"/>
       <c r="W38" s="13"/>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:23">
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
@@ -6048,7 +6186,7 @@
       <c r="V39" s="13"/>
       <c r="W39" s="13"/>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:23">
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -6072,7 +6210,7 @@
       <c r="V40" s="13"/>
       <c r="W40" s="13"/>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:23">
       <c r="B41" s="7" t="s">
         <v>20</v>
       </c>
@@ -6138,7 +6276,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:23">
       <c r="B42" s="6" t="s">
         <v>20</v>
       </c>
@@ -6204,7 +6342,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:23">
       <c r="B43" s="6" t="s">
         <v>21</v>
       </c>
@@ -6270,7 +6408,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:23">
       <c r="B44" s="6" t="s">
         <v>21</v>
       </c>
@@ -6336,7 +6474,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:23">
       <c r="B45" s="6" t="s">
         <v>22</v>
       </c>
@@ -6402,7 +6540,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:23">
       <c r="B46" s="6" t="s">
         <v>22</v>
       </c>
@@ -6468,7 +6606,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:23">
       <c r="B47" s="6" t="s">
         <v>23</v>
       </c>
@@ -6526,7 +6664,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:23">
       <c r="B48" s="6" t="s">
         <v>23</v>
       </c>
@@ -6584,7 +6722,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:23">
       <c r="B49" s="6" t="s">
         <v>24</v>
       </c>
@@ -6646,7 +6784,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:23">
       <c r="B50" s="6" t="s">
         <v>24</v>
       </c>
@@ -6708,7 +6846,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:23">
       <c r="B51" s="6" t="s">
         <v>25</v>
       </c>
@@ -6766,7 +6904,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:23">
       <c r="B52" s="6" t="s">
         <v>25</v>
       </c>
@@ -6824,7 +6962,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:23">
       <c r="B53" s="6" t="s">
         <v>26</v>
       </c>
@@ -6866,7 +7004,7 @@
       <c r="V53" s="13"/>
       <c r="W53" s="13"/>
     </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:23">
       <c r="B54" s="6" t="s">
         <v>26</v>
       </c>
@@ -6908,7 +7046,7 @@
       <c r="V54" s="13"/>
       <c r="W54" s="13"/>
     </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:23">
       <c r="B55" s="5" t="s">
         <v>8</v>
       </c>
@@ -6936,7 +7074,7 @@
       <c r="V55" s="13"/>
       <c r="W55" s="13"/>
     </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:23">
       <c r="B56" s="5" t="s">
         <v>8</v>
       </c>
@@ -6964,7 +7102,7 @@
       <c r="V56" s="13"/>
       <c r="W56" s="13"/>
     </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:23">
       <c r="B57" s="6"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -6988,7 +7126,7 @@
       <c r="V57" s="13"/>
       <c r="W57" s="13"/>
     </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:23">
       <c r="B58" s="6" t="s">
         <v>27</v>
       </c>
@@ -7032,7 +7170,7 @@
       <c r="V58" s="13"/>
       <c r="W58" s="13"/>
     </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:23">
       <c r="B59" s="6" t="s">
         <v>27</v>
       </c>
@@ -7076,7 +7214,7 @@
       <c r="V59" s="13"/>
       <c r="W59" s="13"/>
     </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:23">
       <c r="B60" s="5" t="s">
         <v>8</v>
       </c>
@@ -7104,7 +7242,7 @@
       <c r="V60" s="13"/>
       <c r="W60" s="13"/>
     </row>
-    <row r="61" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:23">
       <c r="B61" s="5" t="s">
         <v>8</v>
       </c>
@@ -7132,7 +7270,7 @@
       <c r="V61" s="13"/>
       <c r="W61" s="13"/>
     </row>
-    <row r="62" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:23">
       <c r="B62" s="6" t="s">
         <v>28</v>
       </c>
@@ -7190,7 +7328,7 @@
       </c>
       <c r="W62" s="13"/>
     </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:23">
       <c r="B63" s="6" t="s">
         <v>28</v>
       </c>
@@ -7248,7 +7386,7 @@
       </c>
       <c r="W63" s="13"/>
     </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:23">
       <c r="B64" s="6" t="s">
         <v>29</v>
       </c>
@@ -7306,7 +7444,7 @@
       </c>
       <c r="W64" s="13"/>
     </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:23">
       <c r="B65" s="6" t="s">
         <v>29</v>
       </c>
@@ -7364,7 +7502,7 @@
       </c>
       <c r="W65" s="13"/>
     </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:23">
       <c r="B66" s="6" t="s">
         <v>30</v>
       </c>
@@ -7404,7 +7542,7 @@
       </c>
       <c r="W66" s="13"/>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:23">
       <c r="B67" s="6" t="s">
         <v>30</v>
       </c>
@@ -7444,7 +7582,7 @@
       </c>
       <c r="W67" s="13"/>
     </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:23">
       <c r="B68" s="5" t="s">
         <v>8</v>
       </c>
@@ -7472,7 +7610,7 @@
       <c r="V68" s="13"/>
       <c r="W68" s="13"/>
     </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:23">
       <c r="B69" s="5" t="s">
         <v>8</v>
       </c>
@@ -7500,7 +7638,7 @@
       <c r="V69" s="13"/>
       <c r="W69" s="13"/>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:23">
       <c r="B70" s="5" t="s">
         <v>8</v>
       </c>
@@ -7528,7 +7666,7 @@
       <c r="V70" s="13"/>
       <c r="W70" s="13"/>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:23">
       <c r="B71" s="5" t="s">
         <v>8</v>
       </c>
@@ -7556,7 +7694,7 @@
       <c r="V71" s="13"/>
       <c r="W71" s="13"/>
     </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:23">
       <c r="B72" s="5" t="s">
         <v>8</v>
       </c>
@@ -7584,7 +7722,7 @@
       <c r="V72" s="13"/>
       <c r="W72" s="13"/>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:23">
       <c r="B73" s="5" t="s">
         <v>8</v>
       </c>
@@ -7612,7 +7750,7 @@
       <c r="V73" s="13"/>
       <c r="W73" s="13"/>
     </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:23">
       <c r="B74" s="6"/>
       <c r="C74" s="3"/>
       <c r="D74" s="20"/>
@@ -7636,7 +7774,7 @@
       <c r="V74" s="13"/>
       <c r="W74" s="13"/>
     </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:23">
       <c r="B75" s="6" t="s">
         <v>13</v>
       </c>
@@ -7702,7 +7840,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:23">
       <c r="B76" s="6" t="s">
         <v>14</v>
       </c>
@@ -7748,7 +7886,7 @@
       <c r="V76" s="13"/>
       <c r="W76" s="13"/>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:23">
       <c r="B77" s="6" t="s">
         <v>15</v>
       </c>
@@ -7794,7 +7932,7 @@
       <c r="V77" s="13"/>
       <c r="W77" s="13"/>
     </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:23">
       <c r="B78" s="6" t="s">
         <v>16</v>
       </c>
@@ -7838,7 +7976,7 @@
       <c r="V78" s="13"/>
       <c r="W78" s="13"/>
     </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:23">
       <c r="B79" s="6" t="s">
         <v>17</v>
       </c>
@@ -7900,7 +8038,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:23">
       <c r="B80" s="6" t="s">
         <v>18</v>
       </c>
@@ -7940,7 +8078,7 @@
       </c>
       <c r="W80" s="13"/>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:23">
       <c r="B81" s="6" t="s">
         <v>19</v>
       </c>
@@ -7984,7 +8122,7 @@
       <c r="V81" s="13"/>
       <c r="W81" s="13"/>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:23">
       <c r="B82" s="5" t="s">
         <v>8</v>
       </c>
@@ -8012,7 +8150,7 @@
       <c r="V82" s="13"/>
       <c r="W82" s="13"/>
     </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:23">
       <c r="B83" s="6" t="s">
         <v>20</v>
       </c>
@@ -8078,7 +8216,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:23">
       <c r="B84" s="6" t="s">
         <v>21</v>
       </c>
@@ -8144,7 +8282,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:23">
       <c r="B85" s="6" t="s">
         <v>22</v>
       </c>
@@ -8210,7 +8348,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:23">
       <c r="B86" s="6" t="s">
         <v>23</v>
       </c>
@@ -8268,7 +8406,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:23">
       <c r="B87" s="6" t="s">
         <v>24</v>
       </c>
@@ -8330,7 +8468,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:23">
       <c r="B88" s="6" t="s">
         <v>25</v>
       </c>
@@ -8388,7 +8526,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:23">
       <c r="B89" s="6" t="s">
         <v>26</v>
       </c>
@@ -8430,7 +8568,7 @@
       <c r="V89" s="13"/>
       <c r="W89" s="13"/>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:23">
       <c r="B90" s="5" t="s">
         <v>8</v>
       </c>
@@ -8458,7 +8596,7 @@
       <c r="V90" s="13"/>
       <c r="W90" s="13"/>
     </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:23">
       <c r="B91" s="6"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
@@ -8482,7 +8620,7 @@
       <c r="V91" s="13"/>
       <c r="W91" s="13"/>
     </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:23">
       <c r="B92" s="6" t="s">
         <v>27</v>
       </c>
@@ -8526,7 +8664,7 @@
       <c r="V92" s="13"/>
       <c r="W92" s="13"/>
     </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:23">
       <c r="B93" s="5" t="s">
         <v>8</v>
       </c>
@@ -8556,7 +8694,7 @@
       <c r="V93" s="13"/>
       <c r="W93" s="13"/>
     </row>
-    <row r="94" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:23">
       <c r="B94" s="6" t="s">
         <v>28</v>
       </c>
@@ -8614,7 +8752,7 @@
       </c>
       <c r="W94" s="13"/>
     </row>
-    <row r="95" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:23">
       <c r="B95" s="6" t="s">
         <v>29</v>
       </c>
@@ -8672,7 +8810,7 @@
       </c>
       <c r="W95" s="13"/>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:23">
       <c r="B96" s="6" t="s">
         <v>30</v>
       </c>
@@ -8712,7 +8850,7 @@
       </c>
       <c r="W96" s="13"/>
     </row>
-    <row r="97" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:23">
       <c r="B97" s="5" t="s">
         <v>8</v>
       </c>
@@ -8740,7 +8878,7 @@
       <c r="V97" s="13"/>
       <c r="W97" s="13"/>
     </row>
-    <row r="98" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:23">
       <c r="B98" s="5" t="s">
         <v>8</v>
       </c>
@@ -8768,7 +8906,7 @@
       <c r="V98" s="13"/>
       <c r="W98" s="13"/>
     </row>
-    <row r="99" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:23">
       <c r="B99" s="5" t="s">
         <v>8</v>
       </c>
@@ -8796,7 +8934,7 @@
       <c r="V99" s="13"/>
       <c r="W99" s="13"/>
     </row>
-    <row r="100" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:23">
       <c r="B100" s="5" t="s">
         <v>8</v>
       </c>
@@ -8824,7 +8962,7 @@
       <c r="V100" s="13"/>
       <c r="W100" s="13"/>
     </row>
-    <row r="101" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:23">
       <c r="B101" s="4" t="s">
         <v>31</v>
       </c>
@@ -8866,7 +9004,7 @@
       <c r="V101" s="13"/>
       <c r="W101" s="13"/>
     </row>
-    <row r="102" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:23">
       <c r="B102" s="8" t="s">
         <v>32</v>
       </c>
@@ -8930,7 +9068,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="103" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:23">
       <c r="B103" s="4" t="s">
         <v>290</v>
       </c>
@@ -8994,7 +9132,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="104" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:23">
       <c r="B104" s="4" t="s">
         <v>291</v>
       </c>
@@ -9036,7 +9174,7 @@
       <c r="V104" s="13"/>
       <c r="W104" s="13"/>
     </row>
-    <row r="105" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:23">
       <c r="B105" s="4" t="s">
         <v>292</v>
       </c>
@@ -9100,7 +9238,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="106" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:23">
       <c r="B106" s="4" t="s">
         <v>33</v>
       </c>
@@ -9164,7 +9302,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="107" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:23">
       <c r="B107" s="4" t="s">
         <v>34</v>
       </c>
@@ -9192,7 +9330,7 @@
       <c r="V107" s="13"/>
       <c r="W107" s="13"/>
     </row>
-    <row r="108" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:23">
       <c r="B108" s="4"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -9216,7 +9354,7 @@
       <c r="V108" s="13"/>
       <c r="W108" s="13"/>
     </row>
-    <row r="109" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:23">
       <c r="B109" s="4" t="s">
         <v>35</v>
       </c>
@@ -9282,7 +9420,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="110" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:23">
       <c r="B110" s="4" t="s">
         <v>36</v>
       </c>
@@ -9344,7 +9482,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="111" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:23">
       <c r="B111" s="4" t="s">
         <v>37</v>
       </c>
@@ -9400,7 +9538,7 @@
       <c r="V111" s="13"/>
       <c r="W111" s="13"/>
     </row>
-    <row r="112" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:23">
       <c r="B112" s="4" t="s">
         <v>38</v>
       </c>
@@ -9460,7 +9598,7 @@
       </c>
       <c r="W112" s="13"/>
     </row>
-    <row r="113" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:23">
       <c r="B113" s="4"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
@@ -9484,7 +9622,7 @@
       <c r="V113" s="13"/>
       <c r="W113" s="13"/>
     </row>
-    <row r="114" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:23">
       <c r="B114" s="4" t="s">
         <v>39</v>
       </c>
@@ -9530,7 +9668,7 @@
       <c r="V114" s="13"/>
       <c r="W114" s="13"/>
     </row>
-    <row r="115" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:23">
       <c r="B115" s="5" t="s">
         <v>8</v>
       </c>
@@ -9558,7 +9696,7 @@
       <c r="V115" s="13"/>
       <c r="W115" s="13"/>
     </row>
-    <row r="116" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:23">
       <c r="B116" s="4" t="s">
         <v>40</v>
       </c>
@@ -9598,7 +9736,7 @@
       </c>
       <c r="W116" s="13"/>
     </row>
-    <row r="117" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:23">
       <c r="B117" s="4" t="s">
         <v>41</v>
       </c>
@@ -9630,7 +9768,7 @@
       <c r="V117" s="13"/>
       <c r="W117" s="13"/>
     </row>
-    <row r="118" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:23">
       <c r="B118" s="4"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
@@ -9654,7 +9792,7 @@
       <c r="V118" s="13"/>
       <c r="W118" s="13"/>
     </row>
-    <row r="119" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:23">
       <c r="B119" s="4" t="s">
         <v>42</v>
       </c>
@@ -9720,7 +9858,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="120" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:23">
       <c r="B120" s="4" t="s">
         <v>43</v>
       </c>
@@ -9778,7 +9916,7 @@
       </c>
       <c r="W120" s="13"/>
     </row>
-    <row r="121" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:23">
       <c r="B121" s="4" t="s">
         <v>44</v>
       </c>
@@ -9836,7 +9974,7 @@
       </c>
       <c r="W121" s="13"/>
     </row>
-    <row r="122" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:23">
       <c r="B122" s="4" t="s">
         <v>45</v>
       </c>
@@ -9882,7 +10020,7 @@
       <c r="V122" s="13"/>
       <c r="W122" s="13"/>
     </row>
-    <row r="123" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:23">
       <c r="B123" s="4"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
@@ -9906,7 +10044,7 @@
       <c r="V123" s="13"/>
       <c r="W123" s="13"/>
     </row>
-    <row r="124" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:23">
       <c r="B124" s="4" t="s">
         <v>46</v>
       </c>
@@ -9936,7 +10074,7 @@
       <c r="V124" s="13"/>
       <c r="W124" s="13"/>
     </row>
-    <row r="125" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:23">
       <c r="B125" s="4" t="s">
         <v>47</v>
       </c>
@@ -9968,7 +10106,7 @@
       <c r="V125" s="13"/>
       <c r="W125" s="13"/>
     </row>
-    <row r="126" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:23">
       <c r="B126" s="4" t="s">
         <v>48</v>
       </c>
@@ -10036,7 +10174,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="127" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:23">
       <c r="B127" s="5" t="s">
         <v>8</v>
       </c>
@@ -10066,7 +10204,7 @@
       <c r="V127" s="13"/>
       <c r="W127" s="13"/>
     </row>
-    <row r="128" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:23">
       <c r="B128" s="4"/>
       <c r="C128" s="3"/>
       <c r="D128" s="19"/>
@@ -10090,7 +10228,7 @@
       <c r="V128" s="13"/>
       <c r="W128" s="13"/>
     </row>
-    <row r="129" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:23">
       <c r="B129" s="4" t="s">
         <v>49</v>
       </c>
@@ -10156,7 +10294,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="130" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:23">
       <c r="B130" s="4" t="s">
         <v>50</v>
       </c>
@@ -10218,7 +10356,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="131" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:23">
       <c r="B131" s="4" t="s">
         <v>51</v>
       </c>
@@ -10284,7 +10422,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="132" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:23">
       <c r="B132" s="4" t="s">
         <v>52</v>
       </c>
@@ -10322,7 +10460,7 @@
       </c>
       <c r="W132" s="13"/>
     </row>
-    <row r="133" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:23">
       <c r="B133" s="4"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
@@ -10346,7 +10484,7 @@
       <c r="V133" s="13"/>
       <c r="W133" s="13"/>
     </row>
-    <row r="134" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:23">
       <c r="B134" s="4" t="s">
         <v>53</v>
       </c>
@@ -10392,7 +10530,7 @@
       <c r="V134" s="13"/>
       <c r="W134" s="13"/>
     </row>
-    <row r="135" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:23">
       <c r="B135" s="4" t="s">
         <v>54</v>
       </c>
@@ -10438,7 +10576,7 @@
       <c r="V135" s="13"/>
       <c r="W135" s="13"/>
     </row>
-    <row r="136" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:23">
       <c r="B136" s="4" t="s">
         <v>55</v>
       </c>
@@ -10484,7 +10622,7 @@
       <c r="V136" s="13"/>
       <c r="W136" s="13"/>
     </row>
-    <row r="137" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:23">
       <c r="B137" s="4" t="s">
         <v>56</v>
       </c>
@@ -10552,7 +10690,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:23">
       <c r="B138" s="4"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
@@ -10576,7 +10714,7 @@
       <c r="V138" s="13"/>
       <c r="W138" s="13"/>
     </row>
-    <row r="139" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:23">
       <c r="B139" s="4" t="s">
         <v>57</v>
       </c>
@@ -10640,7 +10778,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="140" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:23">
       <c r="B140" s="4"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
@@ -10664,7 +10802,7 @@
       <c r="V140" s="13"/>
       <c r="W140" s="13"/>
     </row>
-    <row r="141" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:23">
       <c r="B141" s="4" t="s">
         <v>58</v>
       </c>
@@ -10696,7 +10834,7 @@
       <c r="V141" s="14"/>
       <c r="W141" s="14"/>
     </row>
-    <row r="142" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:23">
       <c r="B142" s="4"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
@@ -10720,7 +10858,7 @@
       <c r="V142" s="13"/>
       <c r="W142" s="13"/>
     </row>
-    <row r="143" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:23">
       <c r="B143" s="4" t="s">
         <v>59</v>
       </c>
@@ -10784,7 +10922,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="144" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:23">
       <c r="B144" s="4" t="s">
         <v>60</v>
       </c>
@@ -10848,7 +10986,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="145" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:23">
       <c r="B145" s="4" t="s">
         <v>61</v>
       </c>
@@ -10912,7 +11050,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="146" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:23">
       <c r="B146" s="4" t="s">
         <v>62</v>
       </c>
@@ -10976,7 +11114,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="147" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:23">
       <c r="B147" s="4" t="s">
         <v>63</v>
       </c>
@@ -11040,7 +11178,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="148" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:23">
       <c r="B148" s="4" t="s">
         <v>64</v>
       </c>
@@ -11100,7 +11238,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="149" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:23">
       <c r="B149" s="4" t="s">
         <v>65</v>
       </c>
@@ -11166,7 +11304,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="150" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:23">
       <c r="B150" s="4" t="s">
         <v>66</v>
       </c>
@@ -11198,7 +11336,7 @@
       <c r="V150" s="13"/>
       <c r="W150" s="13"/>
     </row>
-    <row r="151" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:23">
       <c r="B151" s="4" t="s">
         <v>67</v>
       </c>
@@ -11230,7 +11368,7 @@
       <c r="V151" s="13"/>
       <c r="W151" s="13"/>
     </row>
-    <row r="152" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:23">
       <c r="B152" s="5" t="s">
         <v>8</v>
       </c>
@@ -11258,7 +11396,7 @@
       <c r="V152" s="13"/>
       <c r="W152" s="13"/>
     </row>
-    <row r="153" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:23">
       <c r="B153" s="4" t="s">
         <v>68</v>
       </c>
@@ -11322,7 +11460,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="154" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:23">
       <c r="B154" s="4" t="s">
         <v>68</v>
       </c>
@@ -11386,7 +11524,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="155" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:23">
       <c r="B155" s="4" t="s">
         <v>69</v>
       </c>
@@ -11452,7 +11590,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="156" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:23">
       <c r="B156" s="4" t="s">
         <v>69</v>
       </c>
@@ -11518,7 +11656,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="157" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:23">
       <c r="B157" s="5" t="s">
         <v>8</v>
       </c>
@@ -11546,7 +11684,7 @@
       <c r="V157" s="13"/>
       <c r="W157" s="13"/>
     </row>
-    <row r="158" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:23">
       <c r="B158" s="5" t="s">
         <v>8</v>
       </c>
@@ -11574,7 +11712,7 @@
       <c r="V158" s="13"/>
       <c r="W158" s="13"/>
     </row>
-    <row r="159" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:23">
       <c r="B159" s="4"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
@@ -11598,7 +11736,7 @@
       <c r="V159" s="13"/>
       <c r="W159" s="13"/>
     </row>
-    <row r="160" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:23">
       <c r="B160" s="4" t="s">
         <v>70</v>
       </c>
@@ -11632,7 +11770,7 @@
       <c r="V160" s="13"/>
       <c r="W160" s="13"/>
     </row>
-    <row r="161" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:23">
       <c r="B161" s="4" t="s">
         <v>70</v>
       </c>
@@ -11666,7 +11804,7 @@
       <c r="V161" s="13"/>
       <c r="W161" s="13"/>
     </row>
-    <row r="162" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:23">
       <c r="B162" s="4" t="s">
         <v>71</v>
       </c>
@@ -11710,7 +11848,7 @@
       <c r="V162" s="13"/>
       <c r="W162" s="13"/>
     </row>
-    <row r="163" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:23">
       <c r="B163" s="4" t="s">
         <v>71</v>
       </c>
@@ -11754,7 +11892,7 @@
       <c r="V163" s="13"/>
       <c r="W163" s="13"/>
     </row>
-    <row r="164" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:23">
       <c r="B164" s="4" t="s">
         <v>72</v>
       </c>
@@ -11810,7 +11948,7 @@
       </c>
       <c r="W164" s="13"/>
     </row>
-    <row r="165" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:23">
       <c r="B165" s="4" t="s">
         <v>72</v>
       </c>
@@ -11866,7 +12004,7 @@
       </c>
       <c r="W165" s="13"/>
     </row>
-    <row r="166" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:23">
       <c r="B166" s="4" t="s">
         <v>73</v>
       </c>
@@ -11932,7 +12070,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="167" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:23">
       <c r="B167" s="4" t="s">
         <v>73</v>
       </c>
@@ -11998,7 +12136,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="168" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:23">
       <c r="B168" s="4" t="s">
         <v>74</v>
       </c>
@@ -12042,7 +12180,7 @@
       <c r="V168" s="13"/>
       <c r="W168" s="13"/>
     </row>
-    <row r="169" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:23">
       <c r="B169" s="4" t="s">
         <v>74</v>
       </c>
@@ -12086,7 +12224,7 @@
       <c r="V169" s="13"/>
       <c r="W169" s="13"/>
     </row>
-    <row r="170" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:23">
       <c r="B170" s="5" t="s">
         <v>8</v>
       </c>
@@ -12114,7 +12252,7 @@
       <c r="V170" s="13"/>
       <c r="W170" s="13"/>
     </row>
-    <row r="171" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:23">
       <c r="B171" s="5" t="s">
         <v>8</v>
       </c>
@@ -12142,7 +12280,7 @@
       <c r="V171" s="13"/>
       <c r="W171" s="13"/>
     </row>
-    <row r="172" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:23">
       <c r="B172" s="5" t="s">
         <v>8</v>
       </c>
@@ -12170,7 +12308,7 @@
       <c r="V172" s="13"/>
       <c r="W172" s="13"/>
     </row>
-    <row r="173" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:23">
       <c r="B173" s="5" t="s">
         <v>8</v>
       </c>
@@ -12198,7 +12336,7 @@
       <c r="V173" s="13"/>
       <c r="W173" s="13"/>
     </row>
-    <row r="174" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:23">
       <c r="B174" s="5" t="s">
         <v>8</v>
       </c>
@@ -12226,7 +12364,7 @@
       <c r="V174" s="13"/>
       <c r="W174" s="13"/>
     </row>
-    <row r="175" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:23">
       <c r="B175" s="5" t="s">
         <v>8</v>
       </c>
@@ -12254,7 +12392,7 @@
       <c r="V175" s="13"/>
       <c r="W175" s="13"/>
     </row>
-    <row r="176" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:23">
       <c r="B176" s="4"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
@@ -12278,7 +12416,7 @@
       <c r="V176" s="13"/>
       <c r="W176" s="13"/>
     </row>
-    <row r="177" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:23">
       <c r="B177" s="4" t="s">
         <v>75</v>
       </c>
@@ -12322,7 +12460,7 @@
       <c r="V177" s="13"/>
       <c r="W177" s="13"/>
     </row>
-    <row r="178" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:23">
       <c r="B178" s="4" t="s">
         <v>76</v>
       </c>
@@ -12366,7 +12504,7 @@
       <c r="V178" s="13"/>
       <c r="W178" s="13"/>
     </row>
-    <row r="179" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:23">
       <c r="B179" s="4" t="s">
         <v>77</v>
       </c>
@@ -12410,7 +12548,7 @@
       <c r="V179" s="13"/>
       <c r="W179" s="13"/>
     </row>
-    <row r="180" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:23">
       <c r="B180" s="4" t="s">
         <v>78</v>
       </c>
@@ -12454,7 +12592,7 @@
       <c r="V180" s="13"/>
       <c r="W180" s="13"/>
     </row>
-    <row r="181" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:23">
       <c r="B181" s="5" t="s">
         <v>8</v>
       </c>
@@ -12482,7 +12620,7 @@
       <c r="V181" s="13"/>
       <c r="W181" s="13"/>
     </row>
-    <row r="182" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:23">
       <c r="B182" s="5" t="s">
         <v>8</v>
       </c>
@@ -12510,7 +12648,7 @@
       <c r="V182" s="13"/>
       <c r="W182" s="13"/>
     </row>
-    <row r="183" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:23">
       <c r="B183" s="4" t="s">
         <v>79</v>
       </c>
@@ -12544,7 +12682,7 @@
       <c r="V183" s="13"/>
       <c r="W183" s="13"/>
     </row>
-    <row r="184" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:23">
       <c r="B184" s="4" t="s">
         <v>80</v>
       </c>
@@ -12578,7 +12716,7 @@
       <c r="V184" s="13"/>
       <c r="W184" s="13"/>
     </row>
-    <row r="185" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:23">
       <c r="B185" s="4" t="s">
         <v>81</v>
       </c>
@@ -12612,7 +12750,7 @@
       <c r="V185" s="13"/>
       <c r="W185" s="13"/>
     </row>
-    <row r="186" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:23">
       <c r="B186" s="4" t="s">
         <v>82</v>
       </c>
@@ -12646,7 +12784,7 @@
       <c r="V186" s="13"/>
       <c r="W186" s="13"/>
     </row>
-    <row r="187" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:23">
       <c r="B187" s="4" t="s">
         <v>83</v>
       </c>
@@ -12682,7 +12820,7 @@
       <c r="V187" s="13"/>
       <c r="W187" s="13"/>
     </row>
-    <row r="188" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:23">
       <c r="B188" s="4" t="s">
         <v>84</v>
       </c>
@@ -12716,7 +12854,7 @@
       <c r="V188" s="13"/>
       <c r="W188" s="13"/>
     </row>
-    <row r="189" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:23">
       <c r="B189" s="4" t="s">
         <v>85</v>
       </c>
@@ -12748,7 +12886,7 @@
       <c r="V189" s="13"/>
       <c r="W189" s="13"/>
     </row>
-    <row r="190" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:23">
       <c r="B190" s="5" t="s">
         <v>8</v>
       </c>
@@ -12776,7 +12914,7 @@
       <c r="V190" s="13"/>
       <c r="W190" s="13"/>
     </row>
-    <row r="191" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:23">
       <c r="B191" s="5" t="s">
         <v>8</v>
       </c>
@@ -12804,7 +12942,7 @@
       <c r="V191" s="13"/>
       <c r="W191" s="13"/>
     </row>
-    <row r="192" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:23">
       <c r="B192" s="5" t="s">
         <v>8</v>
       </c>
@@ -12832,7 +12970,7 @@
       <c r="V192" s="13"/>
       <c r="W192" s="13"/>
     </row>
-    <row r="193" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:23">
       <c r="B193" s="4"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
@@ -12856,7 +12994,7 @@
       <c r="V193" s="13"/>
       <c r="W193" s="13"/>
     </row>
-    <row r="194" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:23">
       <c r="B194" s="4" t="s">
         <v>68</v>
       </c>
@@ -12920,7 +13058,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="195" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:23">
       <c r="B195" s="4" t="s">
         <v>68</v>
       </c>
@@ -12984,7 +13122,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="196" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:23">
       <c r="B196" s="4" t="s">
         <v>69</v>
       </c>
@@ -13050,7 +13188,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="197" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:23">
       <c r="B197" s="4" t="s">
         <v>70</v>
       </c>
@@ -13084,7 +13222,7 @@
       <c r="V197" s="13"/>
       <c r="W197" s="13"/>
     </row>
-    <row r="198" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:23">
       <c r="B198" s="4" t="s">
         <v>71</v>
       </c>
@@ -13128,7 +13266,7 @@
       <c r="V198" s="13"/>
       <c r="W198" s="13"/>
     </row>
-    <row r="199" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:23">
       <c r="B199" s="4" t="s">
         <v>72</v>
       </c>
@@ -13184,7 +13322,7 @@
       </c>
       <c r="W199" s="13"/>
     </row>
-    <row r="200" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:23">
       <c r="B200" s="4" t="s">
         <v>73</v>
       </c>
@@ -13250,7 +13388,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="201" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:23">
       <c r="B201" s="4" t="s">
         <v>73</v>
       </c>
@@ -13316,7 +13454,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="202" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:23">
       <c r="B202" s="4" t="s">
         <v>74</v>
       </c>
@@ -13360,7 +13498,7 @@
       <c r="V202" s="13"/>
       <c r="W202" s="13"/>
     </row>
-    <row r="203" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:23">
       <c r="B203" s="5" t="s">
         <v>8</v>
       </c>
@@ -13388,7 +13526,7 @@
       <c r="V203" s="13"/>
       <c r="W203" s="13"/>
     </row>
-    <row r="204" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:23">
       <c r="B204" s="4" t="s">
         <v>86</v>
       </c>
@@ -13452,7 +13590,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="205" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:23">
       <c r="B205" s="5" t="s">
         <v>8</v>
       </c>
@@ -13480,7 +13618,7 @@
       <c r="V205" s="13"/>
       <c r="W205" s="13"/>
     </row>
-    <row r="206" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:23">
       <c r="B206" s="5" t="s">
         <v>8</v>
       </c>
@@ -13508,7 +13646,7 @@
       <c r="V206" s="13"/>
       <c r="W206" s="13"/>
     </row>
-    <row r="207" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:23">
       <c r="B207" s="5" t="s">
         <v>8</v>
       </c>
@@ -13536,7 +13674,7 @@
       <c r="V207" s="13"/>
       <c r="W207" s="13"/>
     </row>
-    <row r="208" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:23">
       <c r="B208" s="5" t="s">
         <v>8</v>
       </c>
@@ -13564,7 +13702,7 @@
       <c r="V208" s="13"/>
       <c r="W208" s="13"/>
     </row>
-    <row r="209" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:23">
       <c r="B209" s="5" t="s">
         <v>8</v>
       </c>
@@ -13592,7 +13730,7 @@
       <c r="V209" s="13"/>
       <c r="W209" s="13"/>
     </row>
-    <row r="210" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:23">
       <c r="B210" s="4"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
@@ -13616,7 +13754,7 @@
       <c r="V210" s="13"/>
       <c r="W210" s="13"/>
     </row>
-    <row r="211" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:23">
       <c r="B211" s="4" t="s">
         <v>87</v>
       </c>
@@ -13682,7 +13820,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="212" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:23">
       <c r="B212" s="4" t="s">
         <v>88</v>
       </c>
@@ -13748,7 +13886,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="213" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:23">
       <c r="B213" s="4" t="s">
         <v>89</v>
       </c>
@@ -13784,7 +13922,7 @@
       <c r="V213" s="13"/>
       <c r="W213" s="13"/>
     </row>
-    <row r="214" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:23">
       <c r="B214" s="4" t="s">
         <v>90</v>
       </c>
@@ -13842,7 +13980,7 @@
       </c>
       <c r="W214" s="13"/>
     </row>
-    <row r="215" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:23">
       <c r="B215" s="4"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
@@ -13866,7 +14004,7 @@
       <c r="V215" s="13"/>
       <c r="W215" s="13"/>
     </row>
-    <row r="216" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:23">
       <c r="B216" s="4" t="s">
         <v>91</v>
       </c>
@@ -13902,7 +14040,7 @@
       <c r="V216" s="13"/>
       <c r="W216" s="13"/>
     </row>
-    <row r="217" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:23">
       <c r="B217" s="4" t="s">
         <v>92</v>
       </c>
@@ -13966,7 +14104,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="218" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:23">
       <c r="B218" s="4" t="s">
         <v>93</v>
       </c>
@@ -14026,7 +14164,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="219" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:23">
       <c r="B219" s="4" t="s">
         <v>94</v>
       </c>
@@ -14092,7 +14230,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="220" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:23">
       <c r="B220" s="4" t="s">
         <v>95</v>
       </c>
@@ -14128,7 +14266,7 @@
       <c r="V220" s="13"/>
       <c r="W220" s="13"/>
     </row>
-    <row r="221" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:23">
       <c r="B221" s="4" t="s">
         <v>96</v>
       </c>
@@ -14164,7 +14302,7 @@
       <c r="V221" s="13"/>
       <c r="W221" s="13"/>
     </row>
-    <row r="222" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:23">
       <c r="B222" s="4" t="s">
         <v>97</v>
       </c>
@@ -14202,7 +14340,7 @@
       <c r="V222" s="13"/>
       <c r="W222" s="13"/>
     </row>
-    <row r="223" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:23">
       <c r="B223" s="4" t="s">
         <v>98</v>
       </c>
@@ -14270,7 +14408,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="224" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:23">
       <c r="B224" s="4"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
@@ -14294,7 +14432,7 @@
       <c r="V224" s="13"/>
       <c r="W224" s="13"/>
     </row>
-    <row r="225" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:23">
       <c r="B225" s="4" t="s">
         <v>68</v>
       </c>
@@ -14360,7 +14498,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="226" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:23">
       <c r="B226" s="4" t="s">
         <v>73</v>
       </c>
@@ -14428,7 +14566,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="227" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:23">
       <c r="B227" s="5" t="s">
         <v>8</v>
       </c>
@@ -14458,7 +14596,7 @@
       <c r="V227" s="13"/>
       <c r="W227" s="13"/>
     </row>
-    <row r="228" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:23">
       <c r="B228" s="5" t="s">
         <v>8</v>
       </c>
@@ -14488,7 +14626,7 @@
       <c r="V228" s="13"/>
       <c r="W228" s="13"/>
     </row>
-    <row r="229" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:23">
       <c r="B229" s="4"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
@@ -14512,7 +14650,7 @@
       <c r="V229" s="13"/>
       <c r="W229" s="13"/>
     </row>
-    <row r="230" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:23">
       <c r="B230" s="4"/>
       <c r="C230" s="3" t="s">
         <v>231</v>
@@ -14554,7 +14692,7 @@
       <c r="V230" s="13"/>
       <c r="W230" s="13"/>
     </row>
-    <row r="231" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:23">
       <c r="B231" s="4"/>
       <c r="C231" s="3" t="s">
         <v>232</v>
@@ -14596,7 +14734,7 @@
       <c r="V231" s="13"/>
       <c r="W231" s="13"/>
     </row>
-    <row r="232" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:23">
       <c r="B232" s="4"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
@@ -14620,7 +14758,7 @@
       <c r="V232" s="13"/>
       <c r="W232" s="13"/>
     </row>
-    <row r="233" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:23">
       <c r="B233" s="4" t="s">
         <v>99</v>
       </c>
@@ -14664,7 +14802,7 @@
       <c r="V233" s="13"/>
       <c r="W233" s="13"/>
     </row>
-    <row r="234" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:23">
       <c r="B234" s="4" t="s">
         <v>100</v>
       </c>
@@ -14708,7 +14846,7 @@
       <c r="V234" s="13"/>
       <c r="W234" s="13"/>
     </row>
-    <row r="235" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:23">
       <c r="B235" s="4" t="s">
         <v>101</v>
       </c>
@@ -14752,7 +14890,7 @@
       <c r="V235" s="13"/>
       <c r="W235" s="13"/>
     </row>
-    <row r="236" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:23">
       <c r="B236" s="5" t="s">
         <v>8</v>
       </c>
@@ -14796,7 +14934,7 @@
       <c r="V236" s="13"/>
       <c r="W236" s="13"/>
     </row>
-    <row r="237" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:23">
       <c r="B237" s="4"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
@@ -14820,7 +14958,7 @@
       <c r="V237" s="13"/>
       <c r="W237" s="13"/>
     </row>
-    <row r="238" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:23">
       <c r="B238" s="4" t="s">
         <v>102</v>
       </c>
@@ -14866,7 +15004,7 @@
       <c r="V238" s="13"/>
       <c r="W238" s="13"/>
     </row>
-    <row r="239" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:23">
       <c r="B239" s="4" t="s">
         <v>77</v>
       </c>
@@ -14912,7 +15050,7 @@
       <c r="V239" s="13"/>
       <c r="W239" s="13"/>
     </row>
-    <row r="240" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:23">
       <c r="B240" s="4" t="s">
         <v>103</v>
       </c>
@@ -14958,7 +15096,7 @@
       <c r="V240" s="13"/>
       <c r="W240" s="13"/>
     </row>
-    <row r="241" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="241" spans="2:23">
       <c r="B241" s="4" t="s">
         <v>78</v>
       </c>
@@ -15004,7 +15142,7 @@
       <c r="V241" s="13"/>
       <c r="W241" s="13"/>
     </row>
-    <row r="242" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:23">
       <c r="B242" s="4"/>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
@@ -15028,7 +15166,7 @@
       <c r="V242" s="13"/>
       <c r="W242" s="13"/>
     </row>
-    <row r="243" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="243" spans="2:23">
       <c r="B243" s="4" t="s">
         <v>104</v>
       </c>
@@ -15076,7 +15214,7 @@
       <c r="V243" s="13"/>
       <c r="W243" s="13"/>
     </row>
-    <row r="244" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="244" spans="2:23">
       <c r="B244" s="4" t="s">
         <v>105</v>
       </c>
@@ -15142,7 +15280,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="245" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:23">
       <c r="B245" s="4" t="s">
         <v>106</v>
       </c>
@@ -15208,7 +15346,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="246" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="246" spans="2:23">
       <c r="B246" s="4" t="s">
         <v>107</v>
       </c>
@@ -15274,7 +15412,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="247" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="247" spans="2:23">
       <c r="B247" s="4" t="s">
         <v>108</v>
       </c>
@@ -15318,7 +15456,7 @@
       <c r="V247" s="13"/>
       <c r="W247" s="13"/>
     </row>
-    <row r="248" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="248" spans="2:23">
       <c r="B248" s="4" t="s">
         <v>109</v>
       </c>
@@ -15384,7 +15522,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="249" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="249" spans="2:23">
       <c r="B249" s="4" t="s">
         <v>110</v>
       </c>
@@ -15450,7 +15588,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="250" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="250" spans="2:23">
       <c r="B250" s="4" t="s">
         <v>111</v>
       </c>
@@ -15512,7 +15650,7 @@
       </c>
       <c r="W250" s="13"/>
     </row>
-    <row r="251" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="251" spans="2:23">
       <c r="B251" s="4" t="s">
         <v>112</v>
       </c>
@@ -15574,7 +15712,7 @@
       </c>
       <c r="W251" s="13"/>
     </row>
-    <row r="252" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="252" spans="2:23">
       <c r="B252" s="4" t="s">
         <v>113</v>
       </c>
@@ -15606,7 +15744,7 @@
       <c r="V252" s="13"/>
       <c r="W252" s="13"/>
     </row>
-    <row r="253" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="253" spans="2:23">
       <c r="B253" s="4" t="s">
         <v>114</v>
       </c>
@@ -15672,7 +15810,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="254" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="254" spans="2:23">
       <c r="B254" s="5" t="s">
         <v>8</v>
       </c>
@@ -15700,7 +15838,7 @@
       <c r="V254" s="13"/>
       <c r="W254" s="13"/>
     </row>
-    <row r="255" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="255" spans="2:23">
       <c r="B255" s="4" t="s">
         <v>115</v>
       </c>
@@ -15732,7 +15870,7 @@
       <c r="V255" s="13"/>
       <c r="W255" s="13"/>
     </row>
-    <row r="256" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="256" spans="2:23">
       <c r="B256" s="4" t="s">
         <v>116</v>
       </c>
@@ -15768,7 +15906,7 @@
       <c r="V256" s="13"/>
       <c r="W256" s="13"/>
     </row>
-    <row r="257" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="257" spans="2:23">
       <c r="B257" s="4" t="s">
         <v>117</v>
       </c>
@@ -15806,7 +15944,7 @@
       <c r="V257" s="13"/>
       <c r="W257" s="13"/>
     </row>
-    <row r="258" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:23">
       <c r="B258" s="4" t="s">
         <v>118</v>
       </c>
@@ -15864,7 +16002,7 @@
       </c>
       <c r="W258" s="13"/>
     </row>
-    <row r="259" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="259" spans="2:23">
       <c r="B259" s="4" t="s">
         <v>119</v>
       </c>
@@ -15922,7 +16060,7 @@
       </c>
       <c r="W259" s="13"/>
     </row>
-    <row r="260" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="260" spans="2:23">
       <c r="B260" s="4" t="s">
         <v>120</v>
       </c>
@@ -15980,7 +16118,7 @@
       </c>
       <c r="W260" s="13"/>
     </row>
-    <row r="261" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="261" spans="2:23">
       <c r="B261" s="4" t="s">
         <v>121</v>
       </c>
@@ -16038,7 +16176,7 @@
       </c>
       <c r="W261" s="13"/>
     </row>
-    <row r="262" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="262" spans="2:23">
       <c r="B262" s="4" t="s">
         <v>122</v>
       </c>
@@ -16084,7 +16222,7 @@
       <c r="V262" s="13"/>
       <c r="W262" s="13"/>
     </row>
-    <row r="263" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="263" spans="2:23">
       <c r="B263" s="5" t="s">
         <v>8</v>
       </c>
@@ -16112,7 +16250,7 @@
       <c r="V263" s="13"/>
       <c r="W263" s="13"/>
     </row>
-    <row r="264" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="264" spans="2:23">
       <c r="B264" s="4" t="s">
         <v>123</v>
       </c>
@@ -16170,7 +16308,7 @@
       </c>
       <c r="W264" s="13"/>
     </row>
-    <row r="265" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="265" spans="2:23">
       <c r="B265" s="4" t="s">
         <v>124</v>
       </c>
@@ -16228,7 +16366,7 @@
       </c>
       <c r="W265" s="13"/>
     </row>
-    <row r="266" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="266" spans="2:23">
       <c r="B266" s="5" t="s">
         <v>8</v>
       </c>
@@ -16256,7 +16394,7 @@
       <c r="V266" s="13"/>
       <c r="W266" s="13"/>
     </row>
-    <row r="267" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="267" spans="2:23">
       <c r="B267" s="5" t="s">
         <v>125</v>
       </c>
@@ -16284,7 +16422,7 @@
       <c r="V267" s="13"/>
       <c r="W267" s="13"/>
     </row>
-    <row r="268" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="268" spans="2:23">
       <c r="B268" s="5" t="s">
         <v>125</v>
       </c>
@@ -16312,7 +16450,7 @@
       <c r="V268" s="13"/>
       <c r="W268" s="13"/>
     </row>
-    <row r="269" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="269" spans="2:23">
       <c r="B269" s="5" t="s">
         <v>125</v>
       </c>
@@ -16340,7 +16478,7 @@
       <c r="V269" s="13"/>
       <c r="W269" s="13"/>
     </row>
-    <row r="270" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="270" spans="2:23">
       <c r="B270" s="5" t="s">
         <v>125</v>
       </c>
@@ -16368,7 +16506,7 @@
       <c r="V270" s="13"/>
       <c r="W270" s="13"/>
     </row>
-    <row r="271" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="271" spans="2:23">
       <c r="B271" s="5" t="s">
         <v>125</v>
       </c>
@@ -16396,7 +16534,7 @@
       <c r="V271" s="13"/>
       <c r="W271" s="13"/>
     </row>
-    <row r="272" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="272" spans="2:23">
       <c r="B272" s="5" t="s">
         <v>125</v>
       </c>
@@ -16424,7 +16562,7 @@
       <c r="V272" s="13"/>
       <c r="W272" s="13"/>
     </row>
-    <row r="273" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="273" spans="2:23">
       <c r="B273" s="5" t="s">
         <v>125</v>
       </c>
@@ -16452,7 +16590,7 @@
       <c r="V273" s="13"/>
       <c r="W273" s="13"/>
     </row>
-    <row r="274" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="274" spans="2:23">
       <c r="B274" s="5" t="s">
         <v>125</v>
       </c>
@@ -16480,7 +16618,7 @@
       <c r="V274" s="13"/>
       <c r="W274" s="13"/>
     </row>
-    <row r="275" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:23">
       <c r="B275" s="4"/>
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
@@ -16504,7 +16642,7 @@
       <c r="V275" s="13"/>
       <c r="W275" s="13"/>
     </row>
-    <row r="276" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="276" spans="2:23">
       <c r="B276" s="4"/>
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
@@ -16528,7 +16666,7 @@
       <c r="V276" s="14"/>
       <c r="W276" s="14"/>
     </row>
-    <row r="277" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="277" spans="2:23">
       <c r="B277" s="4"/>
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
@@ -16552,7 +16690,7 @@
       <c r="V277" s="14"/>
       <c r="W277" s="14"/>
     </row>
-    <row r="278" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="278" spans="2:23">
       <c r="B278" s="4"/>
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
@@ -16576,7 +16714,7 @@
       <c r="V278" s="14"/>
       <c r="W278" s="14"/>
     </row>
-    <row r="279" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="279" spans="2:23">
       <c r="B279" s="4"/>
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
@@ -16600,7 +16738,7 @@
       <c r="V279" s="14"/>
       <c r="W279" s="14"/>
     </row>
-    <row r="280" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="280" spans="2:23">
       <c r="B280" s="4"/>
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
@@ -16624,7 +16762,7 @@
       <c r="V280" s="14"/>
       <c r="W280" s="14"/>
     </row>
-    <row r="281" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="281" spans="2:23">
       <c r="B281" s="4"/>
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
@@ -16648,7 +16786,7 @@
       <c r="V281" s="14"/>
       <c r="W281" s="14"/>
     </row>
-    <row r="282" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="282" spans="2:23">
       <c r="B282" s="4"/>
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
@@ -16672,7 +16810,7 @@
       <c r="V282" s="14"/>
       <c r="W282" s="14"/>
     </row>
-    <row r="283" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="283" spans="2:23">
       <c r="B283" s="4"/>
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
@@ -16696,7 +16834,7 @@
       <c r="V283" s="14"/>
       <c r="W283" s="14"/>
     </row>
-    <row r="284" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="284" spans="2:23">
       <c r="B284" s="4"/>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
@@ -16720,7 +16858,7 @@
       <c r="V284" s="14"/>
       <c r="W284" s="14"/>
     </row>
-    <row r="285" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="285" spans="2:23">
       <c r="B285" s="5"/>
       <c r="C285" s="17"/>
       <c r="D285" s="3"/>
@@ -16744,7 +16882,7 @@
       <c r="V285" s="14"/>
       <c r="W285" s="14"/>
     </row>
-    <row r="286" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="286" spans="2:23">
       <c r="B286" s="4"/>
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
@@ -16768,7 +16906,7 @@
       <c r="V286" s="14"/>
       <c r="W286" s="14"/>
     </row>
-    <row r="287" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="287" spans="2:23">
       <c r="B287" s="5"/>
       <c r="C287" s="17"/>
       <c r="D287" s="3"/>
@@ -16792,7 +16930,7 @@
       <c r="V287" s="14"/>
       <c r="W287" s="14"/>
     </row>
-    <row r="288" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="288" spans="2:23">
       <c r="B288" s="5"/>
       <c r="C288" s="17"/>
       <c r="D288" s="3"/>
@@ -16816,7 +16954,7 @@
       <c r="V288" s="14"/>
       <c r="W288" s="14"/>
     </row>
-    <row r="289" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="289" spans="2:23">
       <c r="B289" s="4"/>
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
@@ -16840,7 +16978,7 @@
       <c r="V289" s="14"/>
       <c r="W289" s="14"/>
     </row>
-    <row r="290" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="290" spans="2:23">
       <c r="B290" s="4"/>
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
@@ -16864,7 +17002,7 @@
       <c r="V290" s="14"/>
       <c r="W290" s="14"/>
     </row>
-    <row r="291" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="291" spans="2:23">
       <c r="B291" s="4"/>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
@@ -16888,7 +17026,7 @@
       <c r="V291" s="14"/>
       <c r="W291" s="14"/>
     </row>
-    <row r="292" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="292" spans="2:23">
       <c r="B292" s="4"/>
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
@@ -16912,7 +17050,7 @@
       <c r="V292" s="13"/>
       <c r="W292" s="13"/>
     </row>
-    <row r="293" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="293" spans="2:23">
       <c r="B293" s="4"/>
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
@@ -16936,7 +17074,7 @@
       <c r="V293" s="14"/>
       <c r="W293" s="14"/>
     </row>
-    <row r="294" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="294" spans="2:23">
       <c r="B294" s="4"/>
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
@@ -16960,7 +17098,7 @@
       <c r="V294" s="14"/>
       <c r="W294" s="14"/>
     </row>
-    <row r="295" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="295" spans="2:23">
       <c r="B295" s="4"/>
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
@@ -16984,7 +17122,7 @@
       <c r="V295" s="14"/>
       <c r="W295" s="14"/>
     </row>
-    <row r="296" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="296" spans="2:23">
       <c r="B296" s="4"/>
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
@@ -17008,7 +17146,7 @@
       <c r="V296" s="14"/>
       <c r="W296" s="14"/>
     </row>
-    <row r="297" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="297" spans="2:23">
       <c r="B297" s="4"/>
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
@@ -17032,7 +17170,7 @@
       <c r="V297" s="14"/>
       <c r="W297" s="14"/>
     </row>
-    <row r="298" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="298" spans="2:23">
       <c r="B298" s="4"/>
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
@@ -17056,7 +17194,7 @@
       <c r="V298" s="14"/>
       <c r="W298" s="14"/>
     </row>
-    <row r="299" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="299" spans="2:23">
       <c r="B299" s="4"/>
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
@@ -17080,7 +17218,7 @@
       <c r="V299" s="14"/>
       <c r="W299" s="14"/>
     </row>
-    <row r="300" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="300" spans="2:23">
       <c r="B300" s="4"/>
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
@@ -17104,7 +17242,7 @@
       <c r="V300" s="14"/>
       <c r="W300" s="14"/>
     </row>
-    <row r="301" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="301" spans="2:23">
       <c r="B301" s="4"/>
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
@@ -17128,7 +17266,7 @@
       <c r="V301" s="14"/>
       <c r="W301" s="14"/>
     </row>
-    <row r="302" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="302" spans="2:23">
       <c r="B302" s="5"/>
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
@@ -17152,7 +17290,7 @@
       <c r="V302" s="14"/>
       <c r="W302" s="14"/>
     </row>
-    <row r="303" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="303" spans="2:23">
       <c r="B303" s="4"/>
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
@@ -17176,7 +17314,7 @@
       <c r="V303" s="14"/>
       <c r="W303" s="14"/>
     </row>
-    <row r="304" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="304" spans="2:23">
       <c r="B304" s="5"/>
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
@@ -17200,7 +17338,7 @@
       <c r="V304" s="14"/>
       <c r="W304" s="14"/>
     </row>
-    <row r="305" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="305" spans="2:23">
       <c r="B305" s="5"/>
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
@@ -17224,7 +17362,7 @@
       <c r="V305" s="14"/>
       <c r="W305" s="14"/>
     </row>
-    <row r="306" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="306" spans="2:23">
       <c r="B306" s="4"/>
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
@@ -17248,7 +17386,7 @@
       <c r="V306" s="14"/>
       <c r="W306" s="14"/>
     </row>
-    <row r="307" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="307" spans="2:23">
       <c r="B307" s="4"/>
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
@@ -17272,7 +17410,7 @@
       <c r="V307" s="14"/>
       <c r="W307" s="14"/>
     </row>
-    <row r="308" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="308" spans="2:23">
       <c r="B308" s="4"/>
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
@@ -17296,7 +17434,7 @@
       <c r="V308" s="14"/>
       <c r="W308" s="14"/>
     </row>
-    <row r="309" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="309" spans="2:23">
       <c r="B309" s="4"/>
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
@@ -17320,7 +17458,7 @@
       <c r="V309" s="13"/>
       <c r="W309" s="13"/>
     </row>
-    <row r="310" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="310" spans="2:23">
       <c r="B310" s="4"/>
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
@@ -17344,7 +17482,7 @@
       <c r="V310" s="14"/>
       <c r="W310" s="14"/>
     </row>
-    <row r="311" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="311" spans="2:23">
       <c r="B311" s="4"/>
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
@@ -17368,7 +17506,7 @@
       <c r="V311" s="14"/>
       <c r="W311" s="14"/>
     </row>
-    <row r="312" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="312" spans="2:23">
       <c r="B312" s="4"/>
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
@@ -17392,7 +17530,7 @@
       <c r="V312" s="14"/>
       <c r="W312" s="14"/>
     </row>
-    <row r="313" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="313" spans="2:23">
       <c r="B313" s="4"/>
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
@@ -17416,7 +17554,7 @@
       <c r="V313" s="14"/>
       <c r="W313" s="14"/>
     </row>
-    <row r="314" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="314" spans="2:23">
       <c r="B314" s="4"/>
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
@@ -17440,7 +17578,7 @@
       <c r="V314" s="14"/>
       <c r="W314" s="14"/>
     </row>
-    <row r="315" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="315" spans="2:23">
       <c r="B315" s="4"/>
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
@@ -17464,7 +17602,7 @@
       <c r="V315" s="14"/>
       <c r="W315" s="14"/>
     </row>
-    <row r="316" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="316" spans="2:23">
       <c r="B316" s="4"/>
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
@@ -17488,7 +17626,7 @@
       <c r="V316" s="14"/>
       <c r="W316" s="14"/>
     </row>
-    <row r="317" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="317" spans="2:23">
       <c r="B317" s="4"/>
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
@@ -17512,7 +17650,7 @@
       <c r="V317" s="14"/>
       <c r="W317" s="14"/>
     </row>
-    <row r="318" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="318" spans="2:23">
       <c r="B318" s="4"/>
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
@@ -17536,7 +17674,7 @@
       <c r="V318" s="14"/>
       <c r="W318" s="14"/>
     </row>
-    <row r="319" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="319" spans="2:23">
       <c r="B319" s="5"/>
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
@@ -17560,7 +17698,7 @@
       <c r="V319" s="14"/>
       <c r="W319" s="14"/>
     </row>
-    <row r="320" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="320" spans="2:23">
       <c r="B320" s="4"/>
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
@@ -17584,7 +17722,7 @@
       <c r="V320" s="14"/>
       <c r="W320" s="14"/>
     </row>
-    <row r="321" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="321" spans="2:23">
       <c r="B321" s="5"/>
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
@@ -17608,7 +17746,7 @@
       <c r="V321" s="14"/>
       <c r="W321" s="14"/>
     </row>
-    <row r="322" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="322" spans="2:23">
       <c r="B322" s="5"/>
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
@@ -17632,7 +17770,7 @@
       <c r="V322" s="14"/>
       <c r="W322" s="14"/>
     </row>
-    <row r="323" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="323" spans="2:23">
       <c r="B323" s="4"/>
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
@@ -17656,7 +17794,7 @@
       <c r="V323" s="14"/>
       <c r="W323" s="14"/>
     </row>
-    <row r="324" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="324" spans="2:23">
       <c r="B324" s="4"/>
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
@@ -17680,7 +17818,7 @@
       <c r="V324" s="14"/>
       <c r="W324" s="14"/>
     </row>
-    <row r="325" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="325" spans="2:23">
       <c r="B325" s="4"/>
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
@@ -17704,7 +17842,7 @@
       <c r="V325" s="14"/>
       <c r="W325" s="14"/>
     </row>
-    <row r="326" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="326" spans="2:23">
       <c r="B326" s="4"/>
       <c r="C326" s="19"/>
       <c r="D326" s="19"/>
@@ -17728,7 +17866,7 @@
       <c r="V326" s="13"/>
       <c r="W326" s="13"/>
     </row>
-    <row r="327" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="327" spans="2:23">
       <c r="B327" s="4"/>
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
@@ -17752,7 +17890,7 @@
       <c r="V327" s="14"/>
       <c r="W327" s="14"/>
     </row>
-    <row r="328" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="328" spans="2:23">
       <c r="B328" s="4"/>
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
@@ -17776,7 +17914,7 @@
       <c r="V328" s="14"/>
       <c r="W328" s="14"/>
     </row>
-    <row r="329" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="329" spans="2:23">
       <c r="B329" s="4"/>
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
@@ -17800,7 +17938,7 @@
       <c r="V329" s="14"/>
       <c r="W329" s="14"/>
     </row>
-    <row r="330" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="330" spans="2:23">
       <c r="B330" s="4"/>
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
@@ -17824,7 +17962,7 @@
       <c r="V330" s="14"/>
       <c r="W330" s="14"/>
     </row>
-    <row r="331" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="331" spans="2:23">
       <c r="B331" s="4"/>
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
@@ -17848,7 +17986,7 @@
       <c r="V331" s="14"/>
       <c r="W331" s="14"/>
     </row>
-    <row r="332" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="332" spans="2:23">
       <c r="B332" s="4"/>
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
@@ -17872,7 +18010,7 @@
       <c r="V332" s="14"/>
       <c r="W332" s="14"/>
     </row>
-    <row r="333" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="333" spans="2:23">
       <c r="B333" s="4"/>
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
@@ -17896,7 +18034,7 @@
       <c r="V333" s="14"/>
       <c r="W333" s="14"/>
     </row>
-    <row r="334" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="334" spans="2:23">
       <c r="B334" s="4"/>
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
@@ -17920,7 +18058,7 @@
       <c r="V334" s="14"/>
       <c r="W334" s="14"/>
     </row>
-    <row r="335" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="335" spans="2:23">
       <c r="B335" s="4"/>
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
@@ -17944,7 +18082,7 @@
       <c r="V335" s="14"/>
       <c r="W335" s="14"/>
     </row>
-    <row r="336" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="336" spans="2:23">
       <c r="B336" s="5"/>
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
@@ -17968,7 +18106,7 @@
       <c r="V336" s="14"/>
       <c r="W336" s="14"/>
     </row>
-    <row r="337" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="337" spans="2:23">
       <c r="B337" s="4"/>
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
@@ -17992,7 +18130,7 @@
       <c r="V337" s="14"/>
       <c r="W337" s="14"/>
     </row>
-    <row r="338" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="338" spans="2:23">
       <c r="B338" s="5"/>
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
@@ -18016,7 +18154,7 @@
       <c r="V338" s="14"/>
       <c r="W338" s="14"/>
     </row>
-    <row r="339" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="339" spans="2:23">
       <c r="B339" s="5"/>
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
@@ -18040,7 +18178,7 @@
       <c r="V339" s="14"/>
       <c r="W339" s="14"/>
     </row>
-    <row r="340" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="340" spans="2:23">
       <c r="B340" s="4"/>
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
@@ -18064,7 +18202,7 @@
       <c r="V340" s="14"/>
       <c r="W340" s="14"/>
     </row>
-    <row r="341" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="341" spans="2:23">
       <c r="B341" s="4"/>
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
@@ -18088,7 +18226,7 @@
       <c r="V341" s="14"/>
       <c r="W341" s="14"/>
     </row>
-    <row r="342" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="342" spans="2:23">
       <c r="B342" s="4"/>
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
@@ -18112,7 +18250,7 @@
       <c r="V342" s="14"/>
       <c r="W342" s="14"/>
     </row>
-    <row r="343" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="343" spans="2:23">
       <c r="B343" s="4"/>
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
@@ -18136,7 +18274,7 @@
       <c r="V343" s="14"/>
       <c r="W343" s="14"/>
     </row>
-    <row r="344" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="344" spans="2:23">
       <c r="B344" s="4"/>
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
@@ -18160,7 +18298,7 @@
       <c r="V344" s="14"/>
       <c r="W344" s="14"/>
     </row>
-    <row r="345" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="345" spans="2:23">
       <c r="B345" s="4"/>
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
@@ -18184,7 +18322,7 @@
       <c r="V345" s="14"/>
       <c r="W345" s="14"/>
     </row>
-    <row r="346" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="346" spans="2:23">
       <c r="B346" s="4"/>
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
@@ -18208,7 +18346,7 @@
       <c r="V346" s="14"/>
       <c r="W346" s="14"/>
     </row>
-    <row r="347" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="347" spans="2:23">
       <c r="B347" s="4"/>
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
@@ -18232,7 +18370,7 @@
       <c r="V347" s="14"/>
       <c r="W347" s="14"/>
     </row>
-    <row r="348" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="348" spans="2:23">
       <c r="B348" s="4"/>
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
@@ -18256,7 +18394,7 @@
       <c r="V348" s="14"/>
       <c r="W348" s="14"/>
     </row>
-    <row r="349" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="349" spans="2:23">
       <c r="B349" s="4"/>
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
@@ -18280,7 +18418,7 @@
       <c r="V349" s="14"/>
       <c r="W349" s="14"/>
     </row>
-    <row r="350" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="350" spans="2:23">
       <c r="B350" s="4"/>
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
@@ -18304,7 +18442,7 @@
       <c r="V350" s="14"/>
       <c r="W350" s="14"/>
     </row>
-    <row r="351" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="351" spans="2:23">
       <c r="B351" s="4"/>
       <c r="C351" s="19"/>
       <c r="D351" s="19"/>
@@ -18328,7 +18466,7 @@
       <c r="V351" s="13"/>
       <c r="W351" s="13"/>
     </row>
-    <row r="352" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="352" spans="2:23">
       <c r="B352" s="4" t="s">
         <v>46</v>
       </c>
@@ -18392,7 +18530,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="353" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="353" spans="2:23">
       <c r="B353" s="4" t="s">
         <v>47</v>
       </c>
@@ -18436,7 +18574,7 @@
       <c r="V353" s="13"/>
       <c r="W353" s="13"/>
     </row>
-    <row r="354" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="354" spans="2:23">
       <c r="B354" s="4" t="s">
         <v>126</v>
       </c>
@@ -18500,7 +18638,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="355" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="355" spans="2:23">
       <c r="B355" s="4" t="s">
         <v>127</v>
       </c>
@@ -18534,7 +18672,7 @@
       </c>
       <c r="W355" s="13"/>
     </row>
-    <row r="356" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="356" spans="2:23">
       <c r="B356" s="4"/>
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
@@ -18558,7 +18696,7 @@
       <c r="V356" s="13"/>
       <c r="W356" s="13"/>
     </row>
-    <row r="357" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="357" spans="2:23">
       <c r="B357" s="4" t="s">
         <v>128</v>
       </c>
@@ -18586,7 +18724,7 @@
       <c r="V357" s="13"/>
       <c r="W357" s="13"/>
     </row>
-    <row r="358" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="358" spans="2:23">
       <c r="B358" s="4" t="s">
         <v>129</v>
       </c>
@@ -18614,7 +18752,7 @@
       <c r="V358" s="13"/>
       <c r="W358" s="13"/>
     </row>
-    <row r="359" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="359" spans="2:23">
       <c r="B359" s="4" t="s">
         <v>130</v>
       </c>
@@ -18642,7 +18780,7 @@
       <c r="V359" s="13"/>
       <c r="W359" s="13"/>
     </row>
-    <row r="360" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="360" spans="2:23">
       <c r="B360" s="4" t="s">
         <v>131</v>
       </c>
@@ -18670,7 +18808,7 @@
       <c r="V360" s="13"/>
       <c r="W360" s="13"/>
     </row>
-    <row r="361" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="361" spans="2:23">
       <c r="B361" s="4" t="s">
         <v>132</v>
       </c>
@@ -18698,7 +18836,7 @@
       <c r="V361" s="13"/>
       <c r="W361" s="13"/>
     </row>
-    <row r="362" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="362" spans="2:23">
       <c r="B362" s="4"/>
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
@@ -18722,7 +18860,7 @@
       <c r="V362" s="13"/>
       <c r="W362" s="13"/>
     </row>
-    <row r="363" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="363" spans="2:23">
       <c r="B363" s="4" t="s">
         <v>128</v>
       </c>
@@ -18750,7 +18888,7 @@
       <c r="V363" s="13"/>
       <c r="W363" s="13"/>
     </row>
-    <row r="364" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="364" spans="2:23">
       <c r="B364" s="4" t="s">
         <v>129</v>
       </c>
@@ -18778,7 +18916,7 @@
       <c r="V364" s="13"/>
       <c r="W364" s="13"/>
     </row>
-    <row r="365" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="365" spans="2:23">
       <c r="B365" s="4" t="s">
         <v>130</v>
       </c>
@@ -18806,7 +18944,7 @@
       <c r="V365" s="13"/>
       <c r="W365" s="13"/>
     </row>
-    <row r="366" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="366" spans="2:23">
       <c r="B366" s="4" t="s">
         <v>131</v>
       </c>
@@ -18834,7 +18972,7 @@
       <c r="V366" s="13"/>
       <c r="W366" s="13"/>
     </row>
-    <row r="367" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="367" spans="2:23">
       <c r="B367" s="4" t="s">
         <v>132</v>
       </c>
@@ -18862,7 +19000,7 @@
       <c r="V367" s="13"/>
       <c r="W367" s="13"/>
     </row>
-    <row r="368" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="368" spans="2:23">
       <c r="B368" s="4"/>
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
@@ -18886,7 +19024,7 @@
       <c r="V368" s="13"/>
       <c r="W368" s="13"/>
     </row>
-    <row r="369" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="369" spans="2:23">
       <c r="B369" s="4" t="s">
         <v>133</v>
       </c>
@@ -18916,7 +19054,7 @@
       <c r="V369" s="13"/>
       <c r="W369" s="13"/>
     </row>
-    <row r="370" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="370" spans="2:23">
       <c r="B370" s="4" t="s">
         <v>134</v>
       </c>
@@ -18946,7 +19084,7 @@
       <c r="V370" s="13"/>
       <c r="W370" s="13"/>
     </row>
-    <row r="371" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="371" spans="2:23">
       <c r="B371" s="4" t="s">
         <v>135</v>
       </c>
@@ -18976,7 +19114,7 @@
       <c r="V371" s="13"/>
       <c r="W371" s="13"/>
     </row>
-    <row r="372" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="372" spans="2:23">
       <c r="B372" s="4"/>
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
@@ -19000,7 +19138,7 @@
       <c r="V372" s="13"/>
       <c r="W372" s="13"/>
     </row>
-    <row r="373" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="373" spans="2:23">
       <c r="B373" s="4" t="s">
         <v>133</v>
       </c>
@@ -19030,7 +19168,7 @@
       <c r="V373" s="13"/>
       <c r="W373" s="13"/>
     </row>
-    <row r="374" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="374" spans="2:23">
       <c r="B374" s="4" t="s">
         <v>134</v>
       </c>
@@ -19060,7 +19198,7 @@
       <c r="V374" s="13"/>
       <c r="W374" s="13"/>
     </row>
-    <row r="375" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="375" spans="2:23">
       <c r="B375" s="4" t="s">
         <v>135</v>
       </c>
@@ -19090,7 +19228,7 @@
       <c r="V375" s="13"/>
       <c r="W375" s="13"/>
     </row>
-    <row r="376" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="376" spans="2:23">
       <c r="B376" s="4"/>
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
@@ -19114,7 +19252,7 @@
       <c r="V376" s="13"/>
       <c r="W376" s="13"/>
     </row>
-    <row r="377" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="377" spans="2:23">
       <c r="B377" s="4"/>
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
@@ -19138,7 +19276,7 @@
       <c r="V377" s="13"/>
       <c r="W377" s="13"/>
     </row>
-    <row r="378" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="378" spans="2:23">
       <c r="B378" s="4"/>
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
@@ -19162,7 +19300,7 @@
       <c r="V378" s="13"/>
       <c r="W378" s="13"/>
     </row>
-    <row r="379" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="379" spans="2:23">
       <c r="B379" s="4"/>
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
@@ -19186,7 +19324,7 @@
       <c r="V379" s="13"/>
       <c r="W379" s="13"/>
     </row>
-    <row r="380" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="380" spans="2:23">
       <c r="B380" s="4"/>
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
@@ -19210,7 +19348,7 @@
       <c r="V380" s="13"/>
       <c r="W380" s="13"/>
     </row>
-    <row r="381" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="381" spans="2:23">
       <c r="B381" s="4"/>
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
@@ -19234,7 +19372,7 @@
       <c r="V381" s="13"/>
       <c r="W381" s="13"/>
     </row>
-    <row r="382" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="382" spans="2:23">
       <c r="B382" s="4"/>
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
@@ -19258,7 +19396,7 @@
       <c r="V382" s="13"/>
       <c r="W382" s="13"/>
     </row>
-    <row r="383" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="383" spans="2:23">
       <c r="B383" s="4"/>
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
@@ -19282,7 +19420,7 @@
       <c r="V383" s="13"/>
       <c r="W383" s="13"/>
     </row>
-    <row r="384" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="384" spans="2:23">
       <c r="B384" s="4"/>
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
@@ -19306,7 +19444,7 @@
       <c r="V384" s="13"/>
       <c r="W384" s="13"/>
     </row>
-    <row r="385" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="385" spans="2:23">
       <c r="B385" s="4"/>
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
@@ -19330,7 +19468,7 @@
       <c r="V385" s="13"/>
       <c r="W385" s="13"/>
     </row>
-    <row r="386" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="386" spans="2:23">
       <c r="B386" s="4"/>
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
@@ -19354,7 +19492,7 @@
       <c r="V386" s="13"/>
       <c r="W386" s="13"/>
     </row>
-    <row r="387" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="387" spans="2:23">
       <c r="B387" s="4"/>
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
@@ -19378,7 +19516,7 @@
       <c r="V387" s="13"/>
       <c r="W387" s="13"/>
     </row>
-    <row r="388" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="388" spans="2:23">
       <c r="B388" s="4"/>
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
@@ -19402,7 +19540,7 @@
       <c r="V388" s="13"/>
       <c r="W388" s="13"/>
     </row>
-    <row r="389" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="389" spans="2:23">
       <c r="B389" s="4"/>
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
@@ -19426,7 +19564,7 @@
       <c r="V389" s="13"/>
       <c r="W389" s="13"/>
     </row>
-    <row r="390" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="390" spans="2:23">
       <c r="B390" s="4"/>
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
@@ -19450,7 +19588,7 @@
       <c r="V390" s="13"/>
       <c r="W390" s="13"/>
     </row>
-    <row r="391" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="391" spans="2:23">
       <c r="B391" s="4"/>
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
@@ -19474,7 +19612,7 @@
       <c r="V391" s="13"/>
       <c r="W391" s="13"/>
     </row>
-    <row r="392" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="392" spans="2:23">
       <c r="B392" s="4"/>
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
@@ -19498,7 +19636,7 @@
       <c r="V392" s="13"/>
       <c r="W392" s="13"/>
     </row>
-    <row r="393" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="393" spans="2:23">
       <c r="B393" s="4"/>
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
@@ -19522,7 +19660,7 @@
       <c r="V393" s="13"/>
       <c r="W393" s="13"/>
     </row>
-    <row r="394" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="394" spans="2:23">
       <c r="B394" s="4"/>
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
@@ -19546,7 +19684,7 @@
       <c r="V394" s="13"/>
       <c r="W394" s="13"/>
     </row>
-    <row r="395" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="395" spans="2:23">
       <c r="B395" s="4"/>
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
@@ -19570,7 +19708,7 @@
       <c r="V395" s="13"/>
       <c r="W395" s="13"/>
     </row>
-    <row r="396" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="396" spans="2:23">
       <c r="B396" s="4"/>
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
@@ -19594,7 +19732,7 @@
       <c r="V396" s="13"/>
       <c r="W396" s="13"/>
     </row>
-    <row r="397" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="397" spans="2:23">
       <c r="B397" s="9"/>
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
@@ -19618,7 +19756,7 @@
       <c r="V397" s="13"/>
       <c r="W397" s="13"/>
     </row>
-    <row r="398" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="398" spans="2:23">
       <c r="B398" s="9"/>
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
@@ -19642,7 +19780,7 @@
       <c r="V398" s="13"/>
       <c r="W398" s="13"/>
     </row>
-    <row r="399" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="399" spans="2:23">
       <c r="B399" s="9"/>
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
@@ -19666,7 +19804,7 @@
       <c r="V399" s="13"/>
       <c r="W399" s="13"/>
     </row>
-    <row r="400" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="400" spans="2:23">
       <c r="B400" s="9"/>
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
@@ -19690,7 +19828,7 @@
       <c r="V400" s="13"/>
       <c r="W400" s="13"/>
     </row>
-    <row r="401" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="401" spans="2:23">
       <c r="B401" s="4"/>
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
